--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -803,7 +803,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -896,7 +896,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tempo k cíli – kumulativní Won vs. Goal</a:t>
+              <a:t>Tempo k cíli – Won vs. Goal</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1613,7 +1613,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1706,7 +1706,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tempo k cíli – kumulativní Won vs. Goal</a:t>
+              <a:t>Tempo k cíli – Won vs. Goal</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2287,7 +2287,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2380,7 +2380,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tempo k cíli – kumulativní Won vs. Goal</a:t>
+              <a:t>Tempo k cíli – Won vs. Goal</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2724,7 +2724,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3054,7 +3054,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3147,7 +3147,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tempo k cíli – kumulativní Won vs. Goal</a:t>
+              <a:t>Tempo k cíli – Won vs. Goal</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3728,7 +3728,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3925,7 +3925,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tempo k cíli – kumulativní Won vs. Goal</a:t>
+              <a:t>Tempo k cíli – Won vs. Goal</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4402,7 +4402,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4940,7 +4940,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5033,7 +5033,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tempo k cíli – kumulativní Won vs. Goal</a:t>
+              <a:t>Tempo k cíli – Won vs. Goal</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5905,7 +5905,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Funnel – rozpad pipeline podle stage (06.07.)</a:t>
+              <a:t>Funnel – rozpad pipeline (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -7485,7 +7485,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generováno týdně z HubSpotu (nahrazuje ruční doplňování)</t>
+          <t>Generováno týdně z HubSpotu</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
         <v>3610753</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>4087400</v>
+        <v>4134600</v>
       </c>
     </row>
     <row r="23">
@@ -11387,7 +11387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G784"/>
+  <dimension ref="A1:G795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11409,7 +11409,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generováno týdně z HubSpotu (nahrazuje ruční doplňování)</t>
+          <t>Generováno týdně z HubSpotu</t>
         </is>
       </c>
     </row>
@@ -32126,16 +32126,16 @@
     </row>
     <row r="779">
       <c r="A779" s="4" t="n">
-        <v>396380044523</v>
+        <v>16200551119</v>
       </c>
       <c r="B779" s="4" t="inlineStr">
         <is>
-          <t>Mashreq Pakistan, Seamless Rijad 25</t>
+          <t>Jordan Ahli Bank, woodpecker</t>
         </is>
       </c>
       <c r="C779" s="4" t="inlineStr">
         <is>
-          <t>Mashreq</t>
+          <t>Jordan Ahli Bank</t>
         </is>
       </c>
       <c r="D779" s="4" t="inlineStr">
@@ -32147,22 +32147,22 @@
         <v>46219</v>
       </c>
       <c r="F779" s="6" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G779" s="4" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" s="4" t="n">
-        <v>460476222664</v>
+        <v>245212643546</v>
       </c>
       <c r="B780" s="4" t="inlineStr">
         <is>
-          <t>Al Barid Bank - from HPS</t>
+          <t>Fintech Dubai:Wio UAE</t>
         </is>
       </c>
       <c r="C780" s="4" t="inlineStr">
         <is>
-          <t>Al Barid Bank</t>
+          <t>Wio UAE</t>
         </is>
       </c>
       <c r="D780" s="4" t="inlineStr">
@@ -32174,22 +32174,22 @@
         <v>46219</v>
       </c>
       <c r="F780" s="6" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G780" s="4" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" s="4" t="n">
-        <v>501313743042</v>
+        <v>285342572762</v>
       </c>
       <c r="B781" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank DXB - discovery</t>
+          <t>Source: Linkedin; Company: Banque Patronus</t>
         </is>
       </c>
       <c r="C781" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>Banque Patronus</t>
         </is>
       </c>
       <c r="D781" s="4" t="inlineStr">
@@ -32201,22 +32201,22 @@
         <v>46219</v>
       </c>
       <c r="F781" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G781" s="4" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" s="4" t="n">
-        <v>501500277973</v>
+        <v>495269111005</v>
       </c>
       <c r="B782" s="4" t="inlineStr">
         <is>
-          <t>HSBC - Dubai OH</t>
+          <t>Manager.one: Melanie FAUCHON - contact form</t>
         </is>
       </c>
       <c r="C782" s="4" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Manager.one</t>
         </is>
       </c>
       <c r="D782" s="4" t="inlineStr">
@@ -32228,22 +32228,22 @@
         <v>46219</v>
       </c>
       <c r="F782" s="6" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G782" s="4" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" s="4" t="n">
-        <v>501500997841</v>
+        <v>285715078373</v>
       </c>
       <c r="B783" s="4" t="inlineStr">
         <is>
-          <t>Abacus Pakistan - OH LinkedIn</t>
+          <t>AXIS India</t>
         </is>
       </c>
       <c r="C783" s="4" t="inlineStr">
         <is>
-          <t>Abacus Cambridge Partners</t>
+          <t>Axis Bank</t>
         </is>
       </c>
       <c r="D783" s="4" t="inlineStr">
@@ -32255,22 +32255,22 @@
         <v>46219</v>
       </c>
       <c r="F783" s="6" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G783" s="4" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" s="4" t="n">
-        <v>496001859797</v>
+        <v>311526355159</v>
       </c>
       <c r="B784" s="4" t="inlineStr">
         <is>
-          <t>Moved to Tapix: Inbound - Manager.one - New Deal</t>
+          <t>MoneyKSA: BSF</t>
         </is>
       </c>
       <c r="C784" s="4" t="inlineStr">
         <is>
-          <t>Manager.one</t>
+          <t>Banque Saudi Fransi</t>
         </is>
       </c>
       <c r="D784" s="4" t="inlineStr">
@@ -32282,9 +32282,306 @@
         <v>46219</v>
       </c>
       <c r="F784" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G784" s="4" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="4" t="n">
+        <v>311549636806</v>
+      </c>
+      <c r="B785" s="4" t="inlineStr">
+        <is>
+          <t>MoneyKSA: Drahim</t>
+        </is>
+      </c>
+      <c r="C785" s="4" t="inlineStr">
+        <is>
+          <t>Drahim</t>
+        </is>
+      </c>
+      <c r="D785" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E785" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F785" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G785" s="4" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="4" t="n">
+        <v>311146490054</v>
+      </c>
+      <c r="B786" s="4" t="inlineStr">
+        <is>
+          <t>MoneyKSA: D360 Bank</t>
+        </is>
+      </c>
+      <c r="C786" s="4" t="inlineStr">
+        <is>
+          <t>D360 Bank</t>
+        </is>
+      </c>
+      <c r="D786" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E786" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F786" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G786" s="4" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="4" t="n">
+        <v>311146494155</v>
+      </c>
+      <c r="B787" s="4" t="inlineStr">
+        <is>
+          <t>LiP2025: United Arab Bank</t>
+        </is>
+      </c>
+      <c r="C787" s="4" t="inlineStr">
+        <is>
+          <t>United Arab Bank</t>
+        </is>
+      </c>
+      <c r="D787" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E787" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F787" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G787" s="4" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="4" t="n">
+        <v>375461881079</v>
+      </c>
+      <c r="B788" s="4" t="inlineStr">
+        <is>
+          <t>Source: SFF25; Company: Mashreq</t>
+        </is>
+      </c>
+      <c r="C788" s="4" t="inlineStr">
+        <is>
+          <t>Mashreq</t>
+        </is>
+      </c>
+      <c r="D788" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E788" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F788" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G788" s="4" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="4" t="n">
+        <v>360458783986</v>
+      </c>
+      <c r="B789" s="4" t="inlineStr">
+        <is>
+          <t>ATM Nearby: Axis Bank - New Deal (Tapix)</t>
+        </is>
+      </c>
+      <c r="C789" s="4" t="inlineStr">
+        <is>
+          <t>Axis Bank</t>
+        </is>
+      </c>
+      <c r="D789" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E789" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F789" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G789" s="4" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="4" t="n">
+        <v>396380044523</v>
+      </c>
+      <c r="B790" s="4" t="inlineStr">
+        <is>
+          <t>Mashreq Pakistan, Seamless Rijad 25</t>
+        </is>
+      </c>
+      <c r="C790" s="4" t="inlineStr">
+        <is>
+          <t>Mashreq</t>
+        </is>
+      </c>
+      <c r="D790" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E790" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F790" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G790" s="4" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="4" t="n">
+        <v>460476222664</v>
+      </c>
+      <c r="B791" s="4" t="inlineStr">
+        <is>
+          <t>Al Barid Bank - from HPS</t>
+        </is>
+      </c>
+      <c r="C791" s="4" t="inlineStr">
+        <is>
+          <t>Al Barid Bank</t>
+        </is>
+      </c>
+      <c r="D791" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E791" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F791" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G791" s="4" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="4" t="n">
+        <v>501313743042</v>
+      </c>
+      <c r="B792" s="4" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank DXB - discovery</t>
+        </is>
+      </c>
+      <c r="C792" s="4" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="D792" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E792" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F792" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G792" s="4" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="4" t="n">
+        <v>501500277973</v>
+      </c>
+      <c r="B793" s="4" t="inlineStr">
+        <is>
+          <t>HSBC - Dubai OH</t>
+        </is>
+      </c>
+      <c r="C793" s="4" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D793" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E793" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F793" s="6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G793" s="4" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="4" t="n">
+        <v>501500997841</v>
+      </c>
+      <c r="B794" s="4" t="inlineStr">
+        <is>
+          <t>Abacus Pakistan - OH LinkedIn</t>
+        </is>
+      </c>
+      <c r="C794" s="4" t="inlineStr">
+        <is>
+          <t>Abacus Cambridge Partners</t>
+        </is>
+      </c>
+      <c r="D794" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E794" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F794" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G794" s="4" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="4" t="n">
+        <v>496001859797</v>
+      </c>
+      <c r="B795" s="4" t="inlineStr">
+        <is>
+          <t>Moved to Tapix: Inbound - Manager.one - New Deal</t>
+        </is>
+      </c>
+      <c r="C795" s="4" t="inlineStr">
+        <is>
+          <t>Manager.one</t>
+        </is>
+      </c>
+      <c r="D795" s="4" t="inlineStr">
+        <is>
+          <t>Olda</t>
+        </is>
+      </c>
+      <c r="E795" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F795" s="6" t="n">
         <v>34175</v>
       </c>
-      <c r="G784" s="4" t="inlineStr"/>
+      <c r="G795" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -32444,7 +32741,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>
@@ -34014,7 +34311,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>
@@ -35517,7 +35814,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>
@@ -37087,7 +37384,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>
@@ -38657,7 +38954,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>
@@ -40227,7 +40524,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>
@@ -41367,7 +41664,7 @@
         <v>164500</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>181500</v>
+        <v>228700</v>
       </c>
     </row>
     <row r="23">
@@ -41797,7 +42094,7 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>06.07.</t>
+          <t>12.07.</t>
         </is>
       </c>
     </row>

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -7530,11 +7530,15 @@
       <c r="A5" s="4" t="n">
         <v>15922606068</v>
       </c>
-      <c r="B5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>J&amp;T Bank CR&amp;SK (Tapix)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>J&amp;T Bank CR</t>
+        </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -7551,36 +7555,44 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>252845309170</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v/>
+        <v>15855277004</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>AIB: Paul Dockery - RFx (Tapix)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>AIB</t>
+        </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
         <v>46083</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>15000</v>
+        <v>370000</v>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>15855277004</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v/>
+        <v>11878287315</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Erste - George use case (Tapix)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Erste Bank Austria</t>
+        </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -7591,42 +7603,50 @@
         <v>46083</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>370000</v>
+        <v>387000</v>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>402515561715</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v/>
+        <v>252845309170</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>M20-25: Swissborg (Tapix) - deal WON</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>swissborg</t>
+        </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
         <v>46083</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>11878287315</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v/>
+        <v>402515561715</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SFF25: Savo digital wallet (Singapore) (Tapix)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Savo Inc</t>
+        </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -7637,7 +7657,7 @@
         <v>46083</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>387000</v>
+        <v>40000</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
@@ -7645,11 +7665,15 @@
       <c r="A10" s="4" t="n">
         <v>141989263567</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ING Belgium, woodpecker (Tapix)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>ING Belgium</t>
+        </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -7668,11 +7692,15 @@
       <c r="A11" s="4" t="n">
         <v>496465392889</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Jupiter: Punit Makwana - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Jupiter AG</t>
+        </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -9416,7 +9444,7 @@
         <v>28970</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>0</v>
+        <v>35270</v>
       </c>
     </row>
     <row r="6">
@@ -9483,7 +9511,7 @@
         <v>103518</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>0</v>
+        <v>34020</v>
       </c>
     </row>
     <row r="7">
@@ -9550,7 +9578,7 @@
         <v>4000</v>
       </c>
       <c r="U7" s="11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -9751,7 +9779,7 @@
         <v>476040</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>0</v>
+        <v>667932</v>
       </c>
     </row>
     <row r="11">
@@ -9818,7 +9846,7 @@
         <v>399035</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>0</v>
+        <v>629635</v>
       </c>
     </row>
     <row r="12">
@@ -9885,7 +9913,7 @@
         <v>1750500</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>0</v>
+        <v>1771538</v>
       </c>
     </row>
     <row r="13">
@@ -9952,7 +9980,7 @@
         <v>509720</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>0</v>
+        <v>790340</v>
       </c>
     </row>
     <row r="14">
@@ -10019,7 +10047,7 @@
         <v>38000</v>
       </c>
       <c r="U14" s="12" t="n">
-        <v>0</v>
+        <v>89015</v>
       </c>
     </row>
     <row r="15">
@@ -10086,7 +10114,7 @@
         <v>118750</v>
       </c>
       <c r="U15" s="11" t="n">
-        <v>0</v>
+        <v>118750</v>
       </c>
     </row>
     <row r="16">
@@ -10248,7 +10276,7 @@
         <v>40000</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>412005</v>
+        <v>369505</v>
       </c>
       <c r="I19" s="14" t="n">
         <v>740003</v>
@@ -10275,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="14" t="n">
-        <v>429003</v>
+        <v>391003</v>
       </c>
       <c r="R19" s="14" t="n">
         <v>0</v>
@@ -10287,7 +10315,7 @@
         <v>12000</v>
       </c>
       <c r="U19" s="14" t="n">
-        <v>600000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="20">
@@ -10354,7 +10382,7 @@
         <v>3610753</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>0</v>
+        <v>4137500</v>
       </c>
     </row>
     <row r="21">
@@ -10421,7 +10449,7 @@
         <v>192400</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>-3610753</v>
+        <v>526747</v>
       </c>
     </row>
     <row r="22">
@@ -10488,7 +10516,7 @@
         <v>3610753</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>4077780</v>
+        <v>4137500</v>
       </c>
     </row>
     <row r="23">
@@ -10516,46 +10544,46 @@
         <v>0.498159509202454</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>0.3976483896954219</v>
+        <v>0.4061005098761943</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>0.2918755086254245</v>
+        <v>0.2964035877975169</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0.2918755086254245</v>
+        <v>0.2964035877975169</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>0.2918755086254245</v>
+        <v>0.2964035877975169</v>
       </c>
       <c r="L23" s="15" t="n">
-        <v>0.2867223538916557</v>
+        <v>0.2910907586570822</v>
       </c>
       <c r="M23" s="15" t="n">
-        <v>0.1812021513069205</v>
+        <v>0.182937145995783</v>
       </c>
       <c r="N23" s="15" t="n">
-        <v>0.1580940554493483</v>
+        <v>0.1594131397654703</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.1368435616873755</v>
+        <v>0.1378307577483547</v>
       </c>
       <c r="P23" s="15" t="n">
-        <v>0.1368435616873755</v>
+        <v>0.1378307577483547</v>
       </c>
       <c r="Q23" s="15" t="n">
-        <v>0.1970262062213411</v>
+        <v>0.199347626841148</v>
       </c>
       <c r="R23" s="15" t="n">
-        <v>0.1970262062213411</v>
+        <v>0.199347626841148</v>
       </c>
       <c r="S23" s="15" t="n">
-        <v>0.1930727427783423</v>
+        <v>0.1953014094395108</v>
       </c>
       <c r="T23" s="15" t="n">
-        <v>0.1927448680617508</v>
+        <v>0.1949659282010056</v>
       </c>
       <c r="U23" s="15" t="n">
-        <v>0.1776598364590334</v>
+        <v>0.1839090144583272</v>
       </c>
     </row>
     <row r="24">
@@ -10583,46 +10611,46 @@
         <v>45277.77777777778</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>32412.77777777778</v>
+        <v>32778.77049180328</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>31258.51685393259</v>
+        <v>31488.59770114943</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>29595.82978723404</v>
+        <v>29777.26086956522</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>28101.09090909091</v>
+        <v>28242.35051546392</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>26971.50476190476</v>
+        <v>27082.60194174757</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>35564.94444444445</v>
+        <v>35795.83064516129</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>38617.91729323308</v>
+        <v>38883.07633587786</v>
       </c>
       <c r="O24" s="14" t="n">
-        <v>40365.87074829932</v>
+        <v>40629.53793103448</v>
       </c>
       <c r="P24" s="14" t="n">
-        <v>40365.87074829932</v>
+        <v>40629.53793103448</v>
       </c>
       <c r="Q24" s="14" t="n">
-        <v>41895.67272727273</v>
+        <v>42174.60493827161</v>
       </c>
       <c r="R24" s="14" t="n">
-        <v>40663.44705882353</v>
+        <v>40911.89221556886</v>
       </c>
       <c r="S24" s="14" t="n">
-        <v>41013.58139534884</v>
+        <v>41265.30177514793</v>
       </c>
       <c r="T24" s="14" t="n">
-        <v>38196.41081081081</v>
+        <v>38383.71428571428</v>
       </c>
       <c r="U24" s="14" t="n">
-        <v>40562.62433862434</v>
+        <v>40031.54594594595</v>
       </c>
     </row>
     <row r="25">
@@ -10874,7 +10902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10993,17 +11021,15 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>14758904767</v>
+        <v>251389531345</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>TBI Bank</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>TBI Bank</t>
-        </is>
+          <t>Ukrgasbank, woodpecker</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v/>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -11014,22 +11040,22 @@
         <v>46027</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>14756394191</v>
+        <v>245983710407</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>M24: maib - new bank in Romania - exp. launch in 25/26</t>
+          <t>Erste Bank Hungary - RPI</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>maib</t>
+          <t>Erste Bank Hungary</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -11041,22 +11067,22 @@
         <v>46027</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>141206749410</v>
+        <v>172443992264</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Vietnam International Bank (VIB) - Ngân Hàng Quốc Tế - New Deal</t>
+          <t>Addiko Bank a.d. Beograd - New Deal</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Vietnam International Bank (VIB) - Ngân Hàng Quốc Tế</t>
+          <t>Addiko Bank a.d. Beograd</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -11068,22 +11094,22 @@
         <v>46027</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>167910650045</v>
+        <v>248392796383</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Raiffeisenbank Hrvatska</t>
+          <t>Source: Unchain2025; Company: Banca Transilvania</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Raiffeisenbank Hrvatska (HR)</t>
+          <t>Banca Transilvania</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -11101,16 +11127,16 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>172443988194</v>
+        <v>14758904767</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>OTP banka Srbija - New Deal</t>
+          <t>TBI Bank</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>OTP Serbia (RS)</t>
+          <t>TBI Bank</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -11122,22 +11148,22 @@
         <v>46027</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>172443992264</v>
+        <v>172443988194</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Addiko Bank a.d. Beograd - New Deal</t>
+          <t>OTP banka Srbija - New Deal</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Addiko Bank a.d. Beograd</t>
+          <t>OTP Serbia (RS)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -11149,22 +11175,22 @@
         <v>46027</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>217669364924</v>
+        <v>14756394191</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Burgan Bank - HPS</t>
+          <t>M24: maib - new bank in Romania - exp. launch in 25/26</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Burgan Bank</t>
+          <t>maib</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -11176,22 +11202,22 @@
         <v>46027</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>245983710407</v>
+        <v>167910650045</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Erste Bank Hungary - RPI</t>
+          <t>Source: Linkedin; Company: Raiffeisenbank Hrvatska</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Erste Bank Hungary</t>
+          <t>Raiffeisenbank Hrvatska (HR)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -11203,22 +11229,22 @@
         <v>46027</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>246885009623</v>
+        <v>359427408097</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Source: Unchain2025; Company: Payall Payment Systems, Inc.</t>
+          <t>Aion Bank, woodpecker</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Payall Payment Systems</t>
+          <t>Aion Bank</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -11236,16 +11262,16 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>248392796383</v>
+        <v>333754784983</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Source: Unchain2025; Company: Banca Transilvania</t>
+          <t>Addiko Bank AG, woodpecker</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Banca Transilvania</t>
+          <t>Addiko Bank AG</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -11263,15 +11289,17 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>251389531345</v>
+        <v>141206749410</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ukrgasbank, woodpecker</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v/>
+          <t>Vietnam International Bank (VIB) - Ngân Hàng Quốc Tế - New Deal</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Vietnam International Bank (VIB) - Ngân Hàng Quốc Tế</t>
+        </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -11282,22 +11310,22 @@
         <v>46027</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>359427408097</v>
+        <v>217669364924</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Aion Bank, woodpecker</t>
+          <t>Burgan Bank - HPS</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Aion Bank</t>
+          <t>Burgan Bank</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -11309,22 +11337,22 @@
         <v>46027</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>333754784983</v>
+        <v>246885009623</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Addiko Bank AG, woodpecker</t>
+          <t>Source: Unchain2025; Company: Payall Payment Systems, Inc.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Addiko Bank AG</t>
+          <t>Payall Payment Systems</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -11396,55 +11424,55 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>309212736760</v>
+        <v>420883062971</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ABS: Atom Bank</t>
+          <t>Soulbac - inbound na Support@tapix.io</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Atom bank</t>
+          <t>Soulbac</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
         <v>46030</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>420883062971</v>
+        <v>309212736760</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Soulbac - inbound na Support@tapix.io</t>
+          <t>ABS: Atom Bank</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Soulbac</t>
+          <t>Atom bank</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
         <v>46030</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
     </row>
@@ -11506,11 +11534,15 @@
       <c r="A26" s="4" t="n">
         <v>426352077012</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>M20-25: PayPo (Tapix)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>PayPo</t>
+        </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
@@ -11527,16 +11559,16 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>14723060424</v>
+        <v>145158419661</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Source: M24; MAIB</t>
+          <t>Source: Linkedin; Company: OTP banka, Slovenija</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>maib</t>
+          <t>OTP banka, Slovenija (SI)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -11548,7 +11580,7 @@
         <v>46035</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
     </row>
@@ -11581,16 +11613,16 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>23044845781</v>
+        <v>14723060424</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Montenegro: CKB bank</t>
+          <t>Source: M24; MAIB</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>CKB bank</t>
+          <t>maib</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -11602,22 +11634,22 @@
         <v>46035</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>145158419661</v>
+        <v>23044845781</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: OTP banka, Slovenija</t>
+          <t>Montenegro: CKB bank</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>OTP banka, Slovenija (SI)</t>
+          <t>CKB bank</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -11718,11 +11750,15 @@
       <c r="A34" s="4" t="n">
         <v>395029775587</v>
       </c>
-      <c r="B34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v/>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Tiime: Brice Gueguen - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Tiime</t>
+        </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
@@ -11820,16 +11856,16 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>431449473269</v>
+        <v>426073329907</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>infaqy.com: waleed dakheel - contact form</t>
+          <t>: Szabolcs Herman - contact form</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>infaqy.com</t>
+          <t>stashbeat.com</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -11847,16 +11883,16 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>426073329907</v>
+        <v>431449473269</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>: Szabolcs Herman - contact form</t>
+          <t>infaqy.com: waleed dakheel - contact form</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>stashbeat.com</t>
+          <t>infaqy.com</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -11876,11 +11912,15 @@
       <c r="A40" s="4" t="n">
         <v>158226602174</v>
       </c>
-      <c r="B40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v/>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Attijariwafa bank - Innovation team via Finshape</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Attijariwafa bank</t>
+        </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
@@ -11899,11 +11939,15 @@
       <c r="A41" s="4" t="n">
         <v>311509526760</v>
       </c>
-      <c r="B41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>NLB Bank GROUP (Tapix)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>NLB Group</t>
+        </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
@@ -11920,21 +11964,21 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>374664054001</v>
+        <v>450475213032</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Bank Pekao S.A.</t>
+          <t>TrustDecision: Mandy Yang - contact form</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Bank Pekao (Pikao)</t>
+          <t>TrustDecision</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -11974,21 +12018,21 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>450475213032</v>
+        <v>374664054001</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>TrustDecision: Mandy Yang - contact form</t>
+          <t>Source: Linkedin; Company: Bank Pekao S.A.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>TrustDecision</t>
+          <t>Bank Pekao (Pikao)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
@@ -12003,11 +12047,15 @@
       <c r="A45" s="4" t="n">
         <v>9140022476</v>
       </c>
-      <c r="B45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Tietoevry - Replacement of Nordigen - first bank</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Tietoevry</t>
+        </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
@@ -12026,11 +12074,15 @@
       <c r="A46" s="4" t="n">
         <v>372346793179</v>
       </c>
-      <c r="B46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v/>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Jeeves: Douglas Germano - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Jeeves</t>
+        </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
@@ -12072,16 +12124,16 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>385673532663</v>
+        <v>416185461970</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>: Yonnys Prieto - contact form</t>
+          <t>CashFish: Tarek Hariss - contact form</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Aixfin</t>
+          <t>CashFish</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -12126,16 +12178,16 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>416185461970</v>
+        <v>385673532663</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CashFish: Tarek Hariss - contact form</t>
+          <t>: Yonnys Prieto - contact form</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>CashFish</t>
+          <t>Aixfin</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -12153,16 +12205,16 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>188033456352</v>
+        <v>247661320378</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ABS: Capital on Tap</t>
+          <t>ABS: Engine by Starling</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Capital on Tap</t>
+          <t>Engine by Starling</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -12180,21 +12232,21 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>247661320378</v>
+        <v>432556676330</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>ABS: Engine by Starling</t>
+          <t>LES TROIS GRENOUILLES: bruno beltempo - contact form</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Engine by Starling</t>
+          <t>LES TROIS GRENOUILLES</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -12207,21 +12259,21 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>450816846068</v>
+        <v>188033456352</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>leiselyhowards.com: Daniel Nkole - contact form</t>
+          <t>ABS: Capital on Tap</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Leisely Howards</t>
+          <t>Capital on Tap</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
@@ -12234,16 +12286,16 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>432556676330</v>
+        <v>450816846068</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>LES TROIS GRENOUILLES: bruno beltempo - contact form</t>
+          <t>leiselyhowards.com: Daniel Nkole - contact form</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>LES TROIS GRENOUILLES</t>
+          <t>Leisely Howards</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -12263,11 +12315,15 @@
       <c r="A55" s="4" t="n">
         <v>328976574664</v>
       </c>
-      <c r="B55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>ICICI Bank UK Plc, transfers logo enrichment (Tapix)</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>ICICI Bank UK Plc</t>
+        </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
@@ -12284,16 +12340,16 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>305946307801</v>
+        <v>445839426798</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>us.quinteft.com: Swami Bhaskaran - contact form</t>
+          <t>MOBILE WALLET INTERNATIONAL "MWI": Gerald Chenyi - contact form</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>us.quinteft.com</t>
+          <t>MOBILE WALLET INTERNATIONAL "MWI"</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -12311,16 +12367,16 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>161176459492</v>
+        <v>403286462680</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Bybit</t>
+          <t>Dating Central Europe Zrt.: Daniel Farkas - contact form</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Dating Central Europe</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -12338,16 +12394,16 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>327181890750</v>
+        <v>305946307801</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>: Amy Allen - contact form</t>
+          <t>us.quinteft.com: Swami Bhaskaran - contact form</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Institute of Commercial Payments</t>
+          <t>us.quinteft.com</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -12365,16 +12421,16 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>335122949315</v>
+        <v>451908503776</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Steyler Ethik Bank, woodpecker</t>
+          <t>PaymentRush: Payrush Payrush - contact form</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Steyler Ethik Bank</t>
+          <t>PaymentRush</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -12419,16 +12475,16 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>445839426798</v>
+        <v>161176459492</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>MOBILE WALLET INTERNATIONAL "MWI": Gerald Chenyi - contact form</t>
+          <t>Source: Linkedin; Company: Bybit</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>MOBILE WALLET INTERNATIONAL "MWI"</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -12446,16 +12502,16 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>451908503776</v>
+        <v>327181890750</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>PaymentRush: Payrush Payrush - contact form</t>
+          <t>: Amy Allen - contact form</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>PaymentRush</t>
+          <t>Institute of Commercial Payments</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -12473,16 +12529,16 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>377605452987</v>
+        <v>335122949315</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Hoblk: عبد الجواد عبد الحليم - contact form</t>
+          <t>Steyler Ethik Bank, woodpecker</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Hoblk</t>
+          <t>Steyler Ethik Bank</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -12500,16 +12556,16 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>385794196689</v>
+        <v>377605452987</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>aixfin.com: Yonnys Prieto - contact form</t>
+          <t>Hoblk: عبد الجواد عبد الحليم - contact form</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Aixfin</t>
+          <t>Hoblk</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -12527,16 +12583,16 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
-        <v>403286462680</v>
+        <v>385794196689</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Dating Central Europe Zrt.: Daniel Farkas - contact form</t>
+          <t>aixfin.com: Yonnys Prieto - contact form</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Dating Central Europe</t>
+          <t>Aixfin</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -12556,11 +12612,15 @@
       <c r="A66" s="4" t="n">
         <v>285690649809</v>
       </c>
-      <c r="B66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v/>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Younited: Romain Mazoué - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Younited</t>
+        </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
@@ -12579,11 +12639,15 @@
       <c r="A67" s="4" t="n">
         <v>399499961589</v>
       </c>
-      <c r="B67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v/>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Ditta: alessio rede - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Ditta</t>
+        </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
@@ -12600,16 +12664,16 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>373912705221</v>
+        <v>334129298647</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ABS: Unioo</t>
+          <t>Workyard: Parisa Gonzalez - contact form</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Unioo</t>
+          <t>Workyard</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -12627,16 +12691,16 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>374662080746</v>
+        <v>373912705221</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive Nordics: CRIF</t>
+          <t>ABS: Unioo</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Crif</t>
+          <t>Unioo</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -12654,16 +12718,16 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
-        <v>379637519563</v>
+        <v>374662080746</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>ABS: Instabank ASA</t>
+          <t>MoneyLive Nordics: CRIF</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Instabank ASA</t>
+          <t>Crif</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -12681,16 +12745,16 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>334129298647</v>
+        <v>379637519563</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Workyard: Parisa Gonzalez - contact form</t>
+          <t>ABS: Instabank ASA</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Workyard</t>
+          <t>Instabank ASA</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -12710,11 +12774,15 @@
       <c r="A72" s="4" t="n">
         <v>311451676902</v>
       </c>
-      <c r="B72" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v/>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>INF24: Erste banka Crna Gora (Tapix)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Erste banka Montenegro</t>
+        </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
@@ -12868,11 +12936,15 @@
       <c r="A78" s="4" t="n">
         <v>177480020215</v>
       </c>
-      <c r="B78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v/>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>UNI25CZ: Lovćen banka AD Podgorica (Tapix)</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Lovćen banka AD Podgorica</t>
+        </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
@@ -12891,11 +12963,15 @@
       <c r="A79" s="4" t="n">
         <v>15752294872</v>
       </c>
-      <c r="B79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v/>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Round Robin: Spendly - Igor Orlov (Tapix)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Spendly</t>
+        </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
@@ -12941,11 +13017,15 @@
       <c r="A81" s="4" t="n">
         <v>245320353004</v>
       </c>
-      <c r="B81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v/>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>getapron.com: Grace Cameron-Douglas - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Apron</t>
+        </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
@@ -13043,124 +13123,136 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>23170666984</v>
-      </c>
-      <c r="B85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v/>
+        <v>392115995838</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Supervielle: Cristian Challier - contact form</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Supervielle</t>
+        </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
         <v>46098</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>60689819863</v>
-      </c>
-      <c r="B86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v/>
+        <v>23170666984</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Security Bank Corporation - New Deal (Tapix)</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Security Bank</t>
+        </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
         <v>46098</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>75000</v>
+        <v>80000</v>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>97474557146</v>
-      </c>
-      <c r="B87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v/>
+        <v>374522089695</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>MoneyLive Nordics: Bigbank</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Bigbank</t>
+        </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
         <v>46098</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>67500</v>
+        <v>0</v>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>374522089695</v>
+        <v>97474557146</v>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive Nordics: Bigbank</t>
+          <t>Sparmakarna: Johan Löf - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Bigbank</t>
+          <t>Sparmakarna</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
         <v>46098</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0</v>
+        <v>67500</v>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>392115995838</v>
+        <v>60689819863</v>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Supervielle: Cristian Challier - contact form</t>
+          <t>Source: Linkedin; Company: Cairo Amman Bank (Tapix)</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Supervielle</t>
+          <t>Cairo Amman Bank</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
         <v>46098</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
     </row>
@@ -13274,13 +13366,17 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
-        <v>103440566459</v>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C94" s="4" t="n">
-        <v/>
+        <v>458536692968</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Custodia: Ade Adenuga - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Custodia</t>
+        </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
@@ -13291,57 +13387,61 @@
         <v>46105</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
-        <v>458536692968</v>
-      </c>
-      <c r="B95" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v/>
+        <v>279823297723</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Source: Linkedin; Company: QNB Group</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Qatar National Bank</t>
+        </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
         <v>46105</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
-        <v>279823297723</v>
+        <v>103440566459</v>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: QNB Group</t>
+          <t>Lipefi: Georgy Taranov - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Qatar National Bank</t>
+          <t>Lipefi</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
         <v>46105</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
     </row>
@@ -13376,11 +13476,15 @@
       <c r="A98" s="4" t="n">
         <v>292771657954</v>
       </c>
-      <c r="B98" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C98" s="4" t="n">
-        <v/>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Allica Bank - New Deal (Tapix)</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Allica Bank</t>
+        </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
@@ -13399,11 +13503,15 @@
       <c r="A99" s="4" t="n">
         <v>496480275643</v>
       </c>
-      <c r="B99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C99" s="4" t="n">
-        <v/>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Gimi (Tapix)</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Gimi – Financial Superskills for Life</t>
+        </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
@@ -13420,62 +13528,70 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
-        <v>496480275643</v>
-      </c>
-      <c r="B100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C100" s="4" t="n">
-        <v/>
+        <v>378001606869</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>MiTrust: Richard Dey - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>MiTrust</t>
+        </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
         <v>46119</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
-        <v>378001606869</v>
-      </c>
-      <c r="B101" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C101" s="4" t="n">
-        <v/>
+        <v>226816087270</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>BNP Paribas Fortis BE, woodpecker</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>BNP Paribas Fortis BE</t>
+        </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
-        <v>497917441210</v>
+        <v>497917440237</v>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Arbitas - New Deal</t>
+          <t>Intellias - New Deal</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Arbitas</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -13493,16 +13609,16 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
-        <v>497917440237</v>
+        <v>497917441210</v>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Intellias - New Deal</t>
+          <t>Arbitas - New Deal</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Arbitas</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -13547,25 +13663,25 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
-        <v>226816087270</v>
+        <v>478331535568</v>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>BNP Paribas Fortis BE, woodpecker</t>
+          <t>Tot Money S.p.a.: Lorenzo Vivaldini - contact form</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>BNP Paribas Fortis BE</t>
+          <t>Tot Money S.p.a.</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>0</v>
@@ -13574,143 +13690,151 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
-        <v>478331535568</v>
+        <v>498502569192</v>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Tot Money S.p.a.: Lorenzo Vivaldini - contact form</t>
+          <t>Arkam Partnership</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Tot Money S.p.a.</t>
+          <t>Arkamtec</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
-        <v>498498917617</v>
-      </c>
-      <c r="B107" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C107" s="4" t="n">
-        <v/>
+        <v>276545506529</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>ING: Maarten Driessen - contact form</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
-        <v>309710516429</v>
-      </c>
-      <c r="B108" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v/>
+        <v>131338994917</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>BCR - client labeling</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>BCR</t>
+        </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>67500</v>
+        <v>0</v>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
-        <v>498502569192</v>
+        <v>469739059449</v>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Arkam Partnership</t>
+          <t>Zapad banka AD Podgorica, woodpecker</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Arkamtec</t>
+          <t>Zapad banka AD Podgorica</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
-        <v>276545506529</v>
+        <v>167867497663</v>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>ING: Maarten Driessen - contact form</t>
+          <t>UniCredit Bank Serbia</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>UniCredit Bank Serbia</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
-        <v>131338994917</v>
+        <v>311084966087</v>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>BCR - client labeling</t>
+          <t>Mastercard Slovenia</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>BCR</t>
+          <t>Mastercard Europe</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -13728,16 +13852,16 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
-        <v>141989380324</v>
+        <v>172850432214</v>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Thales - New Deal</t>
+          <t>Source: Linkedin; Company: Garanti BBVA</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Garanti BBVA ROMANIA (RBI now)</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -13749,22 +13873,22 @@
         <v>46122</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
-        <v>172850432214</v>
+        <v>141989380324</v>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Garanti BBVA</t>
+          <t>Thales - New Deal</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Garanti BBVA ROMANIA (RBI now)</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -13776,22 +13900,22 @@
         <v>46122</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
-        <v>167867497663</v>
+        <v>309831687359</v>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>UniCredit Bank Serbia</t>
+          <t xml:space="preserve">ABS: ING Poland </t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>UniCredit Bank Serbia</t>
+          <t>ING Poland</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -13803,22 +13927,22 @@
         <v>46122</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
-        <v>311084966087</v>
+        <v>445970439384</v>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Mastercard Slovenia</t>
+          <t>Conference: Verestro (Partnership)</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Mastercard Europe</t>
+          <t>Verestro</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -13863,43 +13987,43 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
-        <v>365136108758</v>
+        <v>309710516429</v>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>WFW25 - Nest2M - Turkey partnership</t>
+          <t>Holvi - od Martina (Tapix)</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Nest2Move</t>
+          <t>Holvi</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1</v>
+        <v>67500</v>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
-        <v>445970439384</v>
+        <v>365136108758</v>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Conference: Verestro (Partnership)</t>
+          <t>WFW25 - Nest2M - Turkey partnership</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Verestro</t>
+          <t>Nest2Move</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -13911,23 +14035,21 @@
         <v>46122</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
-        <v>309831687359</v>
+        <v>467637772510</v>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABS: ING Poland </t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>ING Poland</t>
-        </is>
+          <t>, woodpecker</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v/>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
@@ -13944,21 +14066,21 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
-        <v>469739059449</v>
+        <v>400708664525</v>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Zapad banka AD Podgorica, woodpecker</t>
+          <t>instashopify.com: Imran Khan - contact form</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Zapad banka AD Podgorica</t>
+          <t>instashopify</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -13971,21 +14093,19 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
-        <v>400708664525</v>
+        <v>467713169640</v>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>instashopify.com: Imran Khan - contact form</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>instashopify</t>
-        </is>
+          <t>, woodpecker</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v/>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -13998,19 +14118,21 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
-        <v>467637772510</v>
+        <v>286785856703</v>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>, woodpecker</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v/>
+          <t>NORD/LB - Norddeutsche Landesbank Girozentrale, woodpecker</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>NORD/LB - Norddeutsche Landesbank Girozentrale</t>
+        </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -14023,15 +14145,17 @@
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
-        <v>467713169640</v>
+        <v>276512884926</v>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>, woodpecker</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="n">
-        <v/>
+          <t>NORD/LB, woodpecker</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>NORD/LB</t>
+        </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
@@ -14048,16 +14172,16 @@
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
-        <v>286785856703</v>
+        <v>347664847040</v>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB - Norddeutsche Landesbank Girozentrale, woodpecker</t>
+          <t>S-pankki - Visa mandat (Tapix)</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB - Norddeutsche Landesbank Girozentrale</t>
+          <t>S-pankki</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -14066,34 +14190,34 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0</v>
+        <v>290000</v>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
-        <v>276512884926</v>
+        <v>498499524811</v>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB, woodpecker</t>
+          <t>Guillermo - Sandbox inbound</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB</t>
+          <t>ThinkUp</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>0</v>
@@ -14102,39 +14226,43 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
-        <v>347664847040</v>
-      </c>
-      <c r="B126" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v/>
+        <v>498502332660</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Micapay - New Deal</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Micapay</t>
+        </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>290000</v>
+        <v>0</v>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
-        <v>498499524811</v>
+        <v>498503765209</v>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Guillermo - Sandbox inbound</t>
+          <t>LINK.IO - linkedin inbound</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>ThinkUp</t>
+          <t>LINK.IO</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -14152,25 +14280,25 @@
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
-        <v>498502332660</v>
+        <v>311146490105</v>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Micapay - New Deal</t>
+          <t>MoneyKSA: STC</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Micapay</t>
+          <t>STC Bank</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>0</v>
@@ -14179,25 +14307,25 @@
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
-        <v>498503765209</v>
+        <v>15773372113</v>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>LINK.IO - linkedin inbound</t>
+          <t>United Arab Bank, woodpecker</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>LINK.IO</t>
+          <t>United Arab Bank</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>0</v>
@@ -14206,16 +14334,16 @@
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
-        <v>327954289912</v>
+        <v>497918877934</v>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>BFA - Sibos</t>
+          <t>easypaisa digital bank - New Deal</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>easypaisa digital bank</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -14227,22 +14355,22 @@
         <v>46127</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
-        <v>270710947026</v>
+        <v>275565561070</v>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: State Bank of India</t>
+          <t>Source: Linkedin; Company: Al-Mansour Bank For Investment - مصرف المنصور للأستثمار</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Al-Mansour Bank For Investment - مصرف المنصور للأستثمار</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -14287,16 +14415,16 @@
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
-        <v>275565561070</v>
+        <v>282683199716</v>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Al-Mansour Bank For Investment - مصرف المنصور للأستثمار</t>
+          <t>Source: Linkedin; Company: alrajhi bank</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Al-Mansour Bank For Investment - مصرف المنصور للأستثمار</t>
+          <t>alrajhi bank</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -14314,16 +14442,16 @@
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
-        <v>282683199716</v>
+        <v>327954289912</v>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: alrajhi bank</t>
+          <t>BFA - Sibos</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>alrajhi bank</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -14335,22 +14463,22 @@
         <v>46127</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
-        <v>282473940183</v>
+        <v>270710947026</v>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: D360 Bank</t>
+          <t>Source: Linkedin; Company: State Bank of India</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>D360 Bank</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -14368,16 +14496,16 @@
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
-        <v>497918877934</v>
+        <v>282473940183</v>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>easypaisa digital bank - New Deal</t>
+          <t>Source: Linkedin; Company: D360 Bank</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>easypaisa digital bank</t>
+          <t>D360 Bank</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -14395,16 +14523,16 @@
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
-        <v>311146490105</v>
+        <v>311549637860</v>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: STC</t>
+          <t>MoneyKSA: barq</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>STC Bank</t>
+          <t>barq</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -14422,16 +14550,16 @@
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
-        <v>311549637860</v>
+        <v>327598518493</v>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: barq</t>
+          <t>SAB - Sibos</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>barq</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -14443,31 +14571,31 @@
         <v>46127</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
-        <v>15773372113</v>
+        <v>496001262830</v>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>United Arab Bank, woodpecker</t>
+          <t>Pay360: ANNA</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>United Arab Bank</t>
+          <t>ANNA</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>0</v>
@@ -14476,16 +14604,16 @@
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
-        <v>327598518493</v>
+        <v>311549637872</v>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>SAB - Sibos</t>
+          <t>MoneyKSA: ANB</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Arab National Bank</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -14494,61 +14622,61 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
-        <v>496001262830</v>
+        <v>396491691199</v>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Pay360: ANNA</t>
+          <t>Crédit Agricole Egypt SME</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>ANNA</t>
+          <t>Crédit Agricole Egypt</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
         <v>46128</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
-        <v>311549637872</v>
+        <v>156852645094</v>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: ANB</t>
+          <t>MoneyLive 25: Deutsche Bank</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Arab National Bank</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>0</v>
@@ -14557,66 +14685,70 @@
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
-        <v>396491691199</v>
+        <v>403807522024</v>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Crédit Agricole Egypt SME</t>
+          <t>Bank Millennium - PFM/X-selling (Tapix)</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Crédit Agricole Egypt</t>
+          <t>Bank Millennium</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>100000</v>
+        <v>350000</v>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
-        <v>403807522024</v>
-      </c>
-      <c r="B144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C144" s="4" t="n">
-        <v/>
+        <v>103713858805</v>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>ABS: Zurcher Kantonalbank</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Zurcher Kantonalbank</t>
+        </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
         <v>46129</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
-        <v>102674107641</v>
+        <v>103818502365</v>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>ABS:Migros Bank AG</t>
+          <t>ABS: Bank Cler</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Migros Bank AG</t>
+          <t>Bank Cler</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -14634,16 +14766,16 @@
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
-        <v>103713858805</v>
+        <v>102674107641</v>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>ABS: Zurcher Kantonalbank</t>
+          <t>ABS:Migros Bank AG</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Zurcher Kantonalbank</t>
+          <t>Migros Bank AG</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -14661,16 +14793,16 @@
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
-        <v>103818502365</v>
+        <v>159725408500</v>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>ABS: Bank Cler</t>
+          <t>MoneyLive25: Mutual Trust Bank</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Bank Cler</t>
+          <t>Mutual Trust Bank</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -14688,16 +14820,16 @@
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
-        <v>156852645094</v>
+        <v>239570607293</v>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive 25: Deutsche Bank</t>
+          <t>M20-25:IBM</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -14715,16 +14847,16 @@
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
-        <v>159725408500</v>
+        <v>389192580341</v>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive25: Mutual Trust Bank</t>
+          <t>MoneyLive Payments Europe 25</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Mutual Trust Bank</t>
+          <t>Bank of Georgia</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -14736,31 +14868,31 @@
         <v>46129</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
-        <v>239570607293</v>
+        <v>278819580147</v>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>M20-25:IBM</t>
+          <t>Source: Linkedin; Company: DIB</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>DIB</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>0</v>
@@ -14769,28 +14901,28 @@
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
-        <v>389192580341</v>
+        <v>442319480017</v>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive Payments Europe 25</t>
+          <t>MoneyLive25:Nordea Finland</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Bank of Georgia</t>
+          <t>Nordea</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
     </row>
@@ -14823,16 +14955,16 @@
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
-        <v>278819580147</v>
+        <v>279934802121</v>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: DIB</t>
+          <t>Source: Linkedin; Company: D360 Bank</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>DIB</t>
+          <t>D360 Bank</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -14850,25 +14982,25 @@
     </row>
     <row r="154">
       <c r="A154" s="4" t="n">
-        <v>279934802121</v>
+        <v>499595518152</v>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: D360 Bank</t>
+          <t>: Kenny Patel - contact form</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>D360 Bank</t>
+          <t>AIS Technolabs</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>0</v>
@@ -14877,25 +15009,25 @@
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
-        <v>442319480017</v>
+        <v>475421443291</v>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive25:Nordea Finland</t>
+          <t>: Szymon Bubak - contact form</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Nordea</t>
+          <t>Jiai</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>0</v>
@@ -14904,25 +15036,25 @@
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
-        <v>499595518152</v>
+        <v>260160741596</v>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>: Kenny Patel - contact form</t>
+          <t>ABS: HSBC Innovation Banking</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>AIS Technolabs</t>
+          <t>HSBC Innovation Banking</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>0</v>
@@ -14931,16 +15063,16 @@
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
-        <v>260160741596</v>
+        <v>496001965267</v>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>ABS: HSBC Innovation Banking</t>
+          <t>Pay360: iFAST</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>HSBC Innovation Banking</t>
+          <t>iFAST Global Bank Limited</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -14958,25 +15090,25 @@
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
-        <v>496001965267</v>
+        <v>498500356290</v>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Pay360: iFAST</t>
+          <t>ZYPTO: Joe Parkin - contact form</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited</t>
+          <t>Zypto</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>0</v>
@@ -14985,25 +15117,25 @@
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
-        <v>475421443291</v>
+        <v>493904575730</v>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>: Szymon Bubak - contact form</t>
+          <t>MoneyLive 2026: ABB (Tapix)</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Jiai</t>
+          <t>The International Bank of Azerbaijan</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>0</v>
@@ -15012,16 +15144,16 @@
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
-        <v>498500356290</v>
+        <v>431703028948</v>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>ZYPTO: Joe Parkin - contact form</t>
+          <t>: Mohamed mezar abdalwahab abdelall - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Zypto</t>
+          <t>Trillioni Pay</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -15030,25 +15162,25 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="F160" s="6" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
-        <v>493904575730</v>
+        <v>494470747350</v>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive 2026: ABB (Tapix)</t>
+          <t>ABS: Moneybox</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>The International Bank of Azerbaijan</t>
+          <t>Moneybox</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -15057,7 +15189,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>0</v>
@@ -15068,11 +15200,15 @@
       <c r="A162" s="4" t="n">
         <v>459069370612</v>
       </c>
-      <c r="B162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C162" s="4" t="n">
-        <v/>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>: Mitja Simcic - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>USBC</t>
+        </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
@@ -15089,13 +15225,17 @@
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
-        <v>431703028948</v>
-      </c>
-      <c r="B163" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C163" s="4" t="n">
-        <v/>
+        <v>495303654637</v>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>THORWallet: Marcel Harmann - contact form</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>THORWallet</t>
+        </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
@@ -15103,49 +15243,53 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
-        <v>494470747350</v>
+        <v>500721741008</v>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>ABS: Moneybox</t>
+          <t>mytally.io: Igor Carreira - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Moneybox</t>
+          <t>Tally</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="F164" s="6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
-        <v>500721741008</v>
-      </c>
-      <c r="B165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C165" s="4" t="n">
-        <v/>
+        <v>499506157817</v>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>: Magdy Z - contact form</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Magdy Zakey</t>
+        </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
@@ -15156,22 +15300,22 @@
         <v>46149</v>
       </c>
       <c r="F165" s="6" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
-        <v>495303654637</v>
+        <v>494828206297</v>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>THORWallet: Marcel Harmann - contact form</t>
+          <t>Giggle Finance: Joe Salvatore - contact form</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>THORWallet</t>
+          <t>Giggle Finance</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -15180,7 +15324,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>0</v>
@@ -15189,16 +15333,16 @@
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
-        <v>499506157817</v>
+        <v>501908754631</v>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>: Magdy Z - contact form</t>
+          <t>Ai4 Co: Glenn Morizio - contact form</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Magdy Zakey</t>
+          <t>Ai4 Co</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -15207,7 +15351,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>0</v>
@@ -15216,52 +15360,52 @@
     </row>
     <row r="168">
       <c r="A168" s="4" t="n">
-        <v>501908754631</v>
+        <v>361253052612</v>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Ai4 Co: Glenn Morizio - contact form</t>
+          <t>ABS: HSBC - UK (Tapix)</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Ai4 Co</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="F168" s="6" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
-        <v>494828206297</v>
+        <v>317181618398</v>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Giggle Finance: Joe Salvatore - contact form</t>
+          <t>Source: Linkedin; Company: Emirates NBD</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Giggle Finance</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>0</v>
@@ -15270,36 +15414,44 @@
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
-        <v>361253052612</v>
-      </c>
-      <c r="B170" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C170" s="4" t="n">
-        <v/>
+        <v>284788523206</v>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>ABS: Emirates NBD - TBD</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="F170" s="6" t="n">
-        <v>520000</v>
+        <v>0</v>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
-        <v>496216189115</v>
-      </c>
-      <c r="B171" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C171" s="4" t="n">
-        <v/>
+        <v>453943420130</v>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finnovex25 - Emirates NBD </t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
@@ -15310,42 +15462,50 @@
         <v>46155</v>
       </c>
       <c r="F171" s="6" t="n">
-        <v>34175</v>
+        <v>200000</v>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
-        <v>328780895427</v>
-      </c>
-      <c r="B172" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v/>
+        <v>496650984634</v>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>Pay360: Banco do Brasil</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>Banco do Brasil</t>
+        </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
         <v>46155</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
-        <v>31881524471</v>
-      </c>
-      <c r="B173" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C173" s="4" t="n">
-        <v/>
+        <v>328780895427</v>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>FintechDubai - ADIB (Tapix)</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>ADIB</t>
+        </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
@@ -15356,22 +15516,22 @@
         <v>46155</v>
       </c>
       <c r="F173" s="6" t="n">
-        <v>125000</v>
+        <v>270000</v>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n">
-        <v>291359215826</v>
+        <v>285672625370</v>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>BRI - Digital banking</t>
+          <t>Source: Linkedin; Company: The BENEFIT Company</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>PT Bank Rakyat Indonesia (Persero) Tbk</t>
+          <t>Benefit</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -15383,22 +15543,22 @@
         <v>46155</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
-        <v>285672625370</v>
+        <v>311443594430</v>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: The BENEFIT Company</t>
+          <t>LiP2025: CitiBank</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Benefit</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -15416,16 +15576,16 @@
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
-        <v>247761688768</v>
+        <v>496216189115</v>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Fintech Dubai - Mashreq</t>
+          <t>Inbound - Manager.one - New Deal (Tapix)</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Mashreq Bank</t>
+          <t>Manager.one</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -15437,22 +15597,22 @@
         <v>46155</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>0</v>
+        <v>34175</v>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
-        <v>186343187657</v>
+        <v>31881524471</v>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Saudi National Bank (SNB) - New Deal</t>
+          <t>National Bank of Kuwait - Sami (Tapix)</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Saudi National Bank (SNB)</t>
+          <t>National Bank of Kuwait</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -15464,22 +15624,22 @@
         <v>46155</v>
       </c>
       <c r="F177" s="6" t="n">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
-        <v>179030529269</v>
+        <v>291359215826</v>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Network International: Tamara Rezqallah - contact form</t>
+          <t>BRI - Digital banking</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Network International</t>
+          <t>PT Bank Rakyat Indonesia (Persero) Tbk</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -15491,22 +15651,22 @@
         <v>46155</v>
       </c>
       <c r="F178" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
-        <v>54344594667</v>
+        <v>247761688768</v>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>TNB</t>
+          <t>Fintech Dubai - Mashreq</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>The National Bank (TNB)</t>
+          <t>Mashreq Bank</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -15518,22 +15678,22 @@
         <v>46155</v>
       </c>
       <c r="F179" s="6" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
-        <v>284788523206</v>
+        <v>186343187657</v>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>ABS: Emirates NBD - TBD</t>
+          <t>Saudi National Bank (SNB) - New Deal</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Saudi National Bank (SNB)</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -15545,22 +15705,22 @@
         <v>46155</v>
       </c>
       <c r="F180" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
-        <v>317181618398</v>
+        <v>179030529269</v>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Emirates NBD</t>
+          <t>Network International: Tamara Rezqallah - contact form</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Network International</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -15578,16 +15738,16 @@
     </row>
     <row r="182">
       <c r="A182" s="4" t="n">
-        <v>453943420130</v>
+        <v>54344594667</v>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finnovex25 - Emirates NBD </t>
+          <t>TNB</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>The National Bank (TNB)</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -15599,7 +15759,7 @@
         <v>46155</v>
       </c>
       <c r="F182" s="6" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
     </row>
@@ -15659,16 +15819,16 @@
     </row>
     <row r="185">
       <c r="A185" s="4" t="n">
-        <v>311443594430</v>
+        <v>323556661452</v>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>LiP2025: CitiBank</t>
+          <t>Source: Linkedin; Company: QNB Group</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Qatar National Bank</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -15686,52 +15846,52 @@
     </row>
     <row r="186">
       <c r="A186" s="4" t="n">
-        <v>323556661452</v>
+        <v>16641191388</v>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: QNB Group</t>
+          <t>Woodpecker: Arab African International Bank (AAIB) (Tapix) - finshape</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Qatar National Bank</t>
+          <t>Arab African International Bank</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
-        <v>496650984634</v>
+        <v>467775515879</v>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Pay360: Banco do Brasil</t>
+          <t>Arion Bank, woodpecker</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Banco do Brasil</t>
+          <t>Arion Bank</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>0</v>
@@ -15740,48 +15900,52 @@
     </row>
     <row r="188">
       <c r="A188" s="4" t="n">
-        <v>16641191388</v>
-      </c>
-      <c r="B188" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C188" s="4" t="n">
-        <v/>
+        <v>390652136650</v>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>MoneyLive Nordics - Holm Bank</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>Holm Bank</t>
+        </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
-        <v>467775515879</v>
+        <v>503301355746</v>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Arion Bank, woodpecker</t>
+          <t>Natravor: Sheryl George Sheryl George - contact form</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Arion Bank</t>
+          <t>Natravor</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>0</v>
@@ -15790,25 +15954,25 @@
     </row>
     <row r="190">
       <c r="A190" s="4" t="n">
-        <v>390652136650</v>
+        <v>502723689696</v>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive Nordics - Holm Bank</t>
+          <t>DADANADA: Gisele Ingabire - contact form</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Holm Bank</t>
+          <t>DADANADA B.V.</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>0</v>
@@ -15817,67 +15981,71 @@
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
-        <v>503301355746</v>
+        <v>274486206684</v>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Natravor: Sheryl George Sheryl George - contact form</t>
+          <t>ABS: Barclays UK (Tapix)</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Natravor</t>
+          <t>Barclays UK</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F191" s="6" t="n">
-        <v>0</v>
+        <v>617000</v>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n">
-        <v>502723689696</v>
+        <v>505743116486</v>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>DADANADA: Gisele Ingabire - contact form</t>
+          <t>Xapo Bank - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>DADANADA B.V.</t>
+          <t>Xapo Bank</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F192" s="6" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="G192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
-        <v>23389385921</v>
-      </c>
-      <c r="B193" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C193" s="4" t="n">
-        <v/>
+        <v>237657578687</v>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>M20-25: Xapo Bank - business</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Xapo Bank</t>
+        </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
@@ -15888,57 +16056,61 @@
         <v>46164</v>
       </c>
       <c r="F193" s="6" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n">
-        <v>274486206684</v>
-      </c>
-      <c r="B194" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C194" s="4" t="n">
-        <v/>
+        <v>361599102167</v>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Plebicom: Benjamin STUTZ - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>Plebicom</t>
+        </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>617000</v>
+        <v>75000</v>
       </c>
       <c r="G194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
-        <v>237657578687</v>
+        <v>493860038900</v>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>M20-25: Xapo Bank - business</t>
+          <t>Raiffeisenbank HR (Tapix)</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Xapo Bank</t>
+          <t>Raiffeisenbank Hrvatska (HR)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F195" s="6" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
     </row>
@@ -15946,11 +16118,15 @@
       <c r="A196" s="4" t="n">
         <v>480078702810</v>
       </c>
-      <c r="B196" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C196" s="4" t="n">
-        <v/>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Boshhh Group: lewis camilleri - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Boshhh Group</t>
+        </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
@@ -15967,36 +16143,44 @@
     </row>
     <row r="197">
       <c r="A197" s="4" t="n">
-        <v>493860038900</v>
-      </c>
-      <c r="B197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C197" s="4" t="n">
-        <v/>
+        <v>501654154439</v>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>IBEx Network: Christophe Camborde - contact form</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>inblocks</t>
+        </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
         <v>46167</v>
       </c>
       <c r="F197" s="6" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n">
-        <v>361599102167</v>
-      </c>
-      <c r="B198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C198" s="4" t="n">
-        <v/>
+        <v>495334935768</v>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn: Kinesis Money, Martin Aguilar</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Kinesis Money</t>
+        </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
@@ -16007,22 +16191,22 @@
         <v>46167</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="G198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n">
-        <v>501654154439</v>
+        <v>495879879885</v>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>IBEx Network: Christophe Camborde - contact form</t>
+          <t>es.ey.com: Carlota Navarrete - contact form</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>inblocks</t>
+          <t>EY Spain</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -16031,7 +16215,7 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>0</v>
@@ -16040,16 +16224,16 @@
     </row>
     <row r="200">
       <c r="A200" s="4" t="n">
-        <v>495334935768</v>
+        <v>499027245254</v>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn: Kinesis Money, Martin Aguilar</t>
+          <t>BRED Banque Populaire: christelle guibout - contact form</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Kinesis Money</t>
+          <t>BRED Banque Populaire</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -16058,7 +16242,7 @@
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>0</v>
@@ -16148,43 +16332,43 @@
     </row>
     <row r="204">
       <c r="A204" s="4" t="n">
-        <v>495879879885</v>
+        <v>110345261265</v>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>es.ey.com: Carlota Navarrete - contact form</t>
+          <t>Aunalytics: Markus Krusche - contact form</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>EY Spain</t>
+          <t>Aunalytics</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
         <v>46168</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>0</v>
+        <v>222600</v>
       </c>
       <c r="G204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n">
-        <v>499027245254</v>
+        <v>504371551475</v>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>BRED Banque Populaire: christelle guibout - contact form</t>
+          <t>fixv: Ramin Rastegar - contact form</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>BRED Banque Populaire</t>
+          <t>fixv</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -16202,52 +16386,52 @@
     </row>
     <row r="206">
       <c r="A206" s="4" t="n">
-        <v>110345261265</v>
+        <v>444142278902</v>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Aunalytics: Markus Krusche - contact form</t>
+          <t>ABS: Santander Bank Polska (Tapix)</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Aunalytics</t>
+          <t>Santander Bank PL</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>222600</v>
+        <v>300000</v>
       </c>
       <c r="G206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n">
-        <v>504371551475</v>
+        <v>497719804091</v>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>fixv: Ramin Rastegar - contact form</t>
+          <t>Pay360: allpay Limited</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>fixv</t>
+          <t>allpay Limited</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="F207" s="6" t="n">
         <v>0</v>
@@ -16256,48 +16440,52 @@
     </row>
     <row r="208">
       <c r="A208" s="4" t="n">
-        <v>444142278902</v>
-      </c>
-      <c r="B208" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C208" s="4" t="n">
-        <v/>
+        <v>499033732307</v>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>es.ey.com: Victor Vazquez Rey - contact form</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>es.ey.com</t>
+        </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n">
-        <v>497719804091</v>
+        <v>252509831368</v>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Pay360: allpay Limited</t>
+          <t>Brand Boekhouders: Ruben Baggen - contact form</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>allpay Limited</t>
+          <t>Brand Boekhouders</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>0</v>
@@ -16306,16 +16494,16 @@
     </row>
     <row r="210">
       <c r="A210" s="4" t="n">
-        <v>252509831368</v>
+        <v>501540871391</v>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Brand Boekhouders: Ruben Baggen - contact form</t>
+          <t>Carlos Schuenck - Dev Portal Lead</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Brand Boekhouders</t>
+          <t>Carlos Schuenck &amp; Lourenço LDA</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -16324,7 +16512,7 @@
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F210" s="6" t="n">
         <v>0</v>
@@ -16333,25 +16521,23 @@
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
-        <v>499033732307</v>
+        <v>505781803242</v>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>es.ey.com: Victor Vazquez Rey - contact form</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>es.ey.com</t>
-        </is>
+          <t>Kuwait Finance House: Abdulrahman M Alsaqran - contact form</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="n">
+        <v/>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>0</v>
@@ -16360,51 +16546,55 @@
     </row>
     <row r="212">
       <c r="A212" s="4" t="n">
-        <v>501540871391</v>
+        <v>43653769413</v>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Carlos Schuenck - Dev Portal Lead</t>
+          <t>Uniglobal 24: Volksbank Wien</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Carlos Schuenck &amp; Lourenço LDA</t>
+          <t>Volksbank Wien</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n">
-        <v>505743116486</v>
-      </c>
-      <c r="B213" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C213" s="4" t="n">
-        <v/>
+        <v>78258022608</v>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>FintechConnect24: Luzerner Kantonalbank</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Luzerner Kantonalbank</t>
+        </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>38000</v>
+        <v>1</v>
       </c>
       <c r="G213" s="4" t="inlineStr"/>
     </row>
@@ -16412,11 +16602,15 @@
       <c r="A214" s="4" t="n">
         <v>285394684142</v>
       </c>
-      <c r="B214" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C214" s="4" t="n">
-        <v/>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>N26 - RPI (Tapix)</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
@@ -16433,43 +16627,43 @@
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
-        <v>505667256549</v>
+        <v>14786803914</v>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>: misha mikhaylov - contact form</t>
+          <t>M24:Rabobank - New Deal</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Luminar Capital</t>
+          <t>Rabobank</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E215" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="n">
-        <v>14786803914</v>
+        <v>202506743999</v>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>M24:Rabobank - New Deal</t>
+          <t>Belfius</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Rabobank</t>
+          <t>Belfius</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -16481,22 +16675,22 @@
         <v>46184</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="G216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
-        <v>78258022608</v>
+        <v>273762210003</v>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>FintechConnect24: Luzerner Kantonalbank</t>
+          <t>N26, woodpecker</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Luzerner Kantonalbank</t>
+          <t>N26</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -16508,76 +16702,76 @@
         <v>46184</v>
       </c>
       <c r="F217" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="n">
-        <v>90309296366</v>
+        <v>505124448464</v>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>FintechConnect24: Mano.bank</t>
+          <t>Secret Alchemist: Moksha Shah - contact form</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Mano.bank</t>
+          <t>Secret Alchemist</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
-        <v>11400117471</v>
+        <v>505667256549</v>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive: PSA</t>
+          <t>: misha mikhaylov - contact form</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Payment Service Austria</t>
+          <t>Luminar Capital</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E219" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F219" s="6" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="n">
-        <v>43653769413</v>
+        <v>90309296366</v>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Uniglobal 24: Volksbank Wien</t>
+          <t>FintechConnect24: Mano.bank</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Volksbank Wien</t>
+          <t>Mano.bank</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -16589,34 +16783,34 @@
         <v>46184</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>1</v>
+        <v>20000</v>
       </c>
       <c r="G220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="n">
-        <v>505124448464</v>
+        <v>11400117471</v>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Secret Alchemist: Moksha Shah - contact form</t>
+          <t>MoneyLive: PSA</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Secret Alchemist</t>
+          <t>Payment Service Austria</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F221" s="6" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G221" s="4" t="inlineStr"/>
     </row>
@@ -16649,52 +16843,52 @@
     </row>
     <row r="223">
       <c r="A223" s="4" t="n">
-        <v>202506743999</v>
+        <v>459737998579</v>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Belfius</t>
+          <t>ABS: Alpha Bank GR (Tapix)</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Belfius</t>
+          <t>Alpha Bank (GR)</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="F223" s="6" t="n">
-        <v>1</v>
+        <v>250000</v>
       </c>
       <c r="G223" s="4" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n">
-        <v>273762210003</v>
+        <v>450455338177</v>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>N26, woodpecker</t>
+          <t>ABS: Jeton</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>N26</t>
+          <t>Jeton</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="F224" s="6" t="n">
         <v>0</v>
@@ -16703,23 +16897,25 @@
     </row>
     <row r="225">
       <c r="A225" s="4" t="n">
-        <v>505781803242</v>
+        <v>498128344251</v>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Kuwait Finance House: Abdulrahman M Alsaqran - contact form</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="n">
-        <v/>
+          <t>TD Securities, woodpecker</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>TD Securities</t>
+        </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="F225" s="6" t="n">
         <v>0</v>
@@ -16728,48 +16924,50 @@
     </row>
     <row r="226">
       <c r="A226" s="4" t="n">
-        <v>459737998579</v>
-      </c>
-      <c r="B226" s="4" t="n">
-        <v/>
+        <v>504444582088</v>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>LinkedIn: First County Bank</t>
+        </is>
       </c>
       <c r="C226" s="4" t="n">
         <v/>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E226" s="5" t="n">
-        <v>46185</v>
+        <v>46190</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="G226" s="4" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n">
-        <v>450455338177</v>
+        <v>505250577653</v>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>ABS: Jeton</t>
+          <t>: Tom Vrbovsky - contact form</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Jeton</t>
+          <t>cashdog.cz</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E227" s="5" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="F227" s="6" t="n">
         <v>0</v>
@@ -16778,25 +16976,25 @@
     </row>
     <row r="228">
       <c r="A228" s="4" t="n">
-        <v>498128344251</v>
+        <v>505226774776</v>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>TD Securities, woodpecker</t>
+          <t>Coppard Plant Hire: Joby Coppard - contact form</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>TD Securities</t>
+          <t>Coppard Plant Hire</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E228" s="5" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="F228" s="6" t="n">
         <v>0</v>
@@ -16805,50 +17003,50 @@
     </row>
     <row r="229">
       <c r="A229" s="4" t="n">
-        <v>504444582088</v>
+        <v>97504524523</v>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn: First County Bank</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="n">
-        <v/>
+          <t>Finanzfluss: Thomas Kehl - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>Finanzfluss</t>
+        </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">
-        <v>46190</v>
+        <v>46198</v>
       </c>
       <c r="F229" s="6" t="n">
-        <v>0</v>
+        <v>141550</v>
       </c>
       <c r="G229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="n">
-        <v>505250577653</v>
+        <v>504026072307</v>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>: Tom Vrbovsky - contact form</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>cashdog.cz</t>
-        </is>
+          <t>LinkedIn: Kulipa</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="n">
+        <v/>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E230" s="5" t="n">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="F230" s="6" t="n">
         <v>0</v>
@@ -16857,16 +17055,16 @@
     </row>
     <row r="231">
       <c r="A231" s="4" t="n">
-        <v>505226774776</v>
+        <v>314791510235</v>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Coppard Plant Hire: Joby Coppard - contact form</t>
+          <t>FIZ - New Deal Alex Kosovskiy</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Coppard Plant Hire</t>
+          <t>FIZ</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -16875,43 +17073,45 @@
         </is>
       </c>
       <c r="E231" s="5" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="F231" s="6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="n">
-        <v>97504524523</v>
-      </c>
-      <c r="B232" s="4" t="n">
-        <v/>
+        <v>499903363308</v>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>: Camille Bernard - contact form</t>
+        </is>
       </c>
       <c r="C232" s="4" t="n">
         <v/>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E232" s="5" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="F232" s="6" t="n">
-        <v>141550</v>
+        <v>0</v>
       </c>
       <c r="G232" s="4" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
-        <v>504026072307</v>
+        <v>499908905161</v>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn: Kulipa</t>
+          <t>: Léa Morel - contact form</t>
         </is>
       </c>
       <c r="C233" s="4" t="n">
@@ -16923,7 +17123,7 @@
         </is>
       </c>
       <c r="E233" s="5" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="F233" s="6" t="n">
         <v>0</v>
@@ -16932,11 +17132,11 @@
     </row>
     <row r="234">
       <c r="A234" s="4" t="n">
-        <v>499903363308</v>
+        <v>499951318240</v>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>: Camille Bernard - contact form</t>
+          <t>: Antoine Lefebvre - contact form</t>
         </is>
       </c>
       <c r="C234" s="4" t="n">
@@ -16957,11 +17157,11 @@
     </row>
     <row r="235">
       <c r="A235" s="4" t="n">
-        <v>499908905161</v>
+        <v>499915276494</v>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>: Léa Morel - contact form</t>
+          <t>: Alexandre Dupuis - contact form</t>
         </is>
       </c>
       <c r="C235" s="4" t="n">
@@ -16982,11 +17182,11 @@
     </row>
     <row r="236">
       <c r="A236" s="4" t="n">
-        <v>499951318240</v>
+        <v>500570087661</v>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>: Antoine Lefebvre - contact form</t>
+          <t>: Pierre Moreau - contact form</t>
         </is>
       </c>
       <c r="C236" s="4" t="n">
@@ -17007,11 +17207,11 @@
     </row>
     <row r="237">
       <c r="A237" s="4" t="n">
-        <v>499915276494</v>
+        <v>500697270483</v>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>: Alexandre Dupuis - contact form</t>
+          <t>: Marie Rousseau - contact form</t>
         </is>
       </c>
       <c r="C237" s="4" t="n">
@@ -17032,15 +17232,17 @@
     </row>
     <row r="238">
       <c r="A238" s="4" t="n">
-        <v>500570087661</v>
+        <v>500700135636</v>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>: Pierre Moreau - contact form</t>
-        </is>
-      </c>
-      <c r="C238" s="4" t="n">
-        <v/>
+          <t>Calcul.IA: Marie Rousseau - contact form</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Calcul.IA</t>
+        </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
@@ -17057,15 +17259,17 @@
     </row>
     <row r="239">
       <c r="A239" s="4" t="n">
-        <v>500697270483</v>
+        <v>500849831140</v>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>: Marie Rousseau - contact form</t>
-        </is>
-      </c>
-      <c r="C239" s="4" t="n">
-        <v/>
+          <t>Calcul.IA: Camille Bernard - contact form</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Calcul.IA</t>
+        </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
@@ -17082,17 +17286,15 @@
     </row>
     <row r="240">
       <c r="A240" s="4" t="n">
-        <v>500700135636</v>
+        <v>499899778280</v>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Calcul.IA: Marie Rousseau - contact form</t>
-        </is>
-      </c>
-      <c r="C240" s="4" t="inlineStr">
-        <is>
-          <t>Calcul.IA</t>
-        </is>
+          <t>: Chloé Lambert - contact form</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="n">
+        <v/>
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
@@ -17109,16 +17311,16 @@
     </row>
     <row r="241">
       <c r="A241" s="4" t="n">
-        <v>500849831140</v>
+        <v>504456380660</v>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Calcul.IA: Camille Bernard - contact form</t>
+          <t>Cornerstone Asset Managers: Mukisa Moses - contact form</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Calcul.IA</t>
+          <t>Cornerstone Asset Managers</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -17136,15 +17338,17 @@
     </row>
     <row r="242">
       <c r="A242" s="4" t="n">
-        <v>499899778280</v>
+        <v>504698194164</v>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>: Chloé Lambert - contact form</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="n">
-        <v/>
+          <t>Toptal: Stefan Pajkovic - contact form</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>Toptal</t>
+        </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
@@ -17161,16 +17365,16 @@
     </row>
     <row r="243">
       <c r="A243" s="4" t="n">
-        <v>504456380660</v>
+        <v>438194203865</v>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Cornerstone Asset Managers: Mukisa Moses - contact form</t>
+          <t>Fungy: Diaa El Abd - contact form</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Cornerstone Asset Managers</t>
+          <t>Fungy</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -17179,7 +17383,7 @@
         </is>
       </c>
       <c r="E243" s="5" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="F243" s="6" t="n">
         <v>0</v>
@@ -17188,16 +17392,16 @@
     </row>
     <row r="244">
       <c r="A244" s="4" t="n">
-        <v>504698194164</v>
+        <v>508272964823</v>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Toptal: Stefan Pajkovic - contact form</t>
+          <t>Quam: Frank Murges - contact form</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Toptal</t>
+          <t>Quam</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -17206,7 +17410,7 @@
         </is>
       </c>
       <c r="E244" s="5" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="F244" s="6" t="n">
         <v>0</v>
@@ -17215,70 +17419,70 @@
     </row>
     <row r="245">
       <c r="A245" s="4" t="n">
-        <v>314791510235</v>
+        <v>366191757517</v>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>FIZ - New Deal Alex Kosovskiy</t>
+          <t>Source: Linkedin; Company: VeloBank S.A. (Tapix)</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>FIZ</t>
+          <t>VeloBank</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E245" s="5" t="n">
-        <v>46202</v>
+        <v>46211</v>
       </c>
       <c r="F245" s="6" t="n">
-        <v>12000</v>
+        <v>240000</v>
       </c>
       <c r="G245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="n">
-        <v>438194203865</v>
+        <v>504607785173</v>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Fungy: Diaa El Abd - contact form</t>
+          <t>Luminor Group (Tapix)</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Fungy</t>
+          <t>Luminor Group</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E246" s="5" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F246" s="6" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="G246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n">
-        <v>508272964823</v>
+        <v>498185765073</v>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Quam: Frank Murges - contact form</t>
+          <t>: Cassidy Wilson - contact form</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Quam</t>
+          <t>leadsprocentre.com</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -17287,7 +17491,7 @@
         </is>
       </c>
       <c r="E247" s="5" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="F247" s="6" t="n">
         <v>0</v>
@@ -17296,94 +17500,106 @@
     </row>
     <row r="248">
       <c r="A248" s="4" t="n">
-        <v>366191757517</v>
-      </c>
-      <c r="B248" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C248" s="4" t="n">
-        <v/>
+        <v>510128745662</v>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>susleny.co.uk: Susleny Coffee - contact form</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Susleny</t>
+        </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E248" s="5" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="F248" s="6" t="n">
-        <v>240000</v>
+        <v>0</v>
       </c>
       <c r="G248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n">
-        <v>504607785173</v>
-      </c>
-      <c r="B249" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C249" s="4" t="n">
-        <v/>
+        <v>498044744927</v>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Profinch Solutions - Dev Portal Reaction</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>Profinch Solutions</t>
+        </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E249" s="5" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="F249" s="6" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="G249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="n">
-        <v>504607785173</v>
-      </c>
-      <c r="B250" s="4" t="n">
-        <v/>
-      </c>
-      <c r="C250" s="4" t="n">
-        <v/>
+        <v>16200551119</v>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Jordan Ahli Bank, woodpecker</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>Jordan Ahli Bank</t>
+        </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E250" s="5" t="n">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="F250" s="6" t="n">
-        <v>180000</v>
+        <v>50000</v>
       </c>
       <c r="G250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="n">
-        <v>498185765073</v>
+        <v>245212643546</v>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>: Cassidy Wilson - contact form</t>
+          <t>Fintech Dubai:Wio UAE</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>leadsprocentre.com</t>
+          <t>Wio UAE</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="F251" s="6" t="n">
         <v>0</v>
@@ -17392,25 +17608,25 @@
     </row>
     <row r="252">
       <c r="A252" s="4" t="n">
-        <v>510128745662</v>
+        <v>285342572762</v>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>susleny.co.uk: Susleny Coffee - contact form</t>
+          <t>Source: Linkedin; Company: Banque Patronus</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Susleny</t>
+          <t>Banque Patronus</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="F252" s="6" t="n">
         <v>0</v>
@@ -17419,25 +17635,25 @@
     </row>
     <row r="253">
       <c r="A253" s="4" t="n">
-        <v>498044744927</v>
+        <v>495269111005</v>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Profinch Solutions - Dev Portal Reaction</t>
+          <t>Manager.one: Melanie FAUCHON - contact form</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Profinch Solutions</t>
+          <t>Manager.one</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="F253" s="6" t="n">
         <v>0</v>
@@ -17446,16 +17662,16 @@
     </row>
     <row r="254">
       <c r="A254" s="4" t="n">
-        <v>16200551119</v>
+        <v>285715078373</v>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Jordan Ahli Bank, woodpecker</t>
+          <t>AXIS India</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Jordan Ahli Bank</t>
+          <t>Axis Bank</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -17467,22 +17683,22 @@
         <v>46219</v>
       </c>
       <c r="F254" s="6" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G254" s="4" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n">
-        <v>245212643546</v>
+        <v>311526355159</v>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Fintech Dubai:Wio UAE</t>
+          <t>MoneyKSA: BSF</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Wio UAE</t>
+          <t>Banque Saudi Fransi</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -17500,16 +17716,16 @@
     </row>
     <row r="256">
       <c r="A256" s="4" t="n">
-        <v>285342572762</v>
+        <v>311549636806</v>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Banque Patronus</t>
+          <t>MoneyKSA: Drahim</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Banque Patronus</t>
+          <t>Drahim</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -17527,16 +17743,16 @@
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
-        <v>495269111005</v>
+        <v>311146490054</v>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Manager.one: Melanie FAUCHON - contact form</t>
+          <t>MoneyKSA: D360 Bank</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Manager.one</t>
+          <t>D360 Bank</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -17554,16 +17770,16 @@
     </row>
     <row r="258">
       <c r="A258" s="4" t="n">
-        <v>285715078373</v>
+        <v>311146494155</v>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>AXIS India</t>
+          <t>LiP2025: United Arab Bank</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Axis Bank</t>
+          <t>United Arab Bank</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -17575,22 +17791,22 @@
         <v>46219</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n">
-        <v>311526355159</v>
+        <v>375461881079</v>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: BSF</t>
+          <t>Source: SFF25; Company: Mashreq</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Banque Saudi Fransi</t>
+          <t>Mashreq</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -17608,16 +17824,16 @@
     </row>
     <row r="260">
       <c r="A260" s="4" t="n">
-        <v>311549636806</v>
+        <v>360458783986</v>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: Drahim</t>
+          <t>ATM Nearby: Axis Bank - New Deal (Tapix)</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Drahim</t>
+          <t>Axis Bank</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -17629,22 +17845,22 @@
         <v>46219</v>
       </c>
       <c r="F260" s="6" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n">
-        <v>311146490054</v>
+        <v>396380044523</v>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: D360 Bank</t>
+          <t>Mashreq Pakistan, Seamless Rijad 25</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>D360 Bank</t>
+          <t>Mashreq</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -17656,22 +17872,22 @@
         <v>46219</v>
       </c>
       <c r="F261" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n">
-        <v>311146494155</v>
+        <v>460476222664</v>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>LiP2025: United Arab Bank</t>
+          <t>Al Barid Bank - from HPS</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>United Arab Bank</t>
+          <t>Al Barid Bank</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -17683,22 +17899,22 @@
         <v>46219</v>
       </c>
       <c r="F262" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n">
-        <v>375461881079</v>
+        <v>501313743042</v>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Source: SFF25; Company: Mashreq</t>
+          <t>Standard Chartered Bank DXB - discovery</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Mashreq</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -17710,22 +17926,22 @@
         <v>46219</v>
       </c>
       <c r="F263" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G263" s="4" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="n">
-        <v>360458783986</v>
+        <v>501500997841</v>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>ATM Nearby: Axis Bank - New Deal (Tapix)</t>
+          <t>Abacus Pakistan - OH LinkedIn</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Axis Bank</t>
+          <t>Abacus Cambridge Partners</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -17737,22 +17953,22 @@
         <v>46219</v>
       </c>
       <c r="F264" s="6" t="n">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="G264" s="4" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n">
-        <v>396380044523</v>
+        <v>501500277973</v>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Mashreq Pakistan, Seamless Rijad 25</t>
+          <t>HSBC - Dubai OH</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Mashreq</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -17764,22 +17980,22 @@
         <v>46219</v>
       </c>
       <c r="F265" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="G265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="n">
-        <v>460476222664</v>
+        <v>496001859797</v>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Al Barid Bank - from HPS</t>
+          <t>Moved to Tapix: Inbound - Manager.one - New Deal</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Al Barid Bank</t>
+          <t>Manager.one</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -17791,117 +18007,9 @@
         <v>46219</v>
       </c>
       <c r="F266" s="6" t="n">
-        <v>200000</v>
+        <v>34175</v>
       </c>
       <c r="G266" s="4" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="4" t="n">
-        <v>501313743042</v>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>Standard Chartered Bank DXB - discovery</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="inlineStr">
-        <is>
-          <t>Standard Chartered Bank</t>
-        </is>
-      </c>
-      <c r="D267" s="4" t="inlineStr">
-        <is>
-          <t>Olda</t>
-        </is>
-      </c>
-      <c r="E267" s="5" t="n">
-        <v>46219</v>
-      </c>
-      <c r="F267" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G267" s="4" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="4" t="n">
-        <v>501500277973</v>
-      </c>
-      <c r="B268" s="4" t="inlineStr">
-        <is>
-          <t>HSBC - Dubai OH</t>
-        </is>
-      </c>
-      <c r="C268" s="4" t="inlineStr">
-        <is>
-          <t>HSBC</t>
-        </is>
-      </c>
-      <c r="D268" s="4" t="inlineStr">
-        <is>
-          <t>Olda</t>
-        </is>
-      </c>
-      <c r="E268" s="5" t="n">
-        <v>46219</v>
-      </c>
-      <c r="F268" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G268" s="4" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="4" t="n">
-        <v>501500997841</v>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>Abacus Pakistan - OH LinkedIn</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>Abacus Cambridge Partners</t>
-        </is>
-      </c>
-      <c r="D269" s="4" t="inlineStr">
-        <is>
-          <t>Olda</t>
-        </is>
-      </c>
-      <c r="E269" s="5" t="n">
-        <v>46219</v>
-      </c>
-      <c r="F269" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G269" s="4" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="4" t="n">
-        <v>496001859797</v>
-      </c>
-      <c r="B270" s="4" t="inlineStr">
-        <is>
-          <t>Moved to Tapix: Inbound - Manager.one - New Deal</t>
-        </is>
-      </c>
-      <c r="C270" s="4" t="inlineStr">
-        <is>
-          <t>Manager.one</t>
-        </is>
-      </c>
-      <c r="D270" s="4" t="inlineStr">
-        <is>
-          <t>Olda</t>
-        </is>
-      </c>
-      <c r="E270" s="5" t="n">
-        <v>46219</v>
-      </c>
-      <c r="F270" s="6" t="n">
-        <v>34175</v>
-      </c>
-      <c r="G270" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -18129,7 +18237,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
     </row>
     <row r="6">
@@ -18196,7 +18304,7 @@
         <v>98218</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7">
@@ -18263,7 +18371,7 @@
         <v>500</v>
       </c>
       <c r="U7" s="11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -18464,7 +18572,7 @@
         <v>348240</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>0</v>
+        <v>318840</v>
       </c>
     </row>
     <row r="11">
@@ -18531,7 +18639,7 @@
         <v>170000</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>0</v>
+        <v>215600</v>
       </c>
     </row>
     <row r="12">
@@ -18598,7 +18706,7 @@
         <v>1189350</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>0</v>
+        <v>1107900</v>
       </c>
     </row>
     <row r="13">
@@ -18665,7 +18773,7 @@
         <v>408830</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>0</v>
+        <v>612050</v>
       </c>
     </row>
     <row r="14">
@@ -18732,7 +18840,7 @@
         <v>0</v>
       </c>
       <c r="U14" s="12" t="n">
-        <v>0</v>
+        <v>89015</v>
       </c>
     </row>
     <row r="15">
@@ -18961,7 +19069,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>322504</v>
+        <v>280004</v>
       </c>
       <c r="I19" s="14" t="n">
         <v>350000</v>
@@ -19000,7 +19108,7 @@
         <v>0</v>
       </c>
       <c r="U19" s="14" t="n">
-        <v>600000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="20">
@@ -19067,7 +19175,7 @@
         <v>2270938</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>0</v>
+        <v>2348155</v>
       </c>
     </row>
     <row r="21">
@@ -19134,7 +19242,7 @@
         <v>135050</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>-2270938</v>
+        <v>77217</v>
       </c>
     </row>
     <row r="22">
@@ -19201,7 +19309,7 @@
         <v>2270938</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>2346655</v>
+        <v>2348155</v>
       </c>
     </row>
     <row r="23">
@@ -19296,46 +19404,46 @@
         <v>103125</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>36750.2</v>
+        <v>38472.44444444445</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>51666.85714285714</v>
+        <v>54868.63157894737</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>51666.85714285714</v>
+        <v>54868.63157894737</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>51666.85714285714</v>
+        <v>54868.63157894737</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>51666.85714285714</v>
+        <v>54868.63157894737</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>51666.85714285714</v>
+        <v>54868.63157894737</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>51666.85714285714</v>
+        <v>54868.63157894737</v>
       </c>
       <c r="O24" s="14" t="n">
-        <v>66739.30434782608</v>
+        <v>71071.61904761905</v>
       </c>
       <c r="P24" s="14" t="n">
-        <v>66739.30434782608</v>
+        <v>71071.61904761905</v>
       </c>
       <c r="Q24" s="14" t="n">
-        <v>74375.16666666667</v>
+        <v>79204.72727272728</v>
       </c>
       <c r="R24" s="14" t="n">
-        <v>74375.16666666667</v>
+        <v>79204.72727272728</v>
       </c>
       <c r="S24" s="14" t="n">
-        <v>74375.16666666667</v>
+        <v>79204.72727272728</v>
       </c>
       <c r="T24" s="14" t="n">
-        <v>74375.16666666667</v>
+        <v>79204.72727272728</v>
       </c>
       <c r="U24" s="14" t="n">
-        <v>88333.48148148147</v>
+        <v>90104.33333333333</v>
       </c>
     </row>
     <row r="25">
@@ -19699,7 +19807,7 @@
         <v>21370</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>0</v>
+        <v>21370</v>
       </c>
     </row>
     <row r="6">
@@ -19766,7 +19874,7 @@
         <v>3500</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>0</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="7">
@@ -20101,7 +20209,7 @@
         <v>5600</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>0</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="12">
@@ -20168,7 +20276,7 @@
         <v>90000</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="13">
@@ -20369,7 +20477,7 @@
         <v>95000</v>
       </c>
       <c r="U15" s="11" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="16">
@@ -20637,7 +20745,7 @@
         <v>223780</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>0</v>
+        <v>225670</v>
       </c>
     </row>
     <row r="21">
@@ -20704,7 +20812,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>-223780</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="22">
@@ -20771,7 +20879,7 @@
         <v>223780</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>213800</v>
+        <v>225670</v>
       </c>
     </row>
     <row r="23">
@@ -21202,7 +21310,7 @@
         <v>600</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>0</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="6">
@@ -21269,7 +21377,7 @@
         <v>800</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="7">
@@ -21537,7 +21645,7 @@
         <v>12600</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>0</v>
+        <v>149892</v>
       </c>
     </row>
     <row r="11">
@@ -21604,7 +21712,7 @@
         <v>148835</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>0</v>
+        <v>208835</v>
       </c>
     </row>
     <row r="12">
@@ -21671,7 +21779,7 @@
         <v>315000</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>0</v>
+        <v>372488</v>
       </c>
     </row>
     <row r="13">
@@ -21738,7 +21846,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>0</v>
+        <v>77400</v>
       </c>
     </row>
     <row r="14">
@@ -21872,7 +21980,7 @@
         <v>23750</v>
       </c>
       <c r="U15" s="11" t="n">
-        <v>0</v>
+        <v>23750</v>
       </c>
     </row>
     <row r="16">
@@ -22140,7 +22248,7 @@
         <v>505785</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>0</v>
+        <v>841965</v>
       </c>
     </row>
     <row r="21">
@@ -22207,7 +22315,7 @@
         <v>1500</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>-505785</v>
+        <v>336180</v>
       </c>
     </row>
     <row r="22">
@@ -22274,7 +22382,7 @@
         <v>505785</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>815615</v>
+        <v>841965</v>
       </c>
     </row>
     <row r="23">
@@ -23107,7 +23215,7 @@
         <v>19200</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>0</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="11">
@@ -23174,7 +23282,7 @@
         <v>7000</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="12">
@@ -23241,7 +23349,7 @@
         <v>87300</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>0</v>
+        <v>87300</v>
       </c>
     </row>
     <row r="13">
@@ -23308,7 +23416,7 @@
         <v>61200</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>0</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="14">
@@ -23710,7 +23818,7 @@
         <v>257610</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>0</v>
+        <v>181900</v>
       </c>
     </row>
     <row r="21">
@@ -23777,7 +23885,7 @@
         <v>54850</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>-257610</v>
+        <v>-75710</v>
       </c>
     </row>
     <row r="22">
@@ -24342,7 +24450,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>0</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="6">
@@ -24409,7 +24517,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>0</v>
+        <v>16320</v>
       </c>
     </row>
     <row r="7">
@@ -24677,7 +24785,7 @@
         <v>72000</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>0</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="11">
@@ -24744,7 +24852,7 @@
         <v>7600</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>0</v>
+        <v>77200</v>
       </c>
     </row>
     <row r="12">
@@ -24811,7 +24919,7 @@
         <v>68850</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>0</v>
+        <v>68850</v>
       </c>
     </row>
     <row r="13">
@@ -24878,7 +24986,7 @@
         <v>39690</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>0</v>
+        <v>39690</v>
       </c>
     </row>
     <row r="14">
@@ -25201,7 +25309,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="14" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="R19" s="14" t="n">
         <v>0</v>
@@ -25280,7 +25388,7 @@
         <v>188140</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>0</v>
+        <v>283710</v>
       </c>
     </row>
     <row r="21">
@@ -25347,7 +25455,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>-188140</v>
+        <v>95570</v>
       </c>
     </row>
     <row r="22">
@@ -25536,19 +25644,19 @@
         <v>75937.5</v>
       </c>
       <c r="Q24" s="14" t="n">
-        <v>73705.88235294117</v>
+        <v>75937.5</v>
       </c>
       <c r="R24" s="14" t="n">
-        <v>69611.11111111111</v>
+        <v>71470.58823529411</v>
       </c>
       <c r="S24" s="14" t="n">
-        <v>69611.11111111111</v>
+        <v>71470.58823529411</v>
       </c>
       <c r="T24" s="14" t="n">
-        <v>69611.11111111111</v>
+        <v>71470.58823529411</v>
       </c>
       <c r="U24" s="14" t="n">
-        <v>69611.11111111111</v>
+        <v>71470.58823529411</v>
       </c>
     </row>
     <row r="25">
@@ -25912,7 +26020,7 @@
         <v>7000</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6">
@@ -25979,7 +26087,7 @@
         <v>1000</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="7">
@@ -26247,7 +26355,7 @@
         <v>24000</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>0</v>
+        <v>85200</v>
       </c>
     </row>
     <row r="11">
@@ -26314,7 +26422,7 @@
         <v>60000</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="12">
@@ -26381,7 +26489,7 @@
         <v>0</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="13">
@@ -26850,7 +26958,7 @@
         <v>164500</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>0</v>
+        <v>228700</v>
       </c>
     </row>
     <row r="21">
@@ -26917,7 +27025,7 @@
         <v>1000</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>-164500</v>
+        <v>64200</v>
       </c>
     </row>
     <row r="22">
@@ -26984,7 +27092,7 @@
         <v>164500</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>208700</v>
+        <v>228700</v>
       </c>
     </row>
     <row r="23">
@@ -27817,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="11">
@@ -27884,7 +27992,7 @@
         <v>0</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="12">
@@ -28420,7 +28528,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>0</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="21">
@@ -28487,7 +28595,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>0</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="22">

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -10331,58 +10331,58 @@
         <v>4291962</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>3625562</v>
+        <v>4437562</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>3690762</v>
+        <v>4502762</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>3693353</v>
+        <v>4505353</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3705593</v>
+        <v>4517593</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>3798105</v>
+        <v>4610105</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>3673339</v>
+        <v>4485339</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>3719504</v>
+        <v>4531504</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>4104304</v>
+        <v>4916304</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>4131214</v>
+        <v>4943214</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>4359578</v>
+        <v>5171578</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>4052038</v>
+        <v>4864038</v>
       </c>
       <c r="O20" s="14" t="n">
-        <v>4056260</v>
+        <v>4868260</v>
       </c>
       <c r="P20" s="14" t="n">
-        <v>3566908</v>
+        <v>4378908</v>
       </c>
       <c r="Q20" s="14" t="n">
-        <v>3904651</v>
+        <v>4716651</v>
       </c>
       <c r="R20" s="14" t="n">
-        <v>3443501</v>
+        <v>4805501</v>
       </c>
       <c r="S20" s="14" t="n">
-        <v>3418353</v>
+        <v>4780353</v>
       </c>
       <c r="T20" s="14" t="n">
-        <v>3610753</v>
+        <v>4972753</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>4137500</v>
+        <v>5499500</v>
       </c>
     </row>
     <row r="21">
@@ -10395,10 +10395,10 @@
         <v>3496462</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>795500</v>
+        <v>-16500</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>-666400</v>
+        <v>145600</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>65200</v>
@@ -10437,10 +10437,10 @@
         <v>-489352</v>
       </c>
       <c r="Q21" s="14" t="n">
-        <v>337743</v>
+        <v>-212257</v>
       </c>
       <c r="R21" s="14" t="n">
-        <v>-461150</v>
+        <v>88850</v>
       </c>
       <c r="S21" s="14" t="n">
         <v>-25148</v>
@@ -20694,58 +20694,58 @@
         <v>1240780</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>443780</v>
+        <v>1240780</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>413780</v>
+        <v>1210780</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>223780</v>
+        <v>1020780</v>
       </c>
       <c r="O20" s="14" t="n">
-        <v>223780</v>
+        <v>1020780</v>
       </c>
       <c r="P20" s="14" t="n">
-        <v>223780</v>
+        <v>1020780</v>
       </c>
       <c r="Q20" s="14" t="n">
-        <v>223780</v>
+        <v>1020780</v>
       </c>
       <c r="R20" s="14" t="n">
-        <v>223780</v>
+        <v>1020780</v>
       </c>
       <c r="S20" s="14" t="n">
-        <v>223780</v>
+        <v>1020780</v>
       </c>
       <c r="T20" s="14" t="n">
-        <v>223780</v>
+        <v>1020780</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>225670</v>
+        <v>1022670</v>
       </c>
     </row>
     <row r="21">
@@ -20758,10 +20758,10 @@
         <v>481780</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>759000</v>
+        <v>-38000</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>-797000</v>
+        <v>0</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>0</v>
@@ -22197,58 +22197,58 @@
         <v>1054384</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>1039384</v>
+        <v>1054384</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>989884</v>
+        <v>1004884</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>989884</v>
+        <v>1004884</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>992224</v>
+        <v>1007224</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>1013416</v>
+        <v>1028416</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>985636</v>
+        <v>1000636</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>985636</v>
+        <v>1000636</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1005636</v>
+        <v>1020636</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>1005636</v>
+        <v>1020636</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>1229070</v>
+        <v>1244070</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>1229070</v>
+        <v>1244070</v>
       </c>
       <c r="O20" s="14" t="n">
-        <v>1222392</v>
+        <v>1237392</v>
       </c>
       <c r="P20" s="14" t="n">
-        <v>724740</v>
+        <v>739740</v>
       </c>
       <c r="Q20" s="14" t="n">
-        <v>1049983</v>
+        <v>1064983</v>
       </c>
       <c r="R20" s="14" t="n">
-        <v>499983</v>
+        <v>1064983</v>
       </c>
       <c r="S20" s="14" t="n">
-        <v>504285</v>
+        <v>1069285</v>
       </c>
       <c r="T20" s="14" t="n">
-        <v>505785</v>
+        <v>1070785</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>841965</v>
+        <v>1406965</v>
       </c>
     </row>
     <row r="21">
@@ -22261,10 +22261,10 @@
         <v>1039384</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>-49500</v>
@@ -22303,10 +22303,10 @@
         <v>-497652</v>
       </c>
       <c r="Q21" s="14" t="n">
-        <v>325243</v>
+        <v>-224757</v>
       </c>
       <c r="R21" s="14" t="n">
-        <v>-550000</v>
+        <v>0</v>
       </c>
       <c r="S21" s="14" t="n">
         <v>4302</v>

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -9444,7 +9444,7 @@
         <v>28970</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>35270</v>
+        <v>23470</v>
       </c>
     </row>
     <row r="6">
@@ -9511,7 +9511,7 @@
         <v>103518</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>34020</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="7">
@@ -9578,7 +9578,7 @@
         <v>4000</v>
       </c>
       <c r="U7" s="11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9779,7 +9779,7 @@
         <v>476040</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>667932</v>
+        <v>499200</v>
       </c>
     </row>
     <row r="11">
@@ -9846,7 +9846,7 @@
         <v>399035</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>629635</v>
+        <v>424435</v>
       </c>
     </row>
     <row r="12">
@@ -9913,7 +9913,7 @@
         <v>1750500</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>1771538</v>
+        <v>1669050</v>
       </c>
     </row>
     <row r="13">
@@ -9980,7 +9980,7 @@
         <v>509720</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>790340</v>
+        <v>600890</v>
       </c>
     </row>
     <row r="14">
@@ -10382,7 +10382,7 @@
         <v>4972753</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>5499500</v>
+        <v>4798610</v>
       </c>
     </row>
     <row r="21">
@@ -10449,7 +10449,7 @@
         <v>192400</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>526747</v>
+        <v>523847</v>
       </c>
     </row>
     <row r="22">
@@ -10516,7 +10516,7 @@
         <v>3610753</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>4137500</v>
+        <v>4134600</v>
       </c>
     </row>
     <row r="23">
@@ -18237,7 +18237,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -18304,7 +18304,7 @@
         <v>98218</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
@@ -18371,7 +18371,7 @@
         <v>500</v>
       </c>
       <c r="U7" s="11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -18572,7 +18572,7 @@
         <v>348240</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>318840</v>
+        <v>303840</v>
       </c>
     </row>
     <row r="11">
@@ -18639,7 +18639,7 @@
         <v>170000</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>215600</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="12">
@@ -18706,7 +18706,7 @@
         <v>1189350</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>1107900</v>
+        <v>1062900</v>
       </c>
     </row>
     <row r="13">
@@ -18773,7 +18773,7 @@
         <v>408830</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>612050</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="14">
@@ -19175,7 +19175,7 @@
         <v>2270938</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>2348155</v>
+        <v>2106255</v>
       </c>
     </row>
     <row r="21">
@@ -19242,7 +19242,7 @@
         <v>135050</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>77217</v>
+        <v>75717</v>
       </c>
     </row>
     <row r="22">
@@ -19309,7 +19309,7 @@
         <v>2270938</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>2348155</v>
+        <v>2346655</v>
       </c>
     </row>
     <row r="23">
@@ -19874,7 +19874,7 @@
         <v>3500</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>3700</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="7">
@@ -20209,7 +20209,7 @@
         <v>5600</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>15600</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="12">
@@ -20745,7 +20745,7 @@
         <v>1020780</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>1022670</v>
+        <v>1012470</v>
       </c>
     </row>
     <row r="21">
@@ -20812,7 +20812,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>1890</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="22">
@@ -20879,7 +20879,7 @@
         <v>223780</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>225670</v>
+        <v>225470</v>
       </c>
     </row>
     <row r="23">
@@ -21310,7 +21310,7 @@
         <v>600</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>5600</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6">
@@ -21377,7 +21377,7 @@
         <v>800</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>4000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
@@ -21645,7 +21645,7 @@
         <v>12600</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>149892</v>
+        <v>18960</v>
       </c>
     </row>
     <row r="11">
@@ -21712,7 +21712,7 @@
         <v>148835</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>208835</v>
+        <v>148835</v>
       </c>
     </row>
     <row r="12">
@@ -21779,7 +21779,7 @@
         <v>315000</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>372488</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="13">
@@ -21846,7 +21846,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>77400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -22248,7 +22248,7 @@
         <v>1070785</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>1406965</v>
+        <v>1072945</v>
       </c>
     </row>
     <row r="21">
@@ -22315,7 +22315,7 @@
         <v>1500</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>336180</v>
+        <v>334980</v>
       </c>
     </row>
     <row r="22">
@@ -22382,7 +22382,7 @@
         <v>505785</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>841965</v>
+        <v>840765</v>
       </c>
     </row>
     <row r="23">
@@ -23215,7 +23215,7 @@
         <v>19200</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>26400</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="11">
@@ -23818,7 +23818,7 @@
         <v>257610</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>181900</v>
+        <v>174700</v>
       </c>
     </row>
     <row r="21">
@@ -24450,7 +24450,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="11" t="n">
-        <v>6050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -24517,7 +24517,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="12" t="n">
-        <v>16320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -24785,7 +24785,7 @@
         <v>72000</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>75600</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="11">
@@ -24852,7 +24852,7 @@
         <v>7600</v>
       </c>
       <c r="U11" s="11" t="n">
-        <v>77200</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="12">
@@ -25388,7 +25388,7 @@
         <v>188140</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>283710</v>
+        <v>188140</v>
       </c>
     </row>
     <row r="21">
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -28528,7 +28528,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>27400</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -9645,7 +9645,7 @@
         <v>182220</v>
       </c>
       <c r="U8" s="12" t="n">
-        <v>0</v>
+        <v>100560</v>
       </c>
     </row>
     <row r="9">
@@ -10382,7 +10382,7 @@
         <v>4972753</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>4798610</v>
+        <v>4899170</v>
       </c>
     </row>
     <row r="21">
@@ -10449,7 +10449,7 @@
         <v>192400</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>523847</v>
+        <v>718757</v>
       </c>
     </row>
     <row r="22">
@@ -10516,7 +10516,7 @@
         <v>3610753</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>4134600</v>
+        <v>4329510</v>
       </c>
     </row>
     <row r="23">
@@ -18438,7 +18438,7 @@
         <v>55800</v>
       </c>
       <c r="U8" s="12" t="n">
-        <v>0</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="9">
@@ -19175,7 +19175,7 @@
         <v>2270938</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>2106255</v>
+        <v>2162055</v>
       </c>
     </row>
     <row r="21">
@@ -19242,7 +19242,7 @@
         <v>135050</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>75717</v>
+        <v>163017</v>
       </c>
     </row>
     <row r="22">
@@ -19309,7 +19309,7 @@
         <v>2270938</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>2346655</v>
+        <v>2433955</v>
       </c>
     </row>
     <row r="23">
@@ -20008,7 +20008,7 @@
         <v>8310</v>
       </c>
       <c r="U8" s="12" t="n">
-        <v>0</v>
+        <v>8310</v>
       </c>
     </row>
     <row r="9">
@@ -20745,7 +20745,7 @@
         <v>1020780</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>1012470</v>
+        <v>1020780</v>
       </c>
     </row>
     <row r="21">
@@ -20812,7 +20812,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>1690</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="22">
@@ -20879,7 +20879,7 @@
         <v>223780</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>225470</v>
+        <v>233780</v>
       </c>
     </row>
     <row r="23">
@@ -21511,7 +21511,7 @@
         <v>4200</v>
       </c>
       <c r="U8" s="12" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="9">
@@ -22248,7 +22248,7 @@
         <v>1070785</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>1072945</v>
+        <v>1075645</v>
       </c>
     </row>
     <row r="21">
@@ -22315,7 +22315,7 @@
         <v>1500</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>334980</v>
+        <v>362430</v>
       </c>
     </row>
     <row r="22">
@@ -22382,7 +22382,7 @@
         <v>505785</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>840765</v>
+        <v>868215</v>
       </c>
     </row>
     <row r="23">
@@ -25455,7 +25455,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>95570</v>
+        <v>128270</v>
       </c>
     </row>
     <row r="22">
@@ -25522,7 +25522,7 @@
         <v>188140</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>283710</v>
+        <v>316410</v>
       </c>
     </row>
     <row r="23">
@@ -26221,7 +26221,7 @@
         <v>69000</v>
       </c>
       <c r="U8" s="12" t="n">
-        <v>0</v>
+        <v>33750</v>
       </c>
     </row>
     <row r="9">
@@ -26958,7 +26958,7 @@
         <v>164500</v>
       </c>
       <c r="U20" s="14" t="n">
-        <v>228700</v>
+        <v>262450</v>
       </c>
     </row>
     <row r="21">
@@ -27025,7 +27025,7 @@
         <v>1000</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>64200</v>
+        <v>97950</v>
       </c>
     </row>
     <row r="22">
@@ -27092,7 +27092,7 @@
         <v>164500</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>228700</v>
+        <v>262450</v>
       </c>
     </row>
     <row r="23">
@@ -28595,7 +28595,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="14" t="n">
-        <v>27400</v>
+        <v>32800</v>
       </c>
     </row>
     <row r="22">
@@ -28662,7 +28662,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="14" t="n">
-        <v>27400</v>
+        <v>32800</v>
       </c>
     </row>
     <row r="23">

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -10200,61 +10200,61 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>27970</v>
+        <v>24970</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>28970</v>
+        <v>24970</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>26970</v>
+        <v>21970</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>28970</v>
+        <v>22970</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>27970</v>
+        <v>23970</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>27970</v>
+        <v>23970</v>
       </c>
       <c r="P6" s="12" t="n">
-        <v>28970</v>
+        <v>22970</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28970</v>
+        <v>22970</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>28970</v>
+        <v>22970</v>
       </c>
       <c r="S6" s="12" t="n">
-        <v>28970</v>
+        <v>22970</v>
       </c>
       <c r="T6" s="12" t="n">
-        <v>28970</v>
+        <v>22970</v>
       </c>
       <c r="U6" s="12" t="n">
         <v>23470</v>
@@ -10267,61 +10267,61 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>96368</v>
+        <v>7900</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>96368</v>
+        <v>7900</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>96868</v>
+        <v>7900</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>98868</v>
+        <v>5900</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>98868</v>
+        <v>5900</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>98868</v>
+        <v>7400</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>101368</v>
+        <v>7400</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>101368</v>
+        <v>6400</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>101368</v>
+        <v>7400</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>101368</v>
+        <v>6400</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>104368</v>
+        <v>10400</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>104118</v>
+        <v>12400</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>105118</v>
+        <v>11400</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>105118</v>
+        <v>11400</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>103918</v>
+        <v>12200</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>103518</v>
+        <v>11800</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>103868</v>
+        <v>12150</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>103518</v>
+        <v>11800</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>103518</v>
+        <v>11800</v>
       </c>
       <c r="U7" s="11" t="n">
         <v>11800</v>
@@ -10334,61 +10334,61 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K8" s="12" t="n">
         <v>2250</v>
       </c>
-      <c r="C8" s="12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>1750</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>1750</v>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>1750</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>1750</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>4750</v>
-      </c>
       <c r="L8" s="12" t="n">
-        <v>500</v>
+        <v>1250</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>2000</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="S8" s="12" t="n">
-        <v>3000</v>
+        <v>1350</v>
       </c>
       <c r="T8" s="12" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="U8" s="12" t="n">
         <v>0</v>
@@ -10401,61 +10401,61 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>209838</v>
+        <v>175098</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>205338</v>
+        <v>170598</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>207738</v>
+        <v>170598</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>207738</v>
+        <v>170598</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>207738</v>
+        <v>170598</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>211278</v>
+        <v>172038</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>194928</v>
+        <v>155688</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>193188</v>
+        <v>153348</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>196188</v>
+        <v>156348</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>199548</v>
+        <v>159348</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>219798</v>
+        <v>178098</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>207048</v>
+        <v>165348</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>207648</v>
+        <v>165948</v>
       </c>
       <c r="O9" s="11" t="n">
-        <v>200970</v>
+        <v>159270</v>
       </c>
       <c r="P9" s="11" t="n">
-        <v>203970</v>
+        <v>162270</v>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>192270</v>
+        <v>149670</v>
       </c>
       <c r="R9" s="11" t="n">
-        <v>187170</v>
+        <v>143670</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>187170</v>
+        <v>143310</v>
       </c>
       <c r="T9" s="11" t="n">
-        <v>182220</v>
+        <v>137310</v>
       </c>
       <c r="U9" s="11" t="n">
         <v>100560</v>
@@ -10535,22 +10535,22 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>0</v>
+        <v>30249</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0</v>
+        <v>30249</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0</v>
+        <v>30249</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>0</v>
@@ -10586,10 +10586,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="U11" s="11" t="n">
         <v>0</v>
@@ -10690,40 +10690,40 @@
         <v>199000</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>248835</v>
+        <v>264235</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>248835</v>
+        <v>264235</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>257435</v>
+        <v>272835</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>265035</v>
+        <v>280435</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>287435</v>
+        <v>302835</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>277435</v>
+        <v>292835</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>402435</v>
+        <v>417835</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>437635</v>
+        <v>453035</v>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>462035</v>
+        <v>477435</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>507635</v>
+        <v>523035</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>444035</v>
+        <v>459435</v>
       </c>
       <c r="T13" s="11" t="n">
-        <v>399035</v>
+        <v>414435</v>
       </c>
       <c r="U13" s="11" t="n">
         <v>424435</v>
@@ -11808,61 +11808,61 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>3496462</v>
+        <v>3400503</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>4291962</v>
+        <v>4194503</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>4437562</v>
+        <v>4336703</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>4502762</v>
+        <v>4392253</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>4505353</v>
+        <v>4394844</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>4517593</v>
+        <v>4404984</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>4610105</v>
+        <v>4472397</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>4485339</v>
+        <v>4362431</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>4531504</v>
+        <v>4408596</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>4916304</v>
+        <v>4790036</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>4943214</v>
+        <v>4818696</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>5171578</v>
+        <v>5048260</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>4864038</v>
+        <v>4740520</v>
       </c>
       <c r="O31" s="14" t="n">
-        <v>4868260</v>
+        <v>4744242</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>4378908</v>
+        <v>4255390</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>4716651</v>
+        <v>4592233</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>4805501</v>
+        <v>4678183</v>
       </c>
       <c r="S31" s="14" t="n">
-        <v>4780353</v>
+        <v>4657025</v>
       </c>
       <c r="T31" s="14" t="n">
-        <v>4972753</v>
+        <v>4847025</v>
       </c>
       <c r="U31" s="14" t="n">
         <v>7853200</v>
@@ -11875,64 +11875,64 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>3496462</v>
+        <v>3572753</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>-16500</v>
+        <v>6000</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>145600</v>
+        <v>146400</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>65200</v>
+        <v>55550</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>2591</v>
+        <v>35691</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>12240</v>
+        <v>10140</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>92512</v>
+        <v>90663</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>-124766</v>
+        <v>-105466</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>46165</v>
+        <v>49165</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>384800</v>
+        <v>381440</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>26910</v>
+        <v>101260</v>
       </c>
       <c r="M32" s="14" t="n">
-        <v>228364</v>
+        <v>141164</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>-307540</v>
+        <v>-301570</v>
       </c>
       <c r="O32" s="14" t="n">
-        <v>4222</v>
+        <v>23322</v>
       </c>
       <c r="P32" s="14" t="n">
-        <v>-489352</v>
+        <v>-486852</v>
       </c>
       <c r="Q32" s="14" t="n">
-        <v>-212257</v>
+        <v>37480</v>
       </c>
       <c r="R32" s="14" t="n">
-        <v>88850</v>
+        <v>43950</v>
       </c>
       <c r="S32" s="14" t="n">
-        <v>-25148</v>
+        <v>136493</v>
       </c>
       <c r="T32" s="14" t="n">
-        <v>192400</v>
+        <v>276882</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>3811667</v>
+        <v>3207955</v>
       </c>
     </row>
     <row r="33">
@@ -11942,61 +11942,61 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>3496462</v>
+        <v>3572753</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>3479962</v>
+        <v>3578753</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>3625562</v>
+        <v>3725153</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>3690762</v>
+        <v>3780703</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>3693353</v>
+        <v>3816394</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>3705593</v>
+        <v>3826534</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>3798105</v>
+        <v>3917197</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>3673339</v>
+        <v>3811731</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>3719504</v>
+        <v>3860896</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>4104304</v>
+        <v>4242336</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>4131214</v>
+        <v>4343596</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>4359578</v>
+        <v>4484760</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>4052038</v>
+        <v>4183190</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>4056260</v>
+        <v>4206512</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>3566908</v>
+        <v>3719660</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>3354651</v>
+        <v>3757140</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>3443501</v>
+        <v>3801090</v>
       </c>
       <c r="S33" s="14" t="n">
-        <v>3418353</v>
+        <v>3937583</v>
       </c>
       <c r="T33" s="14" t="n">
-        <v>3610753</v>
+        <v>4214465</v>
       </c>
       <c r="U33" s="14" t="n">
         <v>7422420</v>
@@ -12680,61 +12680,61 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>9321802</v>
+        <v>200000</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>9321802</v>
+        <v>200000</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>9371802</v>
+        <v>200000</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>9571802</v>
+        <v>0</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>9571802</v>
+        <v>0</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>9571802</v>
+        <v>150000</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>9821806</v>
+        <v>150000</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>9821806</v>
+        <v>150000</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>9821806</v>
+        <v>150000</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="L8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="M8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="N8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="O8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="P8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="R8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="S8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="T8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="U8" s="22" t="n">
         <v>50000</v>
@@ -12750,58 +12750,58 @@
         <v>200000</v>
       </c>
       <c r="C9" s="22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="22" t="n">
         <v>200000</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="Q9" s="22" t="n">
         <v>200000</v>
       </c>
-      <c r="E9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>150000</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L9" s="22" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>50000</v>
-      </c>
-      <c r="O9" s="22" t="n">
-        <v>50000</v>
-      </c>
-      <c r="P9" s="22" t="n">
-        <v>50000</v>
-      </c>
-      <c r="Q9" s="22" t="n">
-        <v>50000</v>
-      </c>
       <c r="R9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="S9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="T9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U9" s="22" t="n">
         <v>0</v>
@@ -16258,22 +16258,22 @@
         </is>
       </c>
       <c r="B64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="C64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="D64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="G64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="H64" s="22" t="n">
         <v>0</v>
@@ -17763,7 +17763,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="22" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T87" s="22" t="n">
         <v>0</v>
@@ -17779,61 +17779,61 @@
         </is>
       </c>
       <c r="B88" s="22" t="n">
-        <v>1170000</v>
+        <v>12000</v>
       </c>
       <c r="C88" s="22" t="n">
-        <v>1170000</v>
+        <v>12000</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>1250000</v>
+        <v>12000</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>1250000</v>
+        <v>12000</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>1250000</v>
+        <v>12000</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>1320000</v>
+        <v>12000</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>1320000</v>
+        <v>12000</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>1340000</v>
+        <v>12000</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>1340000</v>
+        <v>12000</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>1352000</v>
+        <v>12000</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="O88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="P88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>1432000</v>
+        <v>12000</v>
       </c>
       <c r="R88" s="22" t="n">
-        <v>1462000</v>
+        <v>12000</v>
       </c>
       <c r="S88" s="22" t="n">
-        <v>1462000</v>
+        <v>0</v>
       </c>
       <c r="T88" s="22" t="n">
-        <v>1497000</v>
+        <v>0</v>
       </c>
       <c r="U88" s="22" t="n">
         <v>0</v>
@@ -20888,61 +20888,61 @@
         </is>
       </c>
       <c r="B137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="C137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="D137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="E137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="F137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="H137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="J137" s="22" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="L137" s="22" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="N137" s="22" t="n">
-        <v>600000</v>
+        <v>200000</v>
       </c>
       <c r="O137" s="22" t="n">
-        <v>600000</v>
+        <v>200000</v>
       </c>
       <c r="P137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="Q137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="R137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="S137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="U137" s="22" t="n">
         <v>150000</v>
@@ -20955,61 +20955,61 @@
         </is>
       </c>
       <c r="B138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="C138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="D138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="H138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>125000</v>
+        <v>300000</v>
       </c>
       <c r="J138" s="22" t="n">
-        <v>125000</v>
+        <v>400000</v>
       </c>
       <c r="K138" s="22" t="n">
-        <v>125000</v>
+        <v>400000</v>
       </c>
       <c r="L138" s="22" t="n">
-        <v>125000</v>
+        <v>500000</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="N138" s="22" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="O138" s="22" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="P138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="Q138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="R138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="S138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="U138" s="22" t="n">
         <v>700000</v>
@@ -21022,61 +21022,61 @@
         </is>
       </c>
       <c r="B139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="C139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="D139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="E139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="F139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="H139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>25000</v>
+        <v>125000</v>
       </c>
       <c r="J139" s="22" t="n">
-        <v>25000</v>
+        <v>125000</v>
       </c>
       <c r="K139" s="22" t="n">
-        <v>425000</v>
+        <v>125000</v>
       </c>
       <c r="L139" s="22" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="N139" s="22" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O139" s="22" t="n">
+        <v>200000</v>
+      </c>
+      <c r="P139" s="22" t="n">
         <v>100000</v>
       </c>
-      <c r="O139" s="22" t="n">
-        <v>150000</v>
-      </c>
-      <c r="P139" s="22" t="n">
-        <v>200000</v>
-      </c>
       <c r="Q139" s="22" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="R139" s="22" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="S139" s="22" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="T139" s="22" t="n">
-        <v>350000</v>
+        <v>100000</v>
       </c>
       <c r="U139" s="22" t="n">
         <v>0</v>
@@ -21223,13 +21223,13 @@
         </is>
       </c>
       <c r="B142" s="22" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="C142" s="22" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="D142" s="22" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="E142" s="22" t="n">
         <v>0</v>
@@ -21274,10 +21274,10 @@
         <v>0</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U142" s="22" t="n">
         <v>0</v>
@@ -23033,40 +23033,40 @@
         <v>77000</v>
       </c>
       <c r="I170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="J170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="K170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="L170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="M170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="N170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="O170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="P170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="Q170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="R170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="S170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="T170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="U170" s="22" t="n">
         <v>77000</v>
@@ -25932,37 +25932,37 @@
         <v>0</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="K7" s="22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="L7" s="22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="M7" s="22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="N7" s="22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="O7" s="22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="P7" s="22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>0</v>
+        <v>275000</v>
       </c>
       <c r="R7" s="22" t="n">
-        <v>0</v>
+        <v>275000</v>
       </c>
       <c r="S7" s="22" t="n">
-        <v>0</v>
+        <v>275000</v>
       </c>
       <c r="T7" s="22" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="U7" s="22" t="n">
         <v>75000</v>
@@ -25975,61 +25975,61 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>9321802</v>
+        <v>200000</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>9321802</v>
+        <v>200000</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>9371802</v>
+        <v>200000</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>9571802</v>
+        <v>0</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>9571802</v>
+        <v>0</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>9571802</v>
+        <v>150000</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>9821806</v>
+        <v>150000</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>9821806</v>
+        <v>150000</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>9821806</v>
+        <v>150000</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="L8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="M8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="N8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="O8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="P8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="R8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="S8" s="22" t="n">
-        <v>9821806</v>
+        <v>50000</v>
       </c>
       <c r="T8" s="22" t="n">
-        <v>9821806</v>
+        <v>250000</v>
       </c>
       <c r="U8" s="22" t="n">
         <v>150000</v>
@@ -26045,58 +26045,58 @@
         <v>200000</v>
       </c>
       <c r="C9" s="22" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="D9" s="22" t="n">
         <v>200000</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F9" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="L9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="M9" s="22" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="N9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="O9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="P9" s="22" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="R9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="S9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="T9" s="22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U9" s="22" t="n">
         <v>100000</v>
@@ -26109,61 +26109,61 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>2470001</v>
+        <v>2795001</v>
       </c>
       <c r="C10" s="22" t="n">
-        <v>2420001</v>
+        <v>2745001</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>2420001</v>
+        <v>2745001</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>2420001</v>
+        <v>2745001</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>2420001</v>
+        <v>3195001</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>2390001</v>
+        <v>3165001</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>2290000</v>
+        <v>3065000</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>2290000</v>
+        <v>3065000</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>2290000</v>
+        <v>3140000</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>2290000</v>
+        <v>3140000</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>2290000</v>
+        <v>3240000</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>2290000</v>
+        <v>3240000</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>2310000</v>
+        <v>3260000</v>
       </c>
       <c r="O10" s="22" t="n">
-        <v>2310000</v>
+        <v>3260000</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>2310000</v>
+        <v>3260000</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>2310000</v>
+        <v>3260000</v>
       </c>
       <c r="R10" s="22" t="n">
-        <v>2110000</v>
+        <v>3060000</v>
       </c>
       <c r="S10" s="22" t="n">
-        <v>2110000</v>
+        <v>3060000</v>
       </c>
       <c r="T10" s="22" t="n">
-        <v>1860000</v>
+        <v>3010000</v>
       </c>
       <c r="U10" s="22" t="n">
         <v>2910000</v>
@@ -26310,61 +26310,61 @@
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>2987000</v>
+        <v>3112000</v>
       </c>
       <c r="C13" s="22" t="n">
-        <v>3187000</v>
+        <v>3512000</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>3337000</v>
+        <v>3662000</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>3337000</v>
+        <v>3662000</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>3337000</v>
+        <v>3462000</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>3367000</v>
+        <v>3492000</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>3368000</v>
+        <v>3493000</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>3587000</v>
+        <v>3712000</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>3587000</v>
+        <v>3712000</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>3387000</v>
+        <v>3512000</v>
       </c>
       <c r="L13" s="22" t="n">
-        <v>3387000</v>
+        <v>3512000</v>
       </c>
       <c r="M13" s="22" t="n">
-        <v>3587000</v>
+        <v>3712000</v>
       </c>
       <c r="N13" s="22" t="n">
-        <v>3437000</v>
+        <v>3562000</v>
       </c>
       <c r="O13" s="22" t="n">
-        <v>2617000</v>
+        <v>2742000</v>
       </c>
       <c r="P13" s="22" t="n">
-        <v>2617000</v>
+        <v>2742000</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>2167000</v>
+        <v>2292000</v>
       </c>
       <c r="R13" s="22" t="n">
-        <v>2567000</v>
+        <v>2692000</v>
       </c>
       <c r="S13" s="22" t="n">
-        <v>2712000</v>
+        <v>2837000</v>
       </c>
       <c r="T13" s="22" t="n">
-        <v>2902000</v>
+        <v>3027000</v>
       </c>
       <c r="U13" s="22" t="n">
         <v>2657000</v>
@@ -26389,49 +26389,49 @@
         <v>100000</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>100000</v>
+        <v>328000</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>100000</v>
+        <v>328000</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>100000</v>
+        <v>328000</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>392000</v>
+        <v>620000</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>392000</v>
+        <v>620000</v>
       </c>
       <c r="K14" s="22" t="n">
-        <v>350000</v>
+        <v>578000</v>
       </c>
       <c r="L14" s="22" t="n">
-        <v>350000</v>
+        <v>578000</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>350000</v>
+        <v>578000</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>350000</v>
+        <v>578000</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>1050000</v>
+        <v>1278000</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>1050000</v>
+        <v>1278000</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>1345000</v>
+        <v>1573000</v>
       </c>
       <c r="R14" s="22" t="n">
         <v>1573000</v>
       </c>
       <c r="S14" s="22" t="n">
-        <v>1050000</v>
+        <v>1278000</v>
       </c>
       <c r="T14" s="22" t="n">
-        <v>850000</v>
+        <v>1078000</v>
       </c>
       <c r="U14" s="22" t="n">
         <v>1078000</v>
@@ -26562,10 +26562,10 @@
         <v>537755</v>
       </c>
       <c r="S16" s="22" t="n">
-        <v>454255</v>
+        <v>578755</v>
       </c>
       <c r="T16" s="22" t="n">
-        <v>454255</v>
+        <v>578755</v>
       </c>
       <c r="U16" s="22" t="n">
         <v>680055</v>
@@ -28032,61 +28032,61 @@
         </is>
       </c>
       <c r="B40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="C40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="D40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="K40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="L40" s="22" t="n">
-        <v>178000</v>
+        <v>228000</v>
       </c>
       <c r="M40" s="22" t="n">
-        <v>28000</v>
+        <v>78000</v>
       </c>
       <c r="N40" s="22" t="n">
-        <v>28000</v>
+        <v>78000</v>
       </c>
       <c r="O40" s="22" t="n">
-        <v>28000</v>
+        <v>78000</v>
       </c>
       <c r="P40" s="22" t="n">
-        <v>28000</v>
+        <v>78000</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>28000</v>
+        <v>78000</v>
       </c>
       <c r="R40" s="22" t="n">
-        <v>28000</v>
+        <v>78000</v>
       </c>
       <c r="S40" s="22" t="n">
-        <v>28000</v>
+        <v>78000</v>
       </c>
       <c r="T40" s="22" t="n">
-        <v>28000</v>
+        <v>78000</v>
       </c>
       <c r="U40" s="22" t="n">
         <v>78000</v>
@@ -29272,7 +29272,7 @@
         <v>60010</v>
       </c>
       <c r="T59" s="22" t="n">
-        <v>60010</v>
+        <v>560010</v>
       </c>
       <c r="U59" s="22" t="n">
         <v>560010</v>
@@ -29327,19 +29327,19 @@
         <v>140009</v>
       </c>
       <c r="P60" s="22" t="n">
-        <v>120009</v>
+        <v>320011</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>80008</v>
+        <v>280009</v>
       </c>
       <c r="R60" s="22" t="n">
-        <v>80008</v>
+        <v>280009</v>
       </c>
       <c r="S60" s="22" t="n">
-        <v>80008</v>
+        <v>280009</v>
       </c>
       <c r="T60" s="22" t="n">
-        <v>80008</v>
+        <v>280009</v>
       </c>
       <c r="U60" s="22" t="n">
         <v>280009</v>
@@ -29352,10 +29352,10 @@
         </is>
       </c>
       <c r="B61" s="22" t="n">
-        <v>1</v>
+        <v>110001</v>
       </c>
       <c r="C61" s="22" t="n">
-        <v>1</v>
+        <v>110001</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>0</v>
@@ -29397,13 +29397,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="22" t="n">
         <v>0</v>
@@ -29425,16 +29425,16 @@
         <v>832604</v>
       </c>
       <c r="D62" s="22" t="n">
-        <v>832605</v>
+        <v>942605</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>832605</v>
+        <v>942605</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>832605</v>
+        <v>942605</v>
       </c>
       <c r="G62" s="22" t="n">
-        <v>910605</v>
+        <v>1020605</v>
       </c>
       <c r="H62" s="22" t="n">
         <v>910605</v>
@@ -29464,16 +29464,16 @@
         <v>610007</v>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>90004</v>
+        <v>590005</v>
       </c>
       <c r="R62" s="22" t="n">
-        <v>90004</v>
+        <v>590006</v>
       </c>
       <c r="S62" s="22" t="n">
-        <v>90004</v>
+        <v>590006</v>
       </c>
       <c r="T62" s="22" t="n">
-        <v>140005</v>
+        <v>965008</v>
       </c>
       <c r="U62" s="22" t="n">
         <v>915009</v>
@@ -29553,22 +29553,22 @@
         </is>
       </c>
       <c r="B64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="C64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="D64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="G64" s="22" t="n">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="H64" s="22" t="n">
         <v>0</v>
@@ -29620,61 +29620,61 @@
         </is>
       </c>
       <c r="B65" s="22" t="n">
-        <v>1340175</v>
+        <v>1510175</v>
       </c>
       <c r="C65" s="22" t="n">
-        <v>1340175</v>
+        <v>1510175</v>
       </c>
       <c r="D65" s="22" t="n">
-        <v>1340175</v>
+        <v>1510175</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>1340175</v>
+        <v>1510175</v>
       </c>
       <c r="F65" s="22" t="n">
-        <v>1340175</v>
+        <v>1510175</v>
       </c>
       <c r="G65" s="22" t="n">
-        <v>1340175</v>
+        <v>1510175</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>1629275</v>
+        <v>1909275</v>
       </c>
       <c r="I65" s="22" t="n">
-        <v>1417275</v>
+        <v>1697275</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>1417275</v>
+        <v>1697275</v>
       </c>
       <c r="K65" s="22" t="n">
-        <v>1417275</v>
+        <v>1697275</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>1417275</v>
+        <v>1697275</v>
       </c>
       <c r="M65" s="22" t="n">
-        <v>1223100</v>
+        <v>1503100</v>
       </c>
       <c r="N65" s="22" t="n">
-        <v>1223100</v>
+        <v>1503100</v>
       </c>
       <c r="O65" s="22" t="n">
-        <v>1223100</v>
+        <v>1503100</v>
       </c>
       <c r="P65" s="22" t="n">
-        <v>856000</v>
+        <v>1136000</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>255000</v>
+        <v>855000</v>
       </c>
       <c r="R65" s="22" t="n">
-        <v>255000</v>
+        <v>855000</v>
       </c>
       <c r="S65" s="22" t="n">
-        <v>105000</v>
+        <v>705000</v>
       </c>
       <c r="T65" s="22" t="n">
-        <v>105000</v>
+        <v>1196100</v>
       </c>
       <c r="U65" s="22" t="n">
         <v>1249100</v>
@@ -29732,16 +29732,16 @@
         <v>712175</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>539175</v>
+        <v>839175</v>
       </c>
       <c r="R66" s="22" t="n">
-        <v>539175</v>
+        <v>839175</v>
       </c>
       <c r="S66" s="22" t="n">
-        <v>744175</v>
+        <v>1044175</v>
       </c>
       <c r="T66" s="22" t="n">
-        <v>744175</v>
+        <v>1044175</v>
       </c>
       <c r="U66" s="22" t="n">
         <v>1044175</v>
@@ -29799,16 +29799,16 @@
         <v>796300</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>741550</v>
+        <v>869300</v>
       </c>
       <c r="R67" s="22" t="n">
-        <v>741550</v>
+        <v>869300</v>
       </c>
       <c r="S67" s="22" t="n">
-        <v>700000</v>
+        <v>827750</v>
       </c>
       <c r="T67" s="22" t="n">
-        <v>700000</v>
+        <v>827750</v>
       </c>
       <c r="U67" s="22" t="n">
         <v>827750</v>
@@ -29866,16 +29866,16 @@
         <v>86000</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="R68" s="22" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="S68" s="22" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="T68" s="22" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="U68" s="22" t="n">
         <v>86000</v>
@@ -31058,7 +31058,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="22" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T87" s="22" t="n">
         <v>0</v>
@@ -31074,61 +31074,61 @@
         </is>
       </c>
       <c r="B88" s="22" t="n">
-        <v>1170000</v>
+        <v>12000</v>
       </c>
       <c r="C88" s="22" t="n">
-        <v>1170000</v>
+        <v>12000</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>1250000</v>
+        <v>12000</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>1250000</v>
+        <v>12000</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>1250000</v>
+        <v>12000</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>1320000</v>
+        <v>12000</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>1320000</v>
+        <v>12000</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>1340000</v>
+        <v>12000</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>1340000</v>
+        <v>12000</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>1352000</v>
+        <v>12000</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="O88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="P88" s="22" t="n">
-        <v>1402000</v>
+        <v>12000</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>1432000</v>
+        <v>12000</v>
       </c>
       <c r="R88" s="22" t="n">
-        <v>1462000</v>
+        <v>12000</v>
       </c>
       <c r="S88" s="22" t="n">
-        <v>1462000</v>
+        <v>0</v>
       </c>
       <c r="T88" s="22" t="n">
-        <v>1497000</v>
+        <v>0</v>
       </c>
       <c r="U88" s="22" t="n">
         <v>0</v>
@@ -31329,7 +31329,7 @@
         <v>300000</v>
       </c>
       <c r="T91" s="22" t="n">
-        <v>160000</v>
+        <v>220000</v>
       </c>
       <c r="U91" s="22" t="n">
         <v>220000</v>
@@ -32567,22 +32567,22 @@
         <v>0</v>
       </c>
       <c r="O111" s="22" t="n">
-        <v>0</v>
+        <v>1140000</v>
       </c>
       <c r="P111" s="22" t="n">
-        <v>0</v>
+        <v>570000</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>0</v>
+        <v>605000</v>
       </c>
       <c r="R111" s="22" t="n">
-        <v>0</v>
+        <v>605000</v>
       </c>
       <c r="S111" s="22" t="n">
-        <v>0</v>
+        <v>605000</v>
       </c>
       <c r="T111" s="22" t="n">
-        <v>0</v>
+        <v>605000</v>
       </c>
       <c r="U111" s="22" t="n">
         <v>605000</v>
@@ -32631,25 +32631,25 @@
         <v>0</v>
       </c>
       <c r="N112" s="22" t="n">
-        <v>0</v>
+        <v>617000</v>
       </c>
       <c r="O112" s="22" t="n">
-        <v>0</v>
+        <v>1062000</v>
       </c>
       <c r="P112" s="22" t="n">
-        <v>0</v>
+        <v>1632000</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>0</v>
+        <v>1632000</v>
       </c>
       <c r="R112" s="22" t="n">
-        <v>0</v>
+        <v>1632000</v>
       </c>
       <c r="S112" s="22" t="n">
-        <v>0</v>
+        <v>1632000</v>
       </c>
       <c r="T112" s="22" t="n">
-        <v>0</v>
+        <v>1632000</v>
       </c>
       <c r="U112" s="22" t="n">
         <v>1632000</v>
@@ -32747,43 +32747,43 @@
         <v>445000</v>
       </c>
       <c r="H114" s="22" t="n">
-        <v>0</v>
+        <v>445000</v>
       </c>
       <c r="I114" s="22" t="n">
-        <v>0</v>
+        <v>445000</v>
       </c>
       <c r="J114" s="22" t="n">
-        <v>0</v>
+        <v>445000</v>
       </c>
       <c r="K114" s="22" t="n">
-        <v>0</v>
+        <v>445000</v>
       </c>
       <c r="L114" s="22" t="n">
-        <v>0</v>
+        <v>445000</v>
       </c>
       <c r="M114" s="22" t="n">
-        <v>0</v>
+        <v>965000</v>
       </c>
       <c r="N114" s="22" t="n">
-        <v>0</v>
+        <v>965000</v>
       </c>
       <c r="O114" s="22" t="n">
-        <v>0</v>
+        <v>1090000</v>
       </c>
       <c r="P114" s="22" t="n">
-        <v>0</v>
+        <v>1090000</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>0</v>
+        <v>1090000</v>
       </c>
       <c r="R114" s="22" t="n">
-        <v>0</v>
+        <v>1090000</v>
       </c>
       <c r="S114" s="22" t="n">
-        <v>0</v>
+        <v>1090000</v>
       </c>
       <c r="T114" s="22" t="n">
-        <v>0</v>
+        <v>1090000</v>
       </c>
       <c r="U114" s="22" t="n">
         <v>1090000</v>
@@ -32978,13 +32978,13 @@
         <v>630000</v>
       </c>
       <c r="R117" s="22" t="n">
-        <v>600000</v>
+        <v>630000</v>
       </c>
       <c r="S117" s="22" t="n">
-        <v>600000</v>
+        <v>630000</v>
       </c>
       <c r="T117" s="22" t="n">
-        <v>600000</v>
+        <v>630000</v>
       </c>
       <c r="U117" s="22" t="n">
         <v>630001</v>
@@ -32997,61 +32997,61 @@
         </is>
       </c>
       <c r="B118" s="22" t="n">
-        <v>174000</v>
+        <v>694000</v>
       </c>
       <c r="C118" s="22" t="n">
-        <v>174000</v>
+        <v>694000</v>
       </c>
       <c r="D118" s="22" t="n">
-        <v>142000</v>
+        <v>662000</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="G118" s="22" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="H118" s="22" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="I118" s="22" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="J118" s="22" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="K118" s="22" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="L118" s="22" t="n">
-        <v>38000</v>
+        <v>906000</v>
       </c>
       <c r="M118" s="22" t="n">
-        <v>38000</v>
+        <v>386000</v>
       </c>
       <c r="N118" s="22" t="n">
-        <v>38000</v>
+        <v>386000</v>
       </c>
       <c r="O118" s="22" t="n">
-        <v>38000</v>
+        <v>386000</v>
       </c>
       <c r="P118" s="22" t="n">
-        <v>38000</v>
+        <v>386000</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>38000</v>
+        <v>386000</v>
       </c>
       <c r="R118" s="22" t="n">
-        <v>38000</v>
+        <v>386000</v>
       </c>
       <c r="S118" s="22" t="n">
-        <v>38000</v>
+        <v>386000</v>
       </c>
       <c r="T118" s="22" t="n">
-        <v>38000</v>
+        <v>386000</v>
       </c>
       <c r="U118" s="22" t="n">
         <v>386000</v>
@@ -34183,61 +34183,61 @@
         </is>
       </c>
       <c r="B137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="C137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="D137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="E137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="F137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="H137" s="22" t="n">
-        <v>400001</v>
+        <v>0</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="J137" s="22" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="L137" s="22" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="N137" s="22" t="n">
-        <v>600000</v>
+        <v>200000</v>
       </c>
       <c r="O137" s="22" t="n">
-        <v>600000</v>
+        <v>200000</v>
       </c>
       <c r="P137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="Q137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="R137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="S137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="U137" s="22" t="n">
         <v>150000</v>
@@ -34250,61 +34250,61 @@
         </is>
       </c>
       <c r="B138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="C138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="D138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="H138" s="22" t="n">
-        <v>125001</v>
+        <v>400001</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>125000</v>
+        <v>300000</v>
       </c>
       <c r="J138" s="22" t="n">
-        <v>125000</v>
+        <v>400000</v>
       </c>
       <c r="K138" s="22" t="n">
-        <v>125000</v>
+        <v>400000</v>
       </c>
       <c r="L138" s="22" t="n">
-        <v>125000</v>
+        <v>500000</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="N138" s="22" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="O138" s="22" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="P138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="Q138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="R138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="S138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="U138" s="22" t="n">
         <v>700000</v>
@@ -34317,61 +34317,61 @@
         </is>
       </c>
       <c r="B139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="C139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="D139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="E139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="F139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="H139" s="22" t="n">
-        <v>25000</v>
+        <v>125001</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>25000</v>
+        <v>125000</v>
       </c>
       <c r="J139" s="22" t="n">
-        <v>25000</v>
+        <v>125000</v>
       </c>
       <c r="K139" s="22" t="n">
-        <v>425000</v>
+        <v>125000</v>
       </c>
       <c r="L139" s="22" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="N139" s="22" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O139" s="22" t="n">
+        <v>200000</v>
+      </c>
+      <c r="P139" s="22" t="n">
         <v>100000</v>
       </c>
-      <c r="O139" s="22" t="n">
-        <v>150000</v>
-      </c>
-      <c r="P139" s="22" t="n">
-        <v>200000</v>
-      </c>
       <c r="Q139" s="22" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="R139" s="22" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="S139" s="22" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="T139" s="22" t="n">
-        <v>350000</v>
+        <v>100000</v>
       </c>
       <c r="U139" s="22" t="n">
         <v>0</v>
@@ -34518,13 +34518,13 @@
         </is>
       </c>
       <c r="B142" s="22" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="C142" s="22" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="D142" s="22" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="E142" s="22" t="n">
         <v>0</v>
@@ -34569,10 +34569,10 @@
         <v>0</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U142" s="22" t="n">
         <v>0</v>
@@ -36060,40 +36060,40 @@
         <v>0</v>
       </c>
       <c r="I166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="J166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="K166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="L166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="N166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="P166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="Q166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="R166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T166" s="22" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U166" s="22" t="n">
         <v>180000</v>
@@ -36240,61 +36240,61 @@
         </is>
       </c>
       <c r="B169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="C169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="D169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="J169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="K169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="L169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="M169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="N169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="Q169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="R169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="S169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="T169" s="22" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="U169" s="22" t="n">
         <v>100000</v>
@@ -36328,40 +36328,40 @@
         <v>77000</v>
       </c>
       <c r="I170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="J170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="K170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="L170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="M170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="N170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="O170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="P170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="Q170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="R170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="S170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="T170" s="22" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="U170" s="22" t="n">
         <v>77000</v>
@@ -46387,61 +46387,61 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>93218</v>
+        <v>2000</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>93218</v>
+        <v>2000</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>93718</v>
+        <v>2000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>95718</v>
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>95718</v>
+        <v>0</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>95718</v>
+        <v>1500</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>98218</v>
+        <v>1500</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>98218</v>
+        <v>1500</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>98218</v>
+        <v>1500</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>98218</v>
+        <v>500</v>
       </c>
       <c r="U7" s="11" t="n">
         <v>500</v>
@@ -46457,58 +46457,58 @@
         <v>2000</v>
       </c>
       <c r="C8" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="N8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="Q8" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="M8" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="N8" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O8" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="P8" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q8" s="12" t="n">
-        <v>500</v>
-      </c>
       <c r="R8" s="12" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S8" s="12" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="T8" s="12" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U8" s="12" t="n">
         <v>0</v>
@@ -47928,61 +47928,61 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>1412008</v>
+        <v>1320790</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>1422008</v>
+        <v>1329290</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>1533208</v>
+        <v>1439490</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>1611208</v>
+        <v>1515490</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1611208</v>
+        <v>1515490</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>1615408</v>
+        <v>1519690</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>1709978</v>
+        <v>1611760</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>1623658</v>
+        <v>1525440</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>1665823</v>
+        <v>1567605</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>2005923</v>
+        <v>1908705</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>2005923</v>
+        <v>1907705</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>2072088</v>
+        <v>1974070</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>2054688</v>
+        <v>1956470</v>
       </c>
       <c r="O31" s="14" t="n">
-        <v>2072888</v>
+        <v>1974670</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>2072888</v>
+        <v>1976670</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>2077888</v>
+        <v>1981670</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>2165488</v>
+        <v>2067270</v>
       </c>
       <c r="S31" s="14" t="n">
-        <v>2135888</v>
+        <v>2037670</v>
       </c>
       <c r="T31" s="14" t="n">
-        <v>2270938</v>
+        <v>2172720</v>
       </c>
       <c r="U31" s="14" t="n">
         <v>3764147</v>
@@ -47995,64 +47995,64 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>1412008</v>
+        <v>1345540</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>10000</v>
+        <v>32500</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>111200</v>
+        <v>112200</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>78000</v>
+        <v>76000</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>33100</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>4200</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>94570</v>
+        <v>92070</v>
       </c>
       <c r="I32" s="14" t="n">
         <v>-86320</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>42165</v>
+        <v>45165</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>340100</v>
+        <v>341100</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M32" s="14" t="n">
-        <v>66165</v>
+        <v>66365</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>-17400</v>
+        <v>-17600</v>
       </c>
       <c r="O32" s="14" t="n">
         <v>18200</v>
       </c>
       <c r="P32" s="14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Q32" s="14" t="n">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="R32" s="14" t="n">
-        <v>87600</v>
+        <v>40000</v>
       </c>
       <c r="S32" s="14" t="n">
-        <v>-29600</v>
+        <v>128050</v>
       </c>
       <c r="T32" s="14" t="n">
-        <v>135050</v>
+        <v>141050</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>1803109</v>
+        <v>1691427</v>
       </c>
     </row>
     <row r="33">
@@ -48062,61 +48062,61 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>1412008</v>
+        <v>1345540</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1422008</v>
+        <v>1378040</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>1533208</v>
+        <v>1490240</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>1611208</v>
+        <v>1566240</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1611208</v>
+        <v>1599340</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>1615408</v>
+        <v>1603540</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>1709978</v>
+        <v>1695610</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>1623658</v>
+        <v>1609290</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>1665823</v>
+        <v>1654455</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>2005923</v>
+        <v>1995555</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>2005923</v>
+        <v>1997555</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>2072088</v>
+        <v>2063920</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>2054688</v>
+        <v>2046320</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>2072888</v>
+        <v>2064520</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>2072888</v>
+        <v>2066520</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>2077888</v>
+        <v>2073520</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>2165488</v>
+        <v>2113520</v>
       </c>
       <c r="S33" s="14" t="n">
-        <v>2135888</v>
+        <v>2241570</v>
       </c>
       <c r="T33" s="14" t="n">
-        <v>2270938</v>
+        <v>2382620</v>
       </c>
       <c r="U33" s="14" t="n">
         <v>4074047</v>
@@ -50302,7 +50302,7 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>481780</v>
+        <v>491780</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>-38000</v>
@@ -50359,7 +50359,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>227200</v>
+        <v>217200</v>
       </c>
     </row>
     <row r="33">
@@ -50369,61 +50369,61 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>481780</v>
+        <v>491780</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>443780</v>
+        <v>453780</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>413780</v>
+        <v>423780</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>223780</v>
+        <v>233780</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>223780</v>
+        <v>233780</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>223780</v>
+        <v>233780</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>223780</v>
+        <v>233780</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>223780</v>
+        <v>233780</v>
       </c>
       <c r="S33" s="14" t="n">
-        <v>223780</v>
+        <v>233780</v>
       </c>
       <c r="T33" s="14" t="n">
-        <v>223780</v>
+        <v>233780</v>
       </c>
       <c r="U33" s="14" t="n">
         <v>450980</v>
@@ -51202,22 +51202,22 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0</v>
+        <v>22599</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>0</v>
@@ -52475,22 +52475,22 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>1039384</v>
+        <v>1061983</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>1054384</v>
+        <v>1076983</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>1054384</v>
+        <v>1076983</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>1004884</v>
+        <v>1027483</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1004884</v>
+        <v>1027483</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>1007224</v>
+        <v>1029823</v>
       </c>
       <c r="H31" s="14" t="n">
         <v>1028416</v>
@@ -52542,13 +52542,13 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>1039384</v>
+        <v>1083483</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>-49500</v>
@@ -52560,7 +52560,7 @@
         <v>2340</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>21192</v>
+        <v>8493</v>
       </c>
       <c r="I32" s="14" t="n">
         <v>-27780</v>
@@ -52584,22 +52584,22 @@
         <v>-6678</v>
       </c>
       <c r="P32" s="14" t="n">
-        <v>-497652</v>
+        <v>-495652</v>
       </c>
       <c r="Q32" s="14" t="n">
-        <v>-224757</v>
+        <v>23530</v>
       </c>
       <c r="R32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="S32" s="14" t="n">
-        <v>4302</v>
+        <v>4303</v>
       </c>
       <c r="T32" s="14" t="n">
-        <v>1500</v>
+        <v>75182</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>930988</v>
+        <v>573418</v>
       </c>
     </row>
     <row r="33">
@@ -52609,61 +52609,61 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>1039384</v>
+        <v>1083483</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1039384</v>
+        <v>1083483</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>1039384</v>
+        <v>1085683</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>989884</v>
+        <v>1036183</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>989884</v>
+        <v>1036183</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>992224</v>
+        <v>1038523</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>1013416</v>
+        <v>1047016</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>985636</v>
+        <v>1019236</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>985636</v>
+        <v>1019236</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>1005636</v>
+        <v>1039236</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>1005636</v>
+        <v>1039236</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>1229070</v>
+        <v>1262670</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>1229070</v>
+        <v>1262670</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>1222392</v>
+        <v>1255992</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>724740</v>
+        <v>760340</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>499983</v>
+        <v>783870</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>499983</v>
+        <v>783870</v>
       </c>
       <c r="S33" s="14" t="n">
-        <v>504285</v>
+        <v>788173</v>
       </c>
       <c r="T33" s="14" t="n">
-        <v>505785</v>
+        <v>863355</v>
       </c>
       <c r="U33" s="14" t="n">
         <v>1436773</v>
@@ -53359,7 +53359,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T8" s="12" t="n">
         <v>0</v>
@@ -53375,61 +53375,61 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>35100</v>
+        <v>360</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>35100</v>
+        <v>360</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>37500</v>
+        <v>360</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>37500</v>
+        <v>360</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>37500</v>
+        <v>360</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>39600</v>
+        <v>360</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>39600</v>
+        <v>360</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>40200</v>
+        <v>360</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>40200</v>
+        <v>360</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>40560</v>
+        <v>360</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>42060</v>
+        <v>360</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>42060</v>
+        <v>360</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>42060</v>
+        <v>360</v>
       </c>
       <c r="O9" s="11" t="n">
-        <v>42060</v>
+        <v>360</v>
       </c>
       <c r="P9" s="11" t="n">
-        <v>42060</v>
+        <v>360</v>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>42960</v>
+        <v>360</v>
       </c>
       <c r="R9" s="11" t="n">
-        <v>43860</v>
+        <v>360</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>43860</v>
+        <v>0</v>
       </c>
       <c r="T9" s="11" t="n">
-        <v>44910</v>
+        <v>0</v>
       </c>
       <c r="U9" s="11" t="n">
         <v>0</v>
@@ -54782,61 +54782,61 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>200300</v>
+        <v>165560</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>186800</v>
+        <v>152060</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>197000</v>
+        <v>159860</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>197000</v>
+        <v>159860</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>184600</v>
+        <v>147460</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>195100</v>
+        <v>155860</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>185200</v>
+        <v>145960</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>188200</v>
+        <v>148360</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>188200</v>
+        <v>148360</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>205900</v>
+        <v>165700</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>204760</v>
+        <v>163060</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>206760</v>
+        <v>165060</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>196760</v>
+        <v>155060</v>
       </c>
       <c r="O31" s="14" t="n">
-        <v>188960</v>
+        <v>147260</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>193760</v>
+        <v>152060</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>198260</v>
+        <v>155660</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>203110</v>
+        <v>159610</v>
       </c>
       <c r="S31" s="14" t="n">
-        <v>202760</v>
+        <v>159250</v>
       </c>
       <c r="T31" s="14" t="n">
-        <v>257610</v>
+        <v>212700</v>
       </c>
       <c r="U31" s="14" t="n">
         <v>354340</v>
@@ -54849,13 +54849,13 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>200300</v>
+        <v>165560</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>-13500</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>10200</v>
+        <v>7800</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>0</v>
@@ -54864,22 +54864,22 @@
         <v>-12400</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>10500</v>
+        <v>8400</v>
       </c>
       <c r="H32" s="14" t="n">
         <v>-9900</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>17700</v>
+        <v>17340</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>-1140</v>
+        <v>-2640</v>
       </c>
       <c r="M32" s="14" t="n">
         <v>2000</v>
@@ -54894,19 +54894,19 @@
         <v>4800</v>
       </c>
       <c r="Q32" s="14" t="n">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="R32" s="14" t="n">
-        <v>4850</v>
+        <v>3950</v>
       </c>
       <c r="S32" s="14" t="n">
-        <v>-350</v>
+        <v>-360</v>
       </c>
       <c r="T32" s="14" t="n">
-        <v>54850</v>
+        <v>60650</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>103930</v>
+        <v>141640</v>
       </c>
     </row>
     <row r="33">
@@ -54916,61 +54916,61 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>200300</v>
+        <v>165560</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>186800</v>
+        <v>152060</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>197000</v>
+        <v>159860</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>197000</v>
+        <v>159860</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>184600</v>
+        <v>147460</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>195100</v>
+        <v>155860</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>185200</v>
+        <v>145960</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>188200</v>
+        <v>148360</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>188200</v>
+        <v>148360</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>205900</v>
+        <v>165700</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>204760</v>
+        <v>163060</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>206760</v>
+        <v>165060</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>196760</v>
+        <v>155060</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>188960</v>
+        <v>147260</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>193760</v>
+        <v>152060</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>198260</v>
+        <v>155660</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>203110</v>
+        <v>159610</v>
       </c>
       <c r="S33" s="14" t="n">
-        <v>202760</v>
+        <v>159250</v>
       </c>
       <c r="T33" s="14" t="n">
-        <v>257610</v>
+        <v>219900</v>
       </c>
       <c r="U33" s="14" t="n">
         <v>361540</v>
@@ -57156,7 +57156,7 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>219690</v>
+        <v>323690</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>0</v>
@@ -57174,7 +57174,7 @@
         <v>-4800</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>-13350</v>
+        <v>0</v>
       </c>
       <c r="I32" s="14" t="n">
         <v>0</v>
@@ -57186,25 +57186,25 @@
         <v>0</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>12550</v>
+        <v>82150</v>
       </c>
       <c r="M32" s="14" t="n">
-        <v>0</v>
+        <v>-88400</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>-91140</v>
+        <v>-84970</v>
       </c>
       <c r="O32" s="14" t="n">
-        <v>0</v>
+        <v>19600</v>
       </c>
       <c r="P32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="14" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="R32" s="14" t="n">
-        <v>-3600</v>
+        <v>0</v>
       </c>
       <c r="S32" s="14" t="n">
         <v>0</v>
@@ -57213,7 +57213,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>386000</v>
+        <v>257730</v>
       </c>
     </row>
     <row r="33">
@@ -57223,61 +57223,61 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>219690</v>
+        <v>323690</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>219690</v>
+        <v>323690</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>242090</v>
+        <v>346090</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>277590</v>
+        <v>381590</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>288480</v>
+        <v>392480</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>283680</v>
+        <v>387680</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>270330</v>
+        <v>387680</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>270330</v>
+        <v>387680</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>270330</v>
+        <v>387680</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>270330</v>
+        <v>387680</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>282880</v>
+        <v>469830</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>282880</v>
+        <v>381430</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>191740</v>
+        <v>296460</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>191740</v>
+        <v>316060</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>191740</v>
+        <v>316060</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>191740</v>
+        <v>316410</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>188140</v>
+        <v>316410</v>
       </c>
       <c r="S33" s="14" t="n">
-        <v>188140</v>
+        <v>316410</v>
       </c>
       <c r="T33" s="14" t="n">
-        <v>188140</v>
+        <v>316410</v>
       </c>
       <c r="U33" s="14" t="n">
         <v>574140</v>
@@ -57788,61 +57788,61 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="P6" s="12" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="S6" s="12" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="T6" s="12" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="U6" s="12" t="n">
         <v>1500</v>
@@ -57855,61 +57855,61 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>1250</v>
+        <v>3000</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>1250</v>
+        <v>5000</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="U7" s="11" t="n">
         <v>7000</v>
@@ -57922,61 +57922,61 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>4250</v>
+        <v>1250</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N8" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O8" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P8" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="O8" s="12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="P8" s="12" t="n">
-        <v>2000</v>
-      </c>
       <c r="Q8" s="12" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="S8" s="12" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="T8" s="12" t="n">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="U8" s="12" t="n">
         <v>0</v>
@@ -58123,13 +58123,13 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>0</v>
+        <v>7650</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0</v>
+        <v>7650</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0</v>
+        <v>7650</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>0</v>
@@ -58174,10 +58174,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="T11" s="11" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="U11" s="11" t="n">
         <v>0</v>
@@ -59396,61 +59396,61 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>127900</v>
+        <v>135300</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>152900</v>
+        <v>160300</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>154700</v>
+        <v>162100</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>155900</v>
+        <v>155650</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>160001</v>
+        <v>159751</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>160001</v>
+        <v>159751</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>160001</v>
+        <v>159751</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>161735</v>
+        <v>161485</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>165735</v>
+        <v>165485</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>172735</v>
+        <v>168485</v>
       </c>
       <c r="L31" s="14" t="n">
         <v>188235</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>155000</v>
+        <v>156000</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>156000</v>
+        <v>157000</v>
       </c>
       <c r="O31" s="14" t="n">
-        <v>156500</v>
+        <v>157000</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>160000</v>
+        <v>159000</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>163000</v>
+        <v>162000</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>163000</v>
+        <v>162000</v>
       </c>
       <c r="S31" s="14" t="n">
-        <v>163500</v>
+        <v>166500</v>
       </c>
       <c r="T31" s="14" t="n">
-        <v>164500</v>
+        <v>166500</v>
       </c>
       <c r="U31" s="14" t="n">
         <v>436350</v>
@@ -59463,7 +59463,7 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>127900</v>
+        <v>135300</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>25000</v>
@@ -59472,7 +59472,7 @@
         <v>1800</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>1200</v>
+        <v>-6450</v>
       </c>
       <c r="F32" s="14" t="n">
         <v>4101</v>
@@ -59490,22 +59490,22 @@
         <v>4000</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>15500</v>
+        <v>19750</v>
       </c>
       <c r="M32" s="14" t="n">
-        <v>-33235</v>
+        <v>-32235</v>
       </c>
       <c r="N32" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="O32" s="14" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P32" s="14" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="Q32" s="14" t="n">
         <v>3000</v>
@@ -59514,13 +59514,13 @@
         <v>0</v>
       </c>
       <c r="S32" s="14" t="n">
-        <v>500</v>
+        <v>4500</v>
       </c>
       <c r="T32" s="14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>271850</v>
+        <v>269850</v>
       </c>
     </row>
     <row r="33">
@@ -59530,61 +59530,61 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>127900</v>
+        <v>135300</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>152900</v>
+        <v>160300</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>154700</v>
+        <v>162100</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>155900</v>
+        <v>155650</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>160001</v>
+        <v>159751</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>160001</v>
+        <v>159751</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>160001</v>
+        <v>159751</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>161735</v>
+        <v>161485</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>165735</v>
+        <v>165485</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>172735</v>
+        <v>168485</v>
       </c>
       <c r="L33" s="14" t="n">
         <v>188235</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>155000</v>
+        <v>156000</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>156000</v>
+        <v>157000</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>156500</v>
+        <v>157000</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>160000</v>
+        <v>159000</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>163000</v>
+        <v>162000</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>163000</v>
+        <v>162000</v>
       </c>
       <c r="S33" s="14" t="n">
-        <v>163500</v>
+        <v>166500</v>
       </c>
       <c r="T33" s="14" t="n">
-        <v>164500</v>
+        <v>166500</v>
       </c>
       <c r="U33" s="14" t="n">
         <v>436350</v>
@@ -60585,40 +60585,40 @@
         <v>15400</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="T13" s="11" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="U13" s="11" t="n">
         <v>15400</v>
@@ -61724,40 +61724,40 @@
         <v>15400</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="O31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="S31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="T31" s="14" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="U31" s="14" t="n">
         <v>58840</v>
@@ -61770,7 +61770,7 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>15400</v>
+        <v>27400</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>0</v>
@@ -61791,7 +61791,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>-15400</v>
+        <v>4500</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>0</v>
@@ -61827,7 +61827,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="14" t="n">
-        <v>88240</v>
+        <v>56340</v>
       </c>
     </row>
     <row r="33">
@@ -61837,61 +61837,61 @@
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>15400</v>
+        <v>27400</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>15400</v>
+        <v>27400</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>15400</v>
+        <v>27400</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>15400</v>
+        <v>27400</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>15400</v>
+        <v>27400</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>15400</v>
+        <v>27400</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>15400</v>
+        <v>27400</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="J33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="O33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="S33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="T33" s="14" t="n">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="U33" s="14" t="n">
         <v>88240</v>

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -452,7 +452,7 @@
                   <a:srgbClr val="1F2A44"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Funnel evolution over time – till end of year (weighted values)</a:t>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -460,44 +460,11 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A6</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$6:$AC$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A7</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="3D8B58"/>
@@ -509,297 +476,69 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
+              <f>'Lukáš'!$A$28:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lukáš'!$B$7:$AC$7</f>
+              <f>'Lukáš'!$AC$28:$AC$38</f>
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="C9A227"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$8:$AC$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A9</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$9:$AC$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A10</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$10:$AC$10</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$11:$AC$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="8FA998"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$12:$AC$12</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A13</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$13:$AC$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$14:$AC$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$15:$AC$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="10"/>
-          <order val="10"/>
-          <tx>
-            <strRef>
-              <f>'Lukáš'!A16</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Lukáš'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Lukáš'!$B$16:$AC$16</f>
-            </numRef>
-          </val>
-        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
         <gapWidth val="55"/>
-        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="minMax"/>
+          <orientation val="maxMin"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr rot="-2700000"/>
+          <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -814,7 +553,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <majorGridlines>
           <spPr>
             <a:ln w="6350">
@@ -864,27 +603,9 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
+        <crosses val="min"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <txPr>
-        <a:bodyPr/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
     <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -935,7 +656,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -963,7 +684,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -991,7 +712,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1019,7 +740,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1047,7 +768,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1075,7 +796,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1103,7 +824,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1131,7 +852,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1159,7 +880,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1187,7 +908,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1215,7 +936,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1524,401 +1245,6 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Won vs. Lost (cumulative)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Veronika'!A26</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Veronika'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Veronika'!$B$26:$AC$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Veronika'!A27</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Veronika'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Veronika'!$B$27:$AC$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="55"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr rot="-2700000"/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <txPr>
-        <a:bodyPr/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Veronika'!$A$29:$A$39</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Veronika'!$AC$29:$AC$39</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
-        <gapWidth val="55"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="maxMin"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="100">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="100">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-        <crosses val="min"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -2319,7 +1645,218 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Won vs. Lost (cumulative)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Veronika'!A26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Veronika'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Veronika'!$B$26:$AC$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Veronika'!A27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="B23B3B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Veronika'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Veronika'!$B$27:$AC$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr rot="-2700000"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -2782,6 +2319,190 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Veronika'!$A$29:$A$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Veronika'!$AC$29:$AC$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="100">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="100">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
@@ -2820,7 +2541,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2848,7 +2569,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2876,7 +2597,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2904,7 +2625,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2932,7 +2653,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2960,7 +2681,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2988,7 +2709,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3016,7 +2737,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3044,7 +2765,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3072,7 +2793,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3100,7 +2821,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3409,612 +3130,6 @@
 </file>
 
 <file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Won vs. Lost (cumulative)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Mykyta'!A26</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Mykyta'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Mykyta'!$B$26:$AC$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Mykyta'!A27</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Mykyta'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Mykyta'!$B$27:$AC$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="55"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr rot="-2700000"/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <txPr>
-        <a:bodyPr/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Won vs. Lost (cumulative)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A26</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$26:$AC$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A27</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$27:$AC$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="55"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr rot="-2700000"/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <txPr>
-        <a:bodyPr/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Mykyta'!$A$29:$A$39</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Mykyta'!$AC$29:$AC$39</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
-        <gapWidth val="55"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="maxMin"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="100">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="100">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-        <crosses val="min"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -4415,7 +3530,619 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Pace to goal – pipeline, Rolling 18, Won and Goal for the full year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A52</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="DCE9F2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2E6F9E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$51:$BB$51</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$52:$BB$52</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="200"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A53</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="C9A227"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C9A227"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C9A227"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$51:$BB$51</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$53:$BB$53</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A54</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="2E6F9E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E6F9E"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2E6F9E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$51:$BB$51</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$54:$BB$54</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A55</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="3D8B58"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3D8B58"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="3D8B58"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$51:$BB$51</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$55:$BB$55</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A56</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="6E8B3D"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$51:$BB$51</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$56:$BB$56</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr rot="-2700000"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="3"/>
+      </catAx>
+      <valAx>
+        <axId val="200"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Weekly change (Kč)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="max"/>
+      </valAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Cumulative value (Kč)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Won vs. Lost (cumulative)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Mykyta'!A26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Mykyta'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mykyta'!$B$26:$AC$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Mykyta'!A27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="B23B3B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Mykyta'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mykyta'!$B$27:$AC$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr rot="-2700000"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -4878,6 +4605,190 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Mykyta'!$A$29:$A$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mykyta'!$AC$29:$AC$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="100">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="100">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
@@ -4916,7 +4827,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4944,7 +4855,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4972,7 +4883,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5000,7 +4911,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5028,7 +4939,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5056,7 +4967,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5084,7 +4995,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5112,7 +5023,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5140,7 +5051,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5168,7 +5079,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5196,7 +5107,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -5505,401 +5416,6 @@
 </file>
 
 <file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Won vs. Lost (cumulative)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Richard'!A26</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Richard'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Richard'!$B$26:$AC$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Richard'!A27</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Richard'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Richard'!$B$27:$AC$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="55"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr rot="-2700000"/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <txPr>
-        <a:bodyPr/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Richard'!$A$29:$A$39</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Richard'!$AC$29:$AC$39</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
-        <gapWidth val="55"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="maxMin"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="100">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="100">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-        <crosses val="min"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -6300,7 +5816,218 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Won vs. Lost (cumulative)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Richard'!A26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Richard'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Richard'!$B$26:$AC$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Richard'!A27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="B23B3B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Richard'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Richard'!$B$27:$AC$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr rot="-2700000"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -6763,6 +6490,190 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Richard'!$A$29:$A$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Richard'!$AC$29:$AC$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="100">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="100">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart29.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
@@ -6801,7 +6712,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6829,7 +6740,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6857,7 +6768,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6885,7 +6796,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6913,7 +6824,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6941,7 +6852,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6969,7 +6880,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6997,7 +6908,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -7025,7 +6936,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -7053,7 +6964,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -7081,7 +6992,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -7244,7 +7155,7 @@
                   <a:srgbClr val="1F2A44"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+              <a:t>Won vs. Lost (cumulative)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -7252,11 +7163,16 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A26</f>
+            </strRef>
+          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="3D8B58"/>
@@ -7268,69 +7184,73 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Martin'!$A$29:$A$39</f>
+              <f>'Martin'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Martin'!$AC$29:$AC$39</f>
+              <f>'Martin'!$B$26:$AC$26</f>
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="B23B3B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$27:$AC$27</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="55"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="maxMin"/>
+          <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="100">
+              <a:defRPr sz="900">
                 <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
+                  <a:srgbClr val="6B7280"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="100">
+            <a:endParaRPr sz="900">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="6B7280"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -7395,9 +7315,27 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
-        <crosses val="min"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+        </a:p>
+      </txPr>
+    </legend>
     <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -7574,401 +7512,6 @@
 </file>
 
 <file path=xl/charts/chart31.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Won vs. Lost (cumulative)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Olda'!A26</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Olda'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Olda'!$B$26:$AC$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Olda'!A27</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Olda'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Olda'!$B$27:$AC$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="55"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr rot="-2700000"/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <txPr>
-        <a:bodyPr/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Olda'!$A$29:$A$39</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Olda'!$AC$29:$AC$39</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
-        <gapWidth val="55"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="maxMin"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="100">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="100">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-        <crosses val="min"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart33.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -8369,7 +7912,218 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Won vs. Lost (cumulative)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Olda'!A26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Olda'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Olda'!$B$26:$AC$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Olda'!A27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="B23B3B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Olda'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Olda'!$B$27:$AC$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr rot="-2700000"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart33.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -8832,6 +8586,190 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Olda'!$A$29:$A$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Olda'!$AC$29:$AC$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="100">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="100">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart35.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
@@ -8870,7 +8808,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -8898,7 +8836,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -8926,7 +8864,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -8954,7 +8892,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -8982,7 +8920,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -9010,7 +8948,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -9038,7 +8976,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -9066,7 +9004,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -9094,7 +9032,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -9122,7 +9060,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -9150,7 +9088,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -9687,190 +9625,6 @@
                   <a:srgbClr val="1F2A44"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Julie'!$A$28:$A$38</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Julie'!$AC$28:$AC$38</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
-        <gapWidth val="55"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="maxMin"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="100">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="100">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-        <crosses val="min"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart39.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
               <a:t>Funnel evolution over time – till end of year (weighted values)</a:t>
             </a:r>
           </a:p>
@@ -10316,6 +10070,190 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart39.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Julie'!$A$28:$A$38</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Julie'!$AC$28:$AC$38</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="100">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="100">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
@@ -10334,7 +10272,7 @@
                   <a:srgbClr val="1F2A44"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Pace to goal – pipeline, Rolling 18, Won and Goal for the full year</a:t>
+              <a:t>Funnel evolution over time – till end of year (weighted values)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -10343,211 +10281,320 @@
     <plotArea>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Martin'!A52</f>
+              <f>'Martin'!A6</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="DCE9F2"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="2E6F9E"/>
-              </a:solidFill>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Martin'!$B$51:$BB$51</f>
+              <f>'Martin'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Martin'!$B$52:$BB$52</f>
+              <f>'Martin'!$B$6:$AC$6</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="55"/>
-        <axId val="10"/>
-        <axId val="200"/>
-      </barChart>
-      <lineChart>
-        <grouping val="standard"/>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Martin'!A53</f>
+              <f>'Martin'!A7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="C9A227"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="C9A227"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="C9A227"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Martin'!$B$51:$BB$51</f>
+              <f>'Martin'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Martin'!$B$53:$BB$53</f>
+              <f>'Martin'!$B$7:$AC$7</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="2"/>
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Martin'!A54</f>
+              <f>'Martin'!A8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="2E6F9E"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="C9A227"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E6F9E"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="2E6F9E"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Martin'!$B$51:$BB$51</f>
+              <f>'Martin'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Martin'!$B$54:$BB$54</f>
+              <f>'Martin'!$B$8:$AC$8</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="3"/>
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Martin'!A55</f>
+              <f>'Martin'!A9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="3D8B58"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="6B4C7A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="3D8B58"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="3D8B58"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Martin'!$B$51:$BB$51</f>
+              <f>'Martin'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Martin'!$B$55:$BB$55</f>
+              <f>'Martin'!$B$9:$AC$9</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="4"/>
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Martin'!A56</f>
+              <f>'Martin'!A10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="6E8B3D"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
+            <a:solidFill>
+              <a:srgbClr val="B23B3B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Martin'!$B$51:$BB$51</f>
+              <f>'Martin'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Martin'!$B$56:$BB$56</f>
+              <f>'Martin'!$B$10:$AC$10</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="5B8FB0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$11:$AC$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="8FA998"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$12:$AC$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="D0A85C"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$13:$AC$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9A7BAD"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$14:$AC$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="C77B7B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$15:$AC$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'Martin'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4C6B8A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$B$16:$AC$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="55"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -10579,61 +10626,14 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
+        <tickLblSkip val="2"/>
       </catAx>
-      <valAx>
-        <axId val="200"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Weekly change (Kč)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-        <crosses val="max"/>
-      </valAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
@@ -10654,7 +10654,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Cumulative value (Kč)</a:t>
+                  <a:t>Kč</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -10755,7 +10755,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -10783,7 +10783,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -10811,7 +10811,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -10839,7 +10839,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -10867,7 +10867,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -10895,7 +10895,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -10923,7 +10923,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -10951,7 +10951,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -10979,7 +10979,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -11007,7 +11007,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -11035,7 +11035,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -11572,190 +11572,6 @@
                   <a:srgbClr val="1F2A44"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Dominika'!$A$28:$A$38</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dominika'!$AC$28:$AC$38</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
-        <gapWidth val="55"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="maxMin"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="100">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="100">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-        <crosses val="min"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart44.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
               <a:t>Funnel evolution over time – till end of year (weighted values)</a:t>
             </a:r>
           </a:p>
@@ -12201,6 +12017,190 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart44.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dominika'!$A$28:$A$38</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dominika'!$AC$28:$AC$38</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="100">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="100">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart45.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
@@ -12239,7 +12239,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12267,7 +12267,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12295,7 +12295,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12323,7 +12323,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12351,7 +12351,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12379,7 +12379,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12407,7 +12407,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12435,7 +12435,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12463,7 +12463,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12491,7 +12491,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12519,7 +12519,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12828,401 +12828,6 @@
 </file>
 
 <file path=xl/charts/chart47.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Won vs. Lost (cumulative)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Aggregation'!A26</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Aggregation'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Aggregation'!$B$26:$AC$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Aggregation'!A27</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Aggregation'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Aggregation'!$B$27:$AC$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="55"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr rot="-2700000"/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <txPr>
-        <a:bodyPr/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart48.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <roundedCorners val="0"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1400" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Aggregation'!$A$29:$A$39</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Aggregation'!$AC$29:$AC$39</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
-        <gapWidth val="55"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="maxMin"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="100">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="100">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:srgbClr val="E3E6EA"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900">
-                <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
-                </a:solidFill>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="900">
-              <a:solidFill>
-                <a:srgbClr val="6B7280"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-        <crosses val="min"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="0"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart49.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -13623,7 +13228,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart48.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -13641,7 +13246,7 @@
                   <a:srgbClr val="1F2A44"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Funnel evolution over time – till end of year (weighted values)</a:t>
+              <a:t>Won vs. Lost (cumulative)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -13656,35 +13261,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Martin'!A6</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$6:$AC$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A7</f>
+              <f>'Aggregation'!A26</f>
             </strRef>
           </tx>
           <spPr>
@@ -13698,77 +13275,21 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
+              <f>'Aggregation'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Martin'!$B$7:$AC$7</f>
+              <f>'Aggregation'!$B$26:$AC$26</f>
             </numRef>
           </val>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="1"/>
+          <order val="1"/>
           <tx>
             <strRef>
-              <f>'Martin'!A8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="C9A227"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$8:$AC$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A9</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$9:$AC$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A10</f>
+              <f>'Aggregation'!A27</f>
             </strRef>
           </tx>
           <spPr>
@@ -13782,180 +13303,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
+              <f>'Aggregation'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Martin'!$B$10:$AC$10</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$11:$AC$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="8FA998"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$12:$AC$12</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A13</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$13:$AC$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$14:$AC$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$15:$AC$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="10"/>
-          <order val="10"/>
-          <tx>
-            <strRef>
-              <f>'Martin'!A16</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Martin'!$B$4:$AC$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Martin'!$B$16:$AC$16</f>
+              <f>'Aggregation'!$B$27:$AC$27</f>
             </numRef>
           </val>
         </ser>
@@ -14086,7 +13439,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart49.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
   <chart>
@@ -14549,6 +13902,374 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Martin'!$A$29:$A$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Martin'!$AC$29:$AC$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="100">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="100">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart50.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D8B58"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Aggregation'!$A$29:$A$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Aggregation'!$AC$29:$AC$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="850" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="1F2A44"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+          <separator val=": "/>
+        </dLbls>
+        <gapWidth val="55"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="100">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="100">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E6EA"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Kč</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="6B7280"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="min"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart51.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
@@ -14587,7 +14308,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14615,7 +14336,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14643,7 +14364,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14671,7 +14392,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14699,7 +14420,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14727,7 +14448,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14755,7 +14476,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14783,7 +14504,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14811,7 +14532,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14839,7 +14560,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -14867,7 +14588,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15045,7 +14766,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Aggregation'!B200</f>
+              <f>'Aggregation'!B138</f>
             </strRef>
           </tx>
           <spPr>
@@ -15059,12 +14780,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Aggregation'!$A$201:$A$208</f>
+              <f>'Aggregation'!$A$139:$A$146</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Aggregation'!$B$201:$B$208</f>
+              <f>'Aggregation'!$B$139:$B$146</f>
             </numRef>
           </val>
         </ser>
@@ -15216,7 +14937,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="6B4C7A"/>
+              <a:srgbClr val="2E6F9E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15244,7 +14965,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="B23B3B"/>
+              <a:srgbClr val="3D8B58"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15272,7 +14993,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="5B8FB0"/>
+              <a:srgbClr val="C9A227"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15300,7 +15021,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8FA998"/>
+              <a:srgbClr val="6B4C7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15328,7 +15049,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D0A85C"/>
+              <a:srgbClr val="B23B3B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15356,7 +15077,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A7BAD"/>
+              <a:srgbClr val="5B8FB0"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15384,7 +15105,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="C77B7B"/>
+              <a:srgbClr val="8FA998"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15412,7 +15133,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4C6B8A"/>
+              <a:srgbClr val="D0A85C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15440,7 +15161,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="7BA88F"/>
+              <a:srgbClr val="9A7BAD"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15468,7 +15189,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6F9E"/>
+              <a:srgbClr val="C77B7B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15496,7 +15217,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="3D8B58"/>
+              <a:srgbClr val="4C6B8A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -16033,7 +15754,7 @@
                   <a:srgbClr val="1F2A44"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Funnel – pipeline breakdown, Rolling 18 (12.07.)</a:t>
+              <a:t>Funnel evolution over time – till end of year (weighted values)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -16041,11 +15762,44 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E6F9E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$6:$AC$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A7</f>
+            </strRef>
+          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="3D8B58"/>
@@ -16057,69 +15811,297 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Lukáš'!$A$28:$A$38</f>
+              <f>'Lukáš'!$B$4:$AC$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lukáš'!$AC$28:$AC$38</f>
+              <f>'Lukáš'!$B$7:$AC$7</f>
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <numFmt formatCode="#,##0&quot; Kč&quot;"/>
-          <txPr>
-            <a:bodyPr/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="850" b="1">
-                  <a:solidFill>
-                    <a:srgbClr val="1F2A44"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-            </a:p>
-          </txPr>
-          <showLegendKey val="0"/>
-          <showVal val="1"/>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-          <separator val=": "/>
-        </dLbls>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="C9A227"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$8:$AC$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="6B4C7A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$9:$AC$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="B23B3B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$10:$AC$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="5B8FB0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$11:$AC$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="8FA998"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$12:$AC$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="D0A85C"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$13:$AC$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9A7BAD"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$14:$AC$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="C77B7B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$15:$AC$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'Lukáš'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4C6B8A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Lukáš'!$B$4:$AC$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lukáš'!$B$16:$AC$16</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="55"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="maxMin"/>
+          <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="100">
+              <a:defRPr sz="900">
                 <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
+                  <a:srgbClr val="6B7280"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="100">
+            <a:endParaRPr sz="900">
               <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
+                <a:srgbClr val="6B7280"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -16184,9 +16166,27 @@
           </a:p>
         </txPr>
         <crossAx val="10"/>
-        <crosses val="min"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+        </a:p>
+      </txPr>
+    </legend>
     <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -16225,12 +16225,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -16249,7 +16249,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -16269,12 +16269,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="5400000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -16293,10 +16293,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>150</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -16313,9 +16313,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -16364,7 +16364,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -16384,12 +16384,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -16408,10 +16408,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -16428,9 +16428,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>143</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -16477,12 +16477,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -16501,7 +16501,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -16521,12 +16521,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="5400000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -16545,10 +16545,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>150</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -16565,9 +16565,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -16614,12 +16614,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -16638,7 +16638,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -16658,12 +16658,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="5400000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -16682,10 +16682,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>150</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -16702,9 +16702,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -16751,12 +16751,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -16775,7 +16775,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -16795,12 +16795,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="5400000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -16819,10 +16819,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>150</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -16839,9 +16839,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -16888,12 +16888,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -16912,7 +16912,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -16932,12 +16932,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="5400000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -16956,10 +16956,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>150</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -16976,9 +16976,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -17027,7 +17027,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -17047,12 +17047,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -17071,10 +17071,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -17091,9 +17091,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>143</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -17142,7 +17142,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -17162,12 +17162,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -17186,10 +17186,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -17206,9 +17206,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>143</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -17255,12 +17255,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3780000"/>
+    <ext cx="9720000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -17279,7 +17279,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -17299,12 +17299,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="5400000"/>
+    <ext cx="9720000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -17323,10 +17323,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>150</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9720000" cy="3960000"/>
+    <ext cx="9720000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -17343,9 +17343,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3960000"/>
@@ -17367,7 +17367,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>199</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9720000" cy="3780000"/>
@@ -22173,7 +22173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB208"/>
+  <dimension ref="A1:BB146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -27159,102 +27159,102 @@
         <v>3830000</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="19" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="19" t="inlineStr">
         <is>
           <t>Sales rep leaderboard (Total Won)</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="20" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
         <is>
           <t>Sales rep</t>
         </is>
       </c>
-      <c r="B200" s="20" t="inlineStr">
+      <c r="B138" s="20" t="inlineStr">
         <is>
           <t>Total Won (Kč)</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="21" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="21" t="inlineStr">
         <is>
           <t>Lukáš</t>
         </is>
       </c>
-      <c r="B201" s="22" t="n">
+      <c r="B139" s="22" t="n">
         <v>797000</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="21" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="21" t="inlineStr">
         <is>
           <t>Veronika</t>
         </is>
       </c>
-      <c r="B202" s="22" t="n">
+      <c r="B140" s="22" t="n">
         <v>565000</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="21" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="21" t="inlineStr">
         <is>
           <t>Mykyta</t>
         </is>
       </c>
-      <c r="B203" s="22" t="n">
+      <c r="B141" s="22" t="n">
         <v>40000</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="21" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="21" t="inlineStr">
         <is>
           <t>Martin</t>
         </is>
       </c>
-      <c r="B204" s="22" t="n">
+      <c r="B142" s="22" t="n">
         <v>29700</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="21" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="21" t="inlineStr">
         <is>
           <t>Richard</t>
         </is>
       </c>
-      <c r="B205" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="21" t="inlineStr">
+      <c r="B143" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="21" t="inlineStr">
         <is>
           <t>Olda</t>
         </is>
       </c>
-      <c r="B206" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="21" t="inlineStr">
+      <c r="B144" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="21" t="inlineStr">
         <is>
           <t>Julie</t>
         </is>
       </c>
-      <c r="B207" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="21" t="inlineStr">
+      <c r="B145" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="21" t="inlineStr">
         <is>
           <t>Dominika</t>
         </is>
       </c>
-      <c r="B208" s="22" t="n">
+      <c r="B146" s="22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -381,21 +381,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -403,18 +388,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -564,21 +549,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -586,18 +556,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -1191,21 +1161,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1213,18 +1168,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -1784,21 +1739,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1806,18 +1746,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -2449,21 +2389,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -2471,18 +2396,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -3076,21 +3001,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -3098,18 +3008,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -4070,21 +3980,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -4092,18 +3987,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -4735,21 +4630,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -4757,18 +4637,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -5362,21 +5242,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -5384,18 +5249,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -5955,21 +5820,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -5977,18 +5827,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -6620,21 +6470,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -6642,18 +6477,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -7276,21 +7111,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -7298,18 +7118,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -7458,21 +7278,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -7480,18 +7285,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -8051,21 +7856,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -8073,18 +7863,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -8716,21 +8506,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -8738,18 +8513,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -9343,21 +9118,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -9365,18 +9125,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -9535,21 +9295,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -9557,18 +9302,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -10200,21 +9945,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -10222,18 +9952,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -11290,21 +11020,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -11312,18 +11027,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -11482,21 +11197,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -11504,18 +11204,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -12147,21 +11847,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -12169,18 +11854,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -12774,21 +12459,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -12796,18 +12466,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -13367,21 +13037,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -13389,18 +13044,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -14032,21 +13687,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -14054,18 +13694,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -14216,21 +13856,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -14238,18 +13863,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -15472,21 +15097,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -15494,18 +15104,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -15664,21 +15274,6 @@
             </a:ln>
           </spPr>
         </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Kč</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="#,##0&quot; Kč&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -15686,18 +15281,18 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900">
+              <a:defRPr sz="100">
                 <a:solidFill>
-                  <a:srgbClr val="6B7280"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="900">
+            <a:endParaRPr sz="100">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -17771,28 +17366,28 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>252845309170</v>
+        <v>402515561715</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>M20-25: Swissborg (Tapix) - deal WON</t>
+          <t>SFF25: Savo digital wallet (Singapore) (Tapix)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>swissborg</t>
+          <t>Savo Inc</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
         <v>46083</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>10</v>
@@ -17829,28 +17424,28 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>11878287315</v>
+        <v>252845309170</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Erste - George use case (Tapix)</t>
+          <t>M20-25: Swissborg (Tapix) - deal WON</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Erste Bank Austria</t>
+          <t>swissborg</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
         <v>46083</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>387000</v>
+        <v>15000</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>10</v>
@@ -17858,16 +17453,16 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>402515561715</v>
+        <v>11878287315</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SFF25: Savo digital wallet (Singapore) (Tapix)</t>
+          <t>Erste - George use case (Tapix)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Savo Inc</t>
+          <t>Erste Bank Austria</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -17879,7 +17474,7 @@
         <v>46083</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>40000</v>
+        <v>387000</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>10</v>
@@ -22694,7 +22289,7 @@
         <v>22970</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>23470</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>23470</v>
@@ -22788,7 +22383,7 @@
         <v>11800</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>11800</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="15" t="n">
         <v>11800</v>
@@ -22976,7 +22571,7 @@
         <v>137310</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>100560</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>100560</v>
@@ -23070,7 +22665,7 @@
         <v>476040</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>499200</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>499200</v>
@@ -23164,7 +22759,7 @@
         <v>414435</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>424435</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>424435</v>
@@ -23258,7 +22853,7 @@
         <v>1750500</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>1669050</v>
+        <v>225000</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>1669050</v>
@@ -23352,7 +22947,7 @@
         <v>509720</v>
       </c>
       <c r="AC13" s="15" t="n">
-        <v>600890</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="15" t="n">
         <v>600890</v>
@@ -23446,7 +23041,7 @@
         <v>38000</v>
       </c>
       <c r="AC14" s="14" t="n">
-        <v>89015</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="14" t="n">
         <v>89015</v>
@@ -23540,7 +23135,7 @@
         <v>118750</v>
       </c>
       <c r="AC15" s="15" t="n">
-        <v>118750</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="15" t="n">
         <v>118750</v>
@@ -23916,7 +23511,7 @@
         <v>4872225</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>4928870</v>
+        <v>1616700</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>4968870</v>
@@ -24010,10 +23605,10 @@
         <v>190000</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>56645</v>
+        <v>-3255525</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>40000</v>
+        <v>3352170</v>
       </c>
     </row>
     <row r="22">
@@ -24104,7 +23699,7 @@
         <v>4209965</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>4329510</v>
+        <v>495000</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>4329510</v>
@@ -24198,10 +23793,10 @@
         <v>276882</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>119545</v>
+        <v>-3714965</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>0</v>
+        <v>3834510</v>
       </c>
     </row>
     <row r="24">
@@ -24762,7 +24357,7 @@
         <v>3477010</v>
       </c>
       <c r="AC29" t="n">
-        <v>3527010</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>3527010</v>
@@ -24856,7 +24451,7 @@
         <v>3212009</v>
       </c>
       <c r="AC30" t="n">
-        <v>3112009</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>3112009</v>
@@ -24950,7 +24545,7 @@
         <v>100000</v>
       </c>
       <c r="AC31" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>100000</v>
@@ -25044,7 +24639,7 @@
         <v>7792010</v>
       </c>
       <c r="AC32" t="n">
-        <v>6497011</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>6497011</v>
@@ -25138,7 +24733,7 @@
         <v>5373100</v>
       </c>
       <c r="AC33" t="n">
-        <v>5566101</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>5566101</v>
@@ -25232,7 +24827,7 @@
         <v>2998175</v>
       </c>
       <c r="AC34" t="n">
-        <v>3148175</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>3148175</v>
@@ -25326,7 +24921,7 @@
         <v>4017750</v>
       </c>
       <c r="AC35" t="n">
-        <v>3936750</v>
+        <v>500000</v>
       </c>
       <c r="AD35" t="n">
         <v>3936750</v>
@@ -25420,7 +25015,7 @@
         <v>776855</v>
       </c>
       <c r="AC36" t="n">
-        <v>878155</v>
+        <v>300000</v>
       </c>
       <c r="AD36" t="n">
         <v>878155</v>
@@ -25514,7 +25109,7 @@
         <v>40000</v>
       </c>
       <c r="AC37" t="n">
-        <v>93700</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>93700</v>
@@ -25608,7 +25203,7 @@
         <v>125000</v>
       </c>
       <c r="AC38" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>125000</v>
@@ -25796,7 +25391,7 @@
         <v>34770</v>
       </c>
       <c r="AC40" t="n">
-        <v>35270</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>35270</v>
@@ -25890,7 +25485,7 @@
         <v>32120</v>
       </c>
       <c r="AC41" t="n">
-        <v>31120</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>31120</v>
@@ -25984,7 +25579,7 @@
         <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>1000</v>
@@ -26078,7 +25673,7 @@
         <v>233760</v>
       </c>
       <c r="AC43" t="n">
-        <v>194910</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>194910</v>
@@ -26172,7 +25767,7 @@
         <v>644772</v>
       </c>
       <c r="AC44" t="n">
-        <v>667932</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>667932</v>
@@ -26266,7 +25861,7 @@
         <v>599635</v>
       </c>
       <c r="AC45" t="n">
-        <v>629635</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>629635</v>
@@ -26360,7 +25955,7 @@
         <v>1807988</v>
       </c>
       <c r="AC46" t="n">
-        <v>1771538</v>
+        <v>225000</v>
       </c>
       <c r="AD46" t="n">
         <v>1771538</v>
@@ -26454,7 +26049,7 @@
         <v>699170</v>
       </c>
       <c r="AC47" t="n">
-        <v>790340</v>
+        <v>270000</v>
       </c>
       <c r="AD47" t="n">
         <v>790340</v>
@@ -26548,7 +26143,7 @@
         <v>38000</v>
       </c>
       <c r="AC48" t="n">
-        <v>89015</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>89015</v>
@@ -26642,7 +26237,7 @@
         <v>118750</v>
       </c>
       <c r="AC49" t="n">
-        <v>118750</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>118750</v>
@@ -26996,10 +26591,10 @@
         <v>276882</v>
       </c>
       <c r="AC52" t="n">
-        <v>119545</v>
+        <v>-3714965</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3834510</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -27090,7 +26685,7 @@
         <v>4872225</v>
       </c>
       <c r="AC53" t="n">
-        <v>4928870</v>
+        <v>1616700</v>
       </c>
       <c r="AD53" t="n">
         <v>4968870</v>
@@ -27184,7 +26779,7 @@
         <v>4209965</v>
       </c>
       <c r="AC54" t="n">
-        <v>4329510</v>
+        <v>495000</v>
       </c>
       <c r="AD54" t="n">
         <v>4329510</v>
@@ -27955,7 +27550,7 @@
         <v>50000</v>
       </c>
       <c r="AC7" s="25" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="25" t="n">
         <v>50000</v>
@@ -28143,7 +27738,7 @@
         <v>1860000</v>
       </c>
       <c r="AC9" s="25" t="n">
-        <v>1860000</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="25" t="n">
         <v>1860000</v>
@@ -28237,7 +27832,7 @@
         <v>2902000</v>
       </c>
       <c r="AC10" s="25" t="n">
-        <v>2532000</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="25" t="n">
         <v>2532000</v>
@@ -28331,7 +27926,7 @@
         <v>850000</v>
       </c>
       <c r="AC11" s="25" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="25" t="n">
         <v>750000</v>
@@ -28425,7 +28020,7 @@
         <v>2643000</v>
       </c>
       <c r="AC12" s="25" t="n">
-        <v>2362000</v>
+        <v>500000</v>
       </c>
       <c r="AD12" s="25" t="n">
         <v>2362000</v>
@@ -28519,7 +28114,7 @@
         <v>454255</v>
       </c>
       <c r="AC13" s="25" t="n">
-        <v>555555</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="25" t="n">
         <v>555555</v>
@@ -28613,7 +28208,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="25" t="n">
-        <v>93700</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="25" t="n">
         <v>93700</v>
@@ -29054,7 +28649,7 @@
         <v>2137000</v>
       </c>
       <c r="AC20" s="25" t="n">
-        <v>2137000</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="25" t="n">
         <v>2137000</v>
@@ -29148,7 +28743,7 @@
         <v>350000</v>
       </c>
       <c r="AC21" s="25" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="25" t="n">
         <v>350000</v>
@@ -29336,7 +28931,7 @@
         <v>277002</v>
       </c>
       <c r="AC23" s="25" t="n">
-        <v>277002</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="25" t="n">
         <v>277002</v>
@@ -29524,7 +29119,7 @@
         <v>28000</v>
       </c>
       <c r="AC25" s="25" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="AD25" s="25" t="n">
         <v>28000</v>
@@ -29618,7 +29213,7 @@
         <v>200000</v>
       </c>
       <c r="AC26" s="25" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="25" t="n">
         <v>200000</v>
@@ -29900,7 +29495,7 @@
         <v>100000</v>
       </c>
       <c r="AC29" s="25" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD29" s="25" t="n">
         <v>100000</v>
@@ -30247,7 +29842,7 @@
         <v>60010</v>
       </c>
       <c r="AC34" s="25" t="n">
-        <v>60010</v>
+        <v>0</v>
       </c>
       <c r="AD34" s="25" t="n">
         <v>60010</v>
@@ -30341,7 +29936,7 @@
         <v>80008</v>
       </c>
       <c r="AC35" s="25" t="n">
-        <v>80008</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="25" t="n">
         <v>80008</v>
@@ -30529,7 +30124,7 @@
         <v>140005</v>
       </c>
       <c r="AC37" s="25" t="n">
-        <v>90006</v>
+        <v>0</v>
       </c>
       <c r="AD37" s="25" t="n">
         <v>90006</v>
@@ -30623,7 +30218,7 @@
         <v>105000</v>
       </c>
       <c r="AC38" s="25" t="n">
-        <v>158000</v>
+        <v>0</v>
       </c>
       <c r="AD38" s="25" t="n">
         <v>158000</v>
@@ -30717,7 +30312,7 @@
         <v>744175</v>
       </c>
       <c r="AC39" s="25" t="n">
-        <v>744175</v>
+        <v>0</v>
       </c>
       <c r="AD39" s="25" t="n">
         <v>744175</v>
@@ -30811,7 +30406,7 @@
         <v>700000</v>
       </c>
       <c r="AC40" s="25" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="AD40" s="25" t="n">
         <v>700000</v>
@@ -31093,7 +30688,7 @@
         <v>25000</v>
       </c>
       <c r="AC43" s="25" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AD43" s="25" t="n">
         <v>25000</v>
@@ -31816,7 +31411,7 @@
         <v>160000</v>
       </c>
       <c r="AC52" s="25" t="n">
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="AD52" s="25" t="n">
         <v>160000</v>
@@ -31910,7 +31505,7 @@
         <v>35000</v>
       </c>
       <c r="AC53" s="25" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="AD53" s="25" t="n">
         <v>35000</v>
@@ -32004,7 +31599,7 @@
         <v>194000</v>
       </c>
       <c r="AC54" s="25" t="n">
-        <v>194000</v>
+        <v>0</v>
       </c>
       <c r="AD54" s="25" t="n">
         <v>194000</v>
@@ -32098,7 +31693,7 @@
         <v>68000</v>
       </c>
       <c r="AC55" s="25" t="n">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="AD55" s="25" t="n">
         <v>68000</v>
@@ -33009,7 +32604,7 @@
         <v>600000</v>
       </c>
       <c r="AC66" s="25" t="n">
-        <v>600001</v>
+        <v>0</v>
       </c>
       <c r="AD66" s="25" t="n">
         <v>600001</v>
@@ -33103,7 +32698,7 @@
         <v>38000</v>
       </c>
       <c r="AC67" s="25" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="AD67" s="25" t="n">
         <v>38000</v>
@@ -33197,7 +32792,7 @@
         <v>153000</v>
       </c>
       <c r="AC68" s="25" t="n">
-        <v>153000</v>
+        <v>0</v>
       </c>
       <c r="AD68" s="25" t="n">
         <v>153000</v>
@@ -33291,7 +32886,7 @@
         <v>44100</v>
       </c>
       <c r="AC69" s="25" t="n">
-        <v>44100</v>
+        <v>0</v>
       </c>
       <c r="AD69" s="25" t="n">
         <v>44100</v>
@@ -33826,7 +33421,7 @@
         <v>100000</v>
       </c>
       <c r="AC76" s="25" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="AD76" s="25" t="n">
         <v>150000</v>
@@ -33920,7 +33515,7 @@
         <v>700000</v>
       </c>
       <c r="AC77" s="25" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="AD77" s="25" t="n">
         <v>700000</v>
@@ -34108,7 +33703,7 @@
         <v>2300000</v>
       </c>
       <c r="AC79" s="25" t="n">
-        <v>1125000</v>
+        <v>0</v>
       </c>
       <c r="AD79" s="25" t="n">
         <v>1125000</v>
@@ -34202,7 +33797,7 @@
         <v>200000</v>
       </c>
       <c r="AC80" s="25" t="n">
-        <v>710000</v>
+        <v>0</v>
       </c>
       <c r="AD80" s="25" t="n">
         <v>710000</v>
@@ -34296,7 +33891,7 @@
         <v>300000</v>
       </c>
       <c r="AC81" s="25" t="n">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="AD81" s="25" t="n">
         <v>450000</v>
@@ -34390,7 +33985,7 @@
         <v>0</v>
       </c>
       <c r="AC82" s="25" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD82" s="25" t="n">
         <v>100000</v>
@@ -35489,7 +35084,7 @@
         <v>77000</v>
       </c>
       <c r="AC95" s="25" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="AD95" s="25" t="n">
         <v>77000</v>
@@ -37469,7 +37064,7 @@
         <v>75000</v>
       </c>
       <c r="AC6" s="25" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="25" t="n">
         <v>75000</v>
@@ -37563,7 +37158,7 @@
         <v>250000</v>
       </c>
       <c r="AC7" s="25" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="25" t="n">
         <v>150000</v>
@@ -37657,7 +37252,7 @@
         <v>0</v>
       </c>
       <c r="AC8" s="25" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="25" t="n">
         <v>100000</v>
@@ -37751,7 +37346,7 @@
         <v>3010000</v>
       </c>
       <c r="AC9" s="25" t="n">
-        <v>2910000</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="25" t="n">
         <v>2910000</v>
@@ -37845,7 +37440,7 @@
         <v>3027000</v>
       </c>
       <c r="AC10" s="25" t="n">
-        <v>2657000</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="25" t="n">
         <v>2657000</v>
@@ -37939,7 +37534,7 @@
         <v>1078000</v>
       </c>
       <c r="AC11" s="25" t="n">
-        <v>1078000</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="25" t="n">
         <v>1078000</v>
@@ -38033,7 +37628,7 @@
         <v>2643000</v>
       </c>
       <c r="AC12" s="25" t="n">
-        <v>2462000</v>
+        <v>500000</v>
       </c>
       <c r="AD12" s="25" t="n">
         <v>2462000</v>
@@ -38127,7 +37722,7 @@
         <v>578755</v>
       </c>
       <c r="AC13" s="25" t="n">
-        <v>680055</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="25" t="n">
         <v>680055</v>
@@ -38221,7 +37816,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="25" t="n">
-        <v>93700</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="25" t="n">
         <v>93700</v>
@@ -38662,7 +38257,7 @@
         <v>2137000</v>
       </c>
       <c r="AC20" s="25" t="n">
-        <v>2137000</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="25" t="n">
         <v>2137000</v>
@@ -38756,7 +38351,7 @@
         <v>350000</v>
       </c>
       <c r="AC21" s="25" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="25" t="n">
         <v>350000</v>
@@ -38944,7 +38539,7 @@
         <v>277002</v>
       </c>
       <c r="AC23" s="25" t="n">
-        <v>277002</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="25" t="n">
         <v>277002</v>
@@ -39132,7 +38727,7 @@
         <v>78000</v>
       </c>
       <c r="AC25" s="25" t="n">
-        <v>78000</v>
+        <v>0</v>
       </c>
       <c r="AD25" s="25" t="n">
         <v>78000</v>
@@ -39226,7 +38821,7 @@
         <v>200000</v>
       </c>
       <c r="AC26" s="25" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="25" t="n">
         <v>200000</v>
@@ -39320,7 +38915,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="25" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="AD27" s="25" t="n">
         <v>0</v>
@@ -39508,7 +39103,7 @@
         <v>100000</v>
       </c>
       <c r="AC29" s="25" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD29" s="25" t="n">
         <v>100000</v>
@@ -39855,7 +39450,7 @@
         <v>560010</v>
       </c>
       <c r="AC34" s="25" t="n">
-        <v>560010</v>
+        <v>0</v>
       </c>
       <c r="AD34" s="25" t="n">
         <v>560010</v>
@@ -39949,7 +39544,7 @@
         <v>280009</v>
       </c>
       <c r="AC35" s="25" t="n">
-        <v>280009</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="25" t="n">
         <v>280009</v>
@@ -40137,7 +39732,7 @@
         <v>965008</v>
       </c>
       <c r="AC37" s="25" t="n">
-        <v>915009</v>
+        <v>0</v>
       </c>
       <c r="AD37" s="25" t="n">
         <v>915009</v>
@@ -40231,7 +39826,7 @@
         <v>1196100</v>
       </c>
       <c r="AC38" s="25" t="n">
-        <v>1249100</v>
+        <v>0</v>
       </c>
       <c r="AD38" s="25" t="n">
         <v>1249100</v>
@@ -40325,7 +39920,7 @@
         <v>1044175</v>
       </c>
       <c r="AC39" s="25" t="n">
-        <v>1044175</v>
+        <v>0</v>
       </c>
       <c r="AD39" s="25" t="n">
         <v>1044175</v>
@@ -40419,7 +40014,7 @@
         <v>827750</v>
       </c>
       <c r="AC40" s="25" t="n">
-        <v>827750</v>
+        <v>0</v>
       </c>
       <c r="AD40" s="25" t="n">
         <v>827750</v>
@@ -40513,7 +40108,7 @@
         <v>86000</v>
       </c>
       <c r="AC41" s="25" t="n">
-        <v>86000</v>
+        <v>0</v>
       </c>
       <c r="AD41" s="25" t="n">
         <v>86000</v>
@@ -40701,7 +40296,7 @@
         <v>25000</v>
       </c>
       <c r="AC43" s="25" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AD43" s="25" t="n">
         <v>25000</v>
@@ -41424,7 +41019,7 @@
         <v>220000</v>
       </c>
       <c r="AC52" s="25" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="AD52" s="25" t="n">
         <v>220000</v>
@@ -41518,7 +41113,7 @@
         <v>35000</v>
       </c>
       <c r="AC53" s="25" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="AD53" s="25" t="n">
         <v>35000</v>
@@ -41612,7 +41207,7 @@
         <v>194000</v>
       </c>
       <c r="AC54" s="25" t="n">
-        <v>194000</v>
+        <v>0</v>
       </c>
       <c r="AD54" s="25" t="n">
         <v>194000</v>
@@ -41706,7 +41301,7 @@
         <v>68000</v>
       </c>
       <c r="AC55" s="25" t="n">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="AD55" s="25" t="n">
         <v>68000</v>
@@ -42241,7 +41836,7 @@
         <v>605000</v>
       </c>
       <c r="AC62" s="25" t="n">
-        <v>605000</v>
+        <v>0</v>
       </c>
       <c r="AD62" s="25" t="n">
         <v>605000</v>
@@ -42335,7 +41930,7 @@
         <v>1632000</v>
       </c>
       <c r="AC63" s="25" t="n">
-        <v>1632000</v>
+        <v>0</v>
       </c>
       <c r="AD63" s="25" t="n">
         <v>1632000</v>
@@ -42523,7 +42118,7 @@
         <v>1090000</v>
       </c>
       <c r="AC65" s="25" t="n">
-        <v>1090000</v>
+        <v>0</v>
       </c>
       <c r="AD65" s="25" t="n">
         <v>1090000</v>
@@ -42617,7 +42212,7 @@
         <v>630000</v>
       </c>
       <c r="AC66" s="25" t="n">
-        <v>630001</v>
+        <v>0</v>
       </c>
       <c r="AD66" s="25" t="n">
         <v>630001</v>
@@ -42711,7 +42306,7 @@
         <v>386000</v>
       </c>
       <c r="AC67" s="25" t="n">
-        <v>386000</v>
+        <v>0</v>
       </c>
       <c r="AD67" s="25" t="n">
         <v>386000</v>
@@ -42805,7 +42400,7 @@
         <v>153000</v>
       </c>
       <c r="AC68" s="25" t="n">
-        <v>153000</v>
+        <v>0</v>
       </c>
       <c r="AD68" s="25" t="n">
         <v>153000</v>
@@ -42899,7 +42494,7 @@
         <v>44100</v>
       </c>
       <c r="AC69" s="25" t="n">
-        <v>44100</v>
+        <v>0</v>
       </c>
       <c r="AD69" s="25" t="n">
         <v>44100</v>
@@ -43434,7 +43029,7 @@
         <v>100000</v>
       </c>
       <c r="AC76" s="25" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="AD76" s="25" t="n">
         <v>150000</v>
@@ -43528,7 +43123,7 @@
         <v>700000</v>
       </c>
       <c r="AC77" s="25" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="AD77" s="25" t="n">
         <v>700000</v>
@@ -43716,7 +43311,7 @@
         <v>2300000</v>
       </c>
       <c r="AC79" s="25" t="n">
-        <v>1125000</v>
+        <v>0</v>
       </c>
       <c r="AD79" s="25" t="n">
         <v>1125000</v>
@@ -43810,7 +43405,7 @@
         <v>200000</v>
       </c>
       <c r="AC80" s="25" t="n">
-        <v>710000</v>
+        <v>0</v>
       </c>
       <c r="AD80" s="25" t="n">
         <v>710000</v>
@@ -43904,7 +43499,7 @@
         <v>300000</v>
       </c>
       <c r="AC81" s="25" t="n">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="AD81" s="25" t="n">
         <v>450000</v>
@@ -43998,7 +43593,7 @@
         <v>0</v>
       </c>
       <c r="AC82" s="25" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD82" s="25" t="n">
         <v>100000</v>
@@ -44909,7 +44504,7 @@
         <v>150000</v>
       </c>
       <c r="AC93" s="25" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="AD93" s="25" t="n">
         <v>180000</v>
@@ -45003,7 +44598,7 @@
         <v>100000</v>
       </c>
       <c r="AC94" s="25" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD94" s="25" t="n">
         <v>100000</v>
@@ -45097,7 +44692,7 @@
         <v>77000</v>
       </c>
       <c r="AC95" s="25" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="AD95" s="25" t="n">
         <v>77000</v>
@@ -46846,16 +46441,16 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>217669364924</v>
+        <v>10429685209</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Burgan Bank - HPS</t>
+          <t>Trinity Bank</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Burgan Bank</t>
+          <t>TRINITY BANK a.s.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -46867,7 +46462,7 @@
         <v>46027</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>150000</v>
+        <v>28000</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>2</v>
@@ -46875,16 +46470,16 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>245983710407</v>
+        <v>14758904767</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Erste Bank Hungary - RPI</t>
+          <t>TBI Bank</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Erste Bank Hungary</t>
+          <t>TBI Bank</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -46896,7 +46491,7 @@
         <v>46027</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>2</v>
@@ -46904,16 +46499,16 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>246885009623</v>
+        <v>172443988194</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Source: Unchain2025; Company: Payall Payment Systems, Inc.</t>
+          <t>OTP banka Srbija - New Deal</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Payall Payment Systems</t>
+          <t>OTP Serbia (RS)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -46925,7 +46520,7 @@
         <v>46027</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>2</v>
@@ -46933,16 +46528,16 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>167910650045</v>
+        <v>217669364924</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Raiffeisenbank Hrvatska</t>
+          <t>Burgan Bank - HPS</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Raiffeisenbank Hrvatska (HR)</t>
+          <t>Burgan Bank</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -46954,7 +46549,7 @@
         <v>46027</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>2</v>
@@ -46962,16 +46557,16 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>10429685209</v>
+        <v>245983710407</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Trinity Bank</t>
+          <t>Erste Bank Hungary - RPI</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>TRINITY BANK a.s.</t>
+          <t>Erste Bank Hungary</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -46983,7 +46578,7 @@
         <v>46027</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>28000</v>
+        <v>50000</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>2</v>
@@ -46991,15 +46586,17 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>251389531345</v>
+        <v>246885009623</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ukrgasbank, woodpecker</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v/>
+          <t>Source: Unchain2025; Company: Payall Payment Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Payall Payment Systems</t>
+        </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -47018,16 +46615,16 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>10595004131</v>
+        <v>167910650045</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Contact Form: Arab Bank: Mahmoud Zainab</t>
+          <t>Source: Linkedin; Company: Raiffeisenbank Hrvatska</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arab Bank </t>
+          <t>Raiffeisenbank Hrvatska (HR)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -47039,7 +46636,7 @@
         <v>46027</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>2</v>
@@ -47047,17 +46644,15 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>172443992264</v>
+        <v>251389531345</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Addiko Bank a.d. Beograd - New Deal</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Addiko Bank a.d. Beograd</t>
-        </is>
+          <t>Ukrgasbank, woodpecker</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v/>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -47068,7 +46663,7 @@
         <v>46027</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>2</v>
@@ -47076,16 +46671,16 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>248392796383</v>
+        <v>10595004131</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Source: Unchain2025; Company: Banca Transilvania</t>
+          <t>Contact Form: Arab Bank: Mahmoud Zainab</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Banca Transilvania</t>
+          <t xml:space="preserve">Arab Bank </t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -47097,7 +46692,7 @@
         <v>46027</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>2</v>
@@ -47105,16 +46700,16 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>14758904767</v>
+        <v>172443992264</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TBI Bank</t>
+          <t>Addiko Bank a.d. Beograd - New Deal</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>TBI Bank</t>
+          <t>Addiko Bank a.d. Beograd</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -47126,7 +46721,7 @@
         <v>46027</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>2</v>
@@ -47134,16 +46729,16 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>172443988194</v>
+        <v>248392796383</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>OTP banka Srbija - New Deal</t>
+          <t>Source: Unchain2025; Company: Banca Transilvania</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>OTP Serbia (RS)</t>
+          <t>Banca Transilvania</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -47155,7 +46750,7 @@
         <v>46027</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>2</v>
@@ -47453,16 +47048,16 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>426352077012</v>
+        <v>23044845781</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>M20-25: PayPo (Tapix)</t>
+          <t>Montenegro: CKB bank</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>PayPo</t>
+          <t>CKB bank</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -47474,7 +47069,7 @@
         <v>46035</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>53000</v>
+        <v>0</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>3</v>
@@ -47482,16 +47077,16 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>145158419661</v>
+        <v>426352077012</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: OTP banka, Slovenija</t>
+          <t>M20-25: PayPo (Tapix)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>OTP banka, Slovenija (SI)</t>
+          <t>PayPo</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -47503,7 +47098,7 @@
         <v>46035</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>3</v>
@@ -47511,16 +47106,16 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>15154900711</v>
+        <v>145158419661</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Source: Unchain2024; Company: Exim Banca Romaneasca</t>
+          <t>Source: Linkedin; Company: OTP banka, Slovenija</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Exim Banca Romaneasca</t>
+          <t>OTP banka, Slovenija (SI)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -47540,16 +47135,16 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>14723060424</v>
+        <v>15154900711</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Source: M24; MAIB</t>
+          <t>Source: Unchain2024; Company: Exim Banca Romaneasca</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>maib</t>
+          <t>Exim Banca Romaneasca</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -47561,7 +47156,7 @@
         <v>46035</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>3</v>
@@ -47569,16 +47164,16 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>23044845781</v>
+        <v>14723060424</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Montenegro: CKB bank</t>
+          <t>Source: M24; MAIB</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>CKB bank</t>
+          <t>maib</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -47590,7 +47185,7 @@
         <v>46035</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>3</v>
@@ -48033,28 +47628,26 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>372346793179</v>
+        <v>459214664945</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Jeeves: Douglas Germano - contact form (Tapix)</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Jeeves</t>
-        </is>
+          <t>: haden tours - contact form</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v/>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
         <v>46058</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>6</v>
@@ -48062,26 +47655,28 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>459214664945</v>
+        <v>372346793179</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>: haden tours - contact form</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v/>
+          <t>Jeeves: Douglas Germano - contact form (Tapix)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Jeeves</t>
+        </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
         <v>46058</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>6</v>
@@ -48321,16 +47916,16 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>403286462680</v>
+        <v>327181890750</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Dating Central Europe Zrt.: Daniel Farkas - contact form</t>
+          <t>: Amy Allen - contact form</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Dating Central Europe</t>
+          <t>Institute of Commercial Payments</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -48350,16 +47945,16 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>335122949315</v>
+        <v>403286462680</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Steyler Ethik Bank, woodpecker</t>
+          <t>Dating Central Europe Zrt.: Daniel Farkas - contact form</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Steyler Ethik Bank</t>
+          <t>Dating Central Europe</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -48379,16 +47974,16 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>161176459492</v>
+        <v>335122949315</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Bybit</t>
+          <t>Steyler Ethik Bank, woodpecker</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Steyler Ethik Bank</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -48408,16 +48003,16 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>445839426798</v>
+        <v>161176459492</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>MOBILE WALLET INTERNATIONAL "MWI": Gerald Chenyi - contact form</t>
+          <t>Source: Linkedin; Company: Bybit</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>MOBILE WALLET INTERNATIONAL "MWI"</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -48437,16 +48032,16 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>305946307801</v>
+        <v>445839426798</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>us.quinteft.com: Swami Bhaskaran - contact form</t>
+          <t>MOBILE WALLET INTERNATIONAL "MWI": Gerald Chenyi - contact form</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>us.quinteft.com</t>
+          <t>MOBILE WALLET INTERNATIONAL "MWI"</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -48466,16 +48061,16 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>451908503776</v>
+        <v>305946307801</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>PaymentRush: Payrush Payrush - contact form</t>
+          <t>us.quinteft.com: Swami Bhaskaran - contact form</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>PaymentRush</t>
+          <t>us.quinteft.com</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -48495,16 +48090,16 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>410288932066</v>
+        <v>451908503776</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>ISI Markets: Irina Faizova - contact form</t>
+          <t>PaymentRush: Payrush Payrush - contact form</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>ISI Markets</t>
+          <t>PaymentRush</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -48524,16 +48119,16 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>327181890750</v>
+        <v>410288932066</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>: Amy Allen - contact form</t>
+          <t>ISI Markets: Irina Faizova - contact form</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Institute of Commercial Payments</t>
+          <t>ISI Markets</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -49771,16 +49366,16 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
-        <v>497781911744</v>
+        <v>167867497663</v>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Logicom Public - New Deal</t>
+          <t>UniCredit Bank Serbia</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Logicom Public</t>
+          <t>UniCredit Bank Serbia</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -49792,7 +49387,7 @@
         <v>46122</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>1</v>
+        <v>150000</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>15</v>
@@ -49800,21 +49395,21 @@
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
-        <v>400708664525</v>
+        <v>276512884926</v>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>instashopify.com: Imran Khan - contact form</t>
+          <t>NORD/LB, woodpecker</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>instashopify</t>
+          <t>NORD/LB</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -49829,21 +49424,21 @@
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
-        <v>286785856703</v>
+        <v>131338994917</v>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB - Norddeutsche Landesbank Girozentrale, woodpecker</t>
+          <t>BCR - client labeling</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB - Norddeutsche Landesbank Girozentrale</t>
+          <t>BCR</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -49858,16 +49453,16 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
-        <v>141989380324</v>
+        <v>497781911744</v>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Thales - New Deal</t>
+          <t>Logicom Public - New Deal</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Logicom Public</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -49879,7 +49474,7 @@
         <v>46122</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>15</v>
@@ -49887,21 +49482,21 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
-        <v>276545506529</v>
+        <v>400708664525</v>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>ING: Maarten Driessen - contact form</t>
+          <t>instashopify.com: Imran Khan - contact form</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>instashopify</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -49916,21 +49511,21 @@
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
-        <v>172850432214</v>
+        <v>286785856703</v>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Garanti BBVA</t>
+          <t>NORD/LB - Norddeutsche Landesbank Girozentrale, woodpecker</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Garanti BBVA ROMANIA (RBI now)</t>
+          <t>NORD/LB - Norddeutsche Landesbank Girozentrale</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -49945,15 +49540,17 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
-        <v>467637772510</v>
+        <v>141989380324</v>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>, woodpecker</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="n">
-        <v/>
+          <t>Thales - New Deal</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Thales</t>
+        </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
@@ -49964,7 +49561,7 @@
         <v>46122</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>15</v>
@@ -49972,28 +49569,28 @@
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
-        <v>498502569192</v>
+        <v>276545506529</v>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Arkam Partnership</t>
+          <t>ING: Maarten Driessen - contact form</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Arkamtec</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>15</v>
@@ -50001,16 +49598,16 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
-        <v>131338994917</v>
+        <v>172850432214</v>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>BCR - client labeling</t>
+          <t>Source: Linkedin; Company: Garanti BBVA</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>BCR</t>
+          <t>Garanti BBVA ROMANIA (RBI now)</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -50030,17 +49627,15 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
-        <v>469739059449</v>
+        <v>467637772510</v>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Zapad banka AD Podgorica, woodpecker</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>Zapad banka AD Podgorica</t>
-        </is>
+          <t>, woodpecker</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v/>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
@@ -50059,28 +49654,28 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
-        <v>167867497663</v>
+        <v>498502569192</v>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>UniCredit Bank Serbia</t>
+          <t>Arkam Partnership</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>UniCredit Bank Serbia</t>
+          <t>Arkamtec</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>150000</v>
+        <v>1</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>15</v>
@@ -50088,16 +49683,16 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
-        <v>311084966087</v>
+        <v>469739059449</v>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Mastercard Slovenia</t>
+          <t>Zapad banka AD Podgorica, woodpecker</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Mastercard Europe</t>
+          <t>Zapad banka AD Podgorica</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -50117,16 +49712,16 @@
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
-        <v>309831687359</v>
+        <v>311084966087</v>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABS: ING Poland </t>
+          <t>Mastercard Slovenia</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>ING Poland</t>
+          <t>Mastercard Europe</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -50146,16 +49741,16 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
-        <v>445970439384</v>
+        <v>309831687359</v>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Conference: Verestro (Partnership)</t>
+          <t xml:space="preserve">ABS: ING Poland </t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Verestro</t>
+          <t>ING Poland</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -50175,28 +49770,28 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
-        <v>309710516429</v>
+        <v>445970439384</v>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Holvi - od Martina (Tapix)</t>
+          <t>Conference: Verestro (Partnership)</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Holvi</t>
+          <t>Verestro</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>67500</v>
+        <v>0</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>15</v>
@@ -50204,28 +49799,28 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
-        <v>365136108758</v>
+        <v>309710516429</v>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>WFW25 - Nest2M - Turkey partnership</t>
+          <t>Holvi - od Martina (Tapix)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Nest2Move</t>
+          <t>Holvi</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>1</v>
+        <v>67500</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>15</v>
@@ -50233,26 +49828,28 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
-        <v>467713169640</v>
+        <v>365136108758</v>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>, woodpecker</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v/>
+          <t>WFW25 - Nest2M - Turkey partnership</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Nest2Move</t>
+        </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>15</v>
@@ -50260,17 +49857,15 @@
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
-        <v>276512884926</v>
+        <v>467713169640</v>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB, woodpecker</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>NORD/LB</t>
-        </is>
+          <t>, woodpecker</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v/>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
@@ -52232,16 +51827,16 @@
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
-        <v>237657578687</v>
+        <v>274486206684</v>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>M20-25: Xapo Bank - business</t>
+          <t>ABS: Barclays UK (Tapix)</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Xapo Bank</t>
+          <t>Barclays UK</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -52253,7 +51848,7 @@
         <v>46164</v>
       </c>
       <c r="F191" s="6" t="n">
-        <v>0</v>
+        <v>617000</v>
       </c>
       <c r="G191" s="7" t="n">
         <v>21</v>
@@ -52261,16 +51856,16 @@
     </row>
     <row r="192">
       <c r="A192" s="4" t="n">
-        <v>274486206684</v>
+        <v>237657578687</v>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>ABS: Barclays UK (Tapix)</t>
+          <t>M20-25: Xapo Bank - business</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Barclays UK</t>
+          <t>Xapo Bank</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -52282,7 +51877,7 @@
         <v>46164</v>
       </c>
       <c r="F192" s="6" t="n">
-        <v>617000</v>
+        <v>0</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>21</v>
@@ -52667,28 +52262,28 @@
     </row>
     <row r="206">
       <c r="A206" s="4" t="n">
-        <v>444142278902</v>
+        <v>497719804091</v>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>ABS: Santander Bank Polska (Tapix)</t>
+          <t>Pay360: allpay Limited</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Santander Bank PL</t>
+          <t>allpay Limited</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
         <v>46170</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>22</v>
@@ -52696,28 +52291,28 @@
     </row>
     <row r="207">
       <c r="A207" s="4" t="n">
-        <v>497719804091</v>
+        <v>444142278902</v>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Pay360: allpay Limited</t>
+          <t>ABS: Santander Bank Polska (Tapix)</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>allpay Limited</t>
+          <t>Santander Bank PL</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">
         <v>46170</v>
       </c>
       <c r="F207" s="6" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G207" s="7" t="n">
         <v>22</v>
@@ -52812,16 +52407,16 @@
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
-        <v>273762210003</v>
+        <v>90309296366</v>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>N26, woodpecker</t>
+          <t>FintechConnect24: Mano.bank</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>N26</t>
+          <t>Mano.bank</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -52833,7 +52428,7 @@
         <v>46184</v>
       </c>
       <c r="F211" s="6" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G211" s="7" t="n">
         <v>24</v>
@@ -52841,19 +52436,21 @@
     </row>
     <row r="212">
       <c r="A212" s="4" t="n">
-        <v>505781803242</v>
+        <v>200712206579</v>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Kuwait Finance House: Abdulrahman M Alsaqran - contact form</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="n">
-        <v/>
+          <t>INTELICA CONSULTING: Meiker Lazo - contact form</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>INTELICA CONSULTING</t>
+        </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">
@@ -52868,16 +52465,16 @@
     </row>
     <row r="213">
       <c r="A213" s="4" t="n">
-        <v>43653769413</v>
+        <v>273762210003</v>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Uniglobal 24: Volksbank Wien</t>
+          <t>N26, woodpecker</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Volksbank Wien</t>
+          <t>N26</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -52889,7 +52486,7 @@
         <v>46184</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G213" s="7" t="n">
         <v>24</v>
@@ -52897,28 +52494,26 @@
     </row>
     <row r="214">
       <c r="A214" s="4" t="n">
-        <v>78258022608</v>
+        <v>505781803242</v>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>FintechConnect24: Luzerner Kantonalbank</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>Luzerner Kantonalbank</t>
-        </is>
+          <t>Kuwait Finance House: Abdulrahman M Alsaqran - contact form</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="n">
+        <v/>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G214" s="7" t="n">
         <v>24</v>
@@ -52926,16 +52521,16 @@
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
-        <v>285394684142</v>
+        <v>43653769413</v>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>N26 - RPI (Tapix)</t>
+          <t>Uniglobal 24: Volksbank Wien</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>N26</t>
+          <t>Volksbank Wien</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -52947,7 +52542,7 @@
         <v>46184</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>81000</v>
+        <v>1</v>
       </c>
       <c r="G215" s="7" t="n">
         <v>24</v>
@@ -52955,16 +52550,16 @@
     </row>
     <row r="216">
       <c r="A216" s="4" t="n">
-        <v>14786803914</v>
+        <v>78258022608</v>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>M24:Rabobank - New Deal</t>
+          <t>FintechConnect24: Luzerner Kantonalbank</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Rabobank</t>
+          <t>Luzerner Kantonalbank</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -52976,7 +52571,7 @@
         <v>46184</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="G216" s="7" t="n">
         <v>24</v>
@@ -52984,16 +52579,16 @@
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
-        <v>202506743999</v>
+        <v>285394684142</v>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Belfius</t>
+          <t>N26 - RPI (Tapix)</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Belfius</t>
+          <t>N26</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -53005,7 +52600,7 @@
         <v>46184</v>
       </c>
       <c r="F217" s="6" t="n">
-        <v>1</v>
+        <v>81000</v>
       </c>
       <c r="G217" s="7" t="n">
         <v>24</v>
@@ -53013,28 +52608,28 @@
     </row>
     <row r="218">
       <c r="A218" s="4" t="n">
-        <v>505124448464</v>
+        <v>14786803914</v>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Secret Alchemist: Moksha Shah - contact form</t>
+          <t>M24:Rabobank - New Deal</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Secret Alchemist</t>
+          <t>Rabobank</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>24</v>
@@ -53042,28 +52637,28 @@
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
-        <v>505667256549</v>
+        <v>202506743999</v>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>: misha mikhaylov - contact form</t>
+          <t>Belfius</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Luminar Capital</t>
+          <t>Belfius</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E219" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F219" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G219" s="7" t="n">
         <v>24</v>
@@ -53071,28 +52666,28 @@
     </row>
     <row r="220">
       <c r="A220" s="4" t="n">
-        <v>90309296366</v>
+        <v>505124448464</v>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>FintechConnect24: Mano.bank</t>
+          <t>Secret Alchemist: Moksha Shah - contact form</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Mano.bank</t>
+          <t>Secret Alchemist</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E220" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>24</v>
@@ -53100,28 +52695,28 @@
     </row>
     <row r="221">
       <c r="A221" s="4" t="n">
-        <v>11400117471</v>
+        <v>505667256549</v>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive: PSA</t>
+          <t>: misha mikhaylov - contact form</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Payment Service Austria</t>
+          <t>Luminar Capital</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F221" s="6" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G221" s="7" t="n">
         <v>24</v>
@@ -53129,16 +52724,16 @@
     </row>
     <row r="222">
       <c r="A222" s="4" t="n">
-        <v>200712206579</v>
+        <v>11400117471</v>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>INTELICA CONSULTING: Meiker Lazo - contact form</t>
+          <t>MoneyLive: PSA</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>INTELICA CONSULTING</t>
+          <t>Payment Service Austria</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -53150,7 +52745,7 @@
         <v>46184</v>
       </c>
       <c r="F222" s="6" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G222" s="7" t="n">
         <v>24</v>
@@ -53386,17 +52981,15 @@
     </row>
     <row r="231">
       <c r="A231" s="4" t="n">
-        <v>504456380660</v>
+        <v>499951318240</v>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Cornerstone Asset Managers: Mukisa Moses - contact form</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="inlineStr">
-        <is>
-          <t>Cornerstone Asset Managers</t>
-        </is>
+          <t>: Antoine Lefebvre - contact form</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="n">
+        <v/>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
@@ -53415,15 +53008,17 @@
     </row>
     <row r="232">
       <c r="A232" s="4" t="n">
-        <v>499908905161</v>
+        <v>504456380660</v>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>: Léa Morel - contact form</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="n">
-        <v/>
+          <t>Cornerstone Asset Managers: Mukisa Moses - contact form</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>Cornerstone Asset Managers</t>
+        </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
@@ -53442,17 +53037,15 @@
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
-        <v>314791510235</v>
+        <v>499908905161</v>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>FIZ - New Deal Alex Kosovskiy</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>FIZ</t>
-        </is>
+          <t>: Léa Morel - contact form</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="n">
+        <v/>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
@@ -53463,7 +53056,7 @@
         <v>46202</v>
       </c>
       <c r="F233" s="6" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G233" s="7" t="n">
         <v>27</v>
@@ -53471,15 +53064,17 @@
     </row>
     <row r="234">
       <c r="A234" s="4" t="n">
-        <v>499903363308</v>
+        <v>314791510235</v>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>: Camille Bernard - contact form</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="n">
-        <v/>
+          <t>FIZ - New Deal Alex Kosovskiy</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>FIZ</t>
+        </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
@@ -53490,7 +53085,7 @@
         <v>46202</v>
       </c>
       <c r="F234" s="6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>27</v>
@@ -53498,11 +53093,11 @@
     </row>
     <row r="235">
       <c r="A235" s="4" t="n">
-        <v>499951318240</v>
+        <v>499903363308</v>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>: Antoine Lefebvre - contact form</t>
+          <t>: Camille Bernard - contact form</t>
         </is>
       </c>
       <c r="C235" s="4" t="n">
@@ -53923,16 +53518,16 @@
     </row>
     <row r="250">
       <c r="A250" s="4" t="n">
-        <v>285715078373</v>
+        <v>311526355159</v>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>AXIS India</t>
+          <t>MoneyKSA: BSF</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Axis Bank</t>
+          <t>Banque Saudi Fransi</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -53944,7 +53539,7 @@
         <v>46219</v>
       </c>
       <c r="F250" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G250" s="7" t="n">
         <v>29</v>
@@ -53952,16 +53547,16 @@
     </row>
     <row r="251">
       <c r="A251" s="4" t="n">
-        <v>495269111005</v>
+        <v>16200551119</v>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Manager.one: Melanie FAUCHON - contact form</t>
+          <t>Jordan Ahli Bank, woodpecker</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Manager.one</t>
+          <t>Jordan Ahli Bank</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -53973,7 +53568,7 @@
         <v>46219</v>
       </c>
       <c r="F251" s="6" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G251" s="7" t="n">
         <v>29</v>
@@ -53981,16 +53576,16 @@
     </row>
     <row r="252">
       <c r="A252" s="4" t="n">
-        <v>311549636806</v>
+        <v>285715078373</v>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: Drahim</t>
+          <t>AXIS India</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Drahim</t>
+          <t>Axis Bank</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -54002,7 +53597,7 @@
         <v>46219</v>
       </c>
       <c r="F252" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>29</v>
@@ -54010,16 +53605,16 @@
     </row>
     <row r="253">
       <c r="A253" s="4" t="n">
-        <v>501313743042</v>
+        <v>495269111005</v>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank DXB - discovery</t>
+          <t>Manager.one: Melanie FAUCHON - contact form</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>Manager.one</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -54031,7 +53626,7 @@
         <v>46219</v>
       </c>
       <c r="F253" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G253" s="7" t="n">
         <v>29</v>
@@ -54039,16 +53634,16 @@
     </row>
     <row r="254">
       <c r="A254" s="4" t="n">
-        <v>460476222664</v>
+        <v>311549636806</v>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Al Barid Bank - from HPS</t>
+          <t>MoneyKSA: Drahim</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Al Barid Bank</t>
+          <t>Drahim</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -54060,7 +53655,7 @@
         <v>46219</v>
       </c>
       <c r="F254" s="6" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G254" s="7" t="n">
         <v>29</v>
@@ -54068,16 +53663,16 @@
     </row>
     <row r="255">
       <c r="A255" s="4" t="n">
-        <v>285342572762</v>
+        <v>501313743042</v>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Banque Patronus</t>
+          <t>Standard Chartered Bank DXB - discovery</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Banque Patronus</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -54089,7 +53684,7 @@
         <v>46219</v>
       </c>
       <c r="F255" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G255" s="7" t="n">
         <v>29</v>
@@ -54097,16 +53692,16 @@
     </row>
     <row r="256">
       <c r="A256" s="4" t="n">
-        <v>16200551119</v>
+        <v>460476222664</v>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Jordan Ahli Bank, woodpecker</t>
+          <t>Al Barid Bank - from HPS</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Jordan Ahli Bank</t>
+          <t>Al Barid Bank</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -54118,7 +53713,7 @@
         <v>46219</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>29</v>
@@ -54126,16 +53721,16 @@
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
-        <v>245212643546</v>
+        <v>285342572762</v>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Fintech Dubai:Wio UAE</t>
+          <t>Source: Linkedin; Company: Banque Patronus</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Wio UAE</t>
+          <t>Banque Patronus</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -54155,16 +53750,16 @@
     </row>
     <row r="258">
       <c r="A258" s="4" t="n">
-        <v>311526355159</v>
+        <v>245212643546</v>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: BSF</t>
+          <t>Fintech Dubai:Wio UAE</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Banque Saudi Fransi</t>
+          <t>Wio UAE</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -54935,7 +54530,7 @@
         <v>500</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="15" t="n">
         <v>500</v>
@@ -55123,7 +54718,7 @@
         <v>55800</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>55800</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>55800</v>
@@ -55217,7 +54812,7 @@
         <v>348240</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>303840</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>303840</v>
@@ -55311,7 +54906,7 @@
         <v>170000</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>150000</v>
@@ -55405,7 +55000,7 @@
         <v>1189350</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>1062900</v>
+        <v>225000</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>1062900</v>
@@ -55499,7 +55094,7 @@
         <v>408830</v>
       </c>
       <c r="AC13" s="15" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="15" t="n">
         <v>500000</v>
@@ -55593,7 +55188,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="14" t="n">
-        <v>89015</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="14" t="n">
         <v>89015</v>
@@ -56063,7 +55658,7 @@
         <v>2202420</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>2191755</v>
+        <v>254700</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>2191755</v>
@@ -56157,10 +55752,10 @@
         <v>135050</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-10665</v>
+        <v>-1947720</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>0</v>
+        <v>1937055</v>
       </c>
     </row>
     <row r="22">
@@ -56251,7 +55846,7 @@
         <v>2382620</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>2433955</v>
+        <v>225000</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>2433955</v>
@@ -56345,10 +55940,10 @@
         <v>141050</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>51335</v>
+        <v>-2157620</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>0</v>
+        <v>2208955</v>
       </c>
     </row>
     <row r="24">
@@ -56909,7 +56504,7 @@
         <v>75000</v>
       </c>
       <c r="AC29" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>75000</v>
@@ -57003,7 +56598,7 @@
         <v>250000</v>
       </c>
       <c r="AC30" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>150000</v>
@@ -57097,7 +56692,7 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>100000</v>
@@ -57191,7 +56786,7 @@
         <v>3010000</v>
       </c>
       <c r="AC32" t="n">
-        <v>2910000</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>2910000</v>
@@ -57285,7 +56880,7 @@
         <v>3027000</v>
       </c>
       <c r="AC33" t="n">
-        <v>2657000</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>2657000</v>
@@ -57379,7 +56974,7 @@
         <v>1078000</v>
       </c>
       <c r="AC34" t="n">
-        <v>1078000</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>1078000</v>
@@ -57473,7 +57068,7 @@
         <v>2643000</v>
       </c>
       <c r="AC35" t="n">
-        <v>2462000</v>
+        <v>500000</v>
       </c>
       <c r="AD35" t="n">
         <v>2462000</v>
@@ -57567,7 +57162,7 @@
         <v>578755</v>
       </c>
       <c r="AC36" t="n">
-        <v>680055</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>680055</v>
@@ -57661,7 +57256,7 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>93700</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>93700</v>
@@ -57943,7 +57538,7 @@
         <v>750</v>
       </c>
       <c r="AC40" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>750</v>
@@ -58037,7 +57632,7 @@
         <v>2500</v>
       </c>
       <c r="AC41" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>1500</v>
@@ -58131,7 +57726,7 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>1000</v>
@@ -58225,7 +57820,7 @@
         <v>90300</v>
       </c>
       <c r="AC43" t="n">
-        <v>87300</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>87300</v>
@@ -58319,7 +57914,7 @@
         <v>363240</v>
       </c>
       <c r="AC44" t="n">
-        <v>318840</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>318840</v>
@@ -58413,7 +58008,7 @@
         <v>215600</v>
       </c>
       <c r="AC45" t="n">
-        <v>215600</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>215600</v>
@@ -58507,7 +58102,7 @@
         <v>1189350</v>
       </c>
       <c r="AC46" t="n">
-        <v>1107900</v>
+        <v>225000</v>
       </c>
       <c r="AD46" t="n">
         <v>1107900</v>
@@ -58601,7 +58196,7 @@
         <v>520880</v>
       </c>
       <c r="AC47" t="n">
-        <v>612050</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>612050</v>
@@ -58695,7 +58290,7 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>89015</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>89015</v>
@@ -59143,10 +58738,10 @@
         <v>141050</v>
       </c>
       <c r="AC52" t="n">
-        <v>51335</v>
+        <v>-2157620</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2208955</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -59237,7 +58832,7 @@
         <v>2202420</v>
       </c>
       <c r="AC53" t="n">
-        <v>2191755</v>
+        <v>254700</v>
       </c>
       <c r="AD53" t="n">
         <v>2191755</v>
@@ -59331,7 +58926,7 @@
         <v>2382620</v>
       </c>
       <c r="AC54" t="n">
-        <v>2433955</v>
+        <v>225000</v>
       </c>
       <c r="AD54" t="n">
         <v>2433955</v>
@@ -59996,7 +59591,7 @@
         <v>21370</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>21370</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>21370</v>
@@ -60090,7 +59685,7 @@
         <v>3500</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="15" t="n">
         <v>3500</v>
@@ -60278,7 +59873,7 @@
         <v>8310</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>8310</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>8310</v>
@@ -60466,7 +60061,7 @@
         <v>5600</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>5600</v>
@@ -60560,7 +60155,7 @@
         <v>90000</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>90000</v>
@@ -60842,7 +60437,7 @@
         <v>95000</v>
       </c>
       <c r="AC15" s="15" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="15" t="n">
         <v>95000</v>
@@ -61218,7 +60813,7 @@
         <v>1020780</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>1020780</v>
+        <v>797000</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>1020780</v>
@@ -61312,10 +60907,10 @@
         <v>0</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>0</v>
+        <v>-223780</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>0</v>
+        <v>223780</v>
       </c>
     </row>
     <row r="22">
@@ -61406,7 +61001,7 @@
         <v>233780</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>233780</v>
+        <v>270000</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>233780</v>
@@ -61500,10 +61095,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>0</v>
+        <v>36220</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>0</v>
+        <v>-36220</v>
       </c>
     </row>
     <row r="24">
@@ -61970,7 +61565,7 @@
         <v>2137000</v>
       </c>
       <c r="AC28" t="n">
-        <v>2137000</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>2137000</v>
@@ -62064,7 +61659,7 @@
         <v>350000</v>
       </c>
       <c r="AC29" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>350000</v>
@@ -62252,7 +61847,7 @@
         <v>277002</v>
       </c>
       <c r="AC31" t="n">
-        <v>277002</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>277002</v>
@@ -62440,7 +62035,7 @@
         <v>78000</v>
       </c>
       <c r="AC33" t="n">
-        <v>78000</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>78000</v>
@@ -62534,7 +62129,7 @@
         <v>200000</v>
       </c>
       <c r="AC34" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>200000</v>
@@ -62628,7 +62223,7 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -62816,7 +62411,7 @@
         <v>100000</v>
       </c>
       <c r="AC37" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>100000</v>
@@ -63004,7 +62599,7 @@
         <v>21370</v>
       </c>
       <c r="AC39" t="n">
-        <v>21370</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>21370</v>
@@ -63098,7 +62693,7 @@
         <v>3500</v>
       </c>
       <c r="AC40" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>3500</v>
@@ -63286,7 +62881,7 @@
         <v>8310</v>
       </c>
       <c r="AC42" t="n">
-        <v>8310</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>8310</v>
@@ -63474,7 +63069,7 @@
         <v>15600</v>
       </c>
       <c r="AC44" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>15600</v>
@@ -63568,7 +63163,7 @@
         <v>90000</v>
       </c>
       <c r="AC45" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>90000</v>
@@ -63662,7 +63257,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -63850,7 +63445,7 @@
         <v>95000</v>
       </c>
       <c r="AC48" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>95000</v>
@@ -64349,7 +63944,7 @@
         <v>600</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>600</v>
@@ -64443,7 +64038,7 @@
         <v>800</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="15" t="n">
         <v>800</v>
@@ -64631,7 +64226,7 @@
         <v>4200</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>2700</v>
@@ -64725,7 +64320,7 @@
         <v>12600</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>18960</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>18960</v>
@@ -64819,7 +64414,7 @@
         <v>148835</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>148835</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>148835</v>
@@ -64913,7 +64508,7 @@
         <v>315000</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>315000</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>315000</v>
@@ -65195,7 +64790,7 @@
         <v>23750</v>
       </c>
       <c r="AC15" s="15" t="n">
-        <v>23750</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="15" t="n">
         <v>23750</v>
@@ -65571,7 +65166,7 @@
         <v>1070785</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>1075645</v>
+        <v>565000</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>1075645</v>
@@ -65665,10 +65260,10 @@
         <v>1500</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>4860</v>
+        <v>-505785</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>0</v>
+        <v>510645</v>
       </c>
     </row>
     <row r="22">
@@ -65759,7 +65354,7 @@
         <v>863355</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>868215</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>868215</v>
@@ -65853,10 +65448,10 @@
         <v>75182</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>4860</v>
+        <v>-863355</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>0</v>
+        <v>868215</v>
       </c>
     </row>
     <row r="24">
@@ -66417,7 +66012,7 @@
         <v>560010</v>
       </c>
       <c r="AC29" t="n">
-        <v>560010</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>560010</v>
@@ -66511,7 +66106,7 @@
         <v>280009</v>
       </c>
       <c r="AC30" t="n">
-        <v>280009</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>280009</v>
@@ -66699,7 +66294,7 @@
         <v>965008</v>
       </c>
       <c r="AC32" t="n">
-        <v>915009</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>915009</v>
@@ -66793,7 +66388,7 @@
         <v>1196100</v>
       </c>
       <c r="AC33" t="n">
-        <v>1249100</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>1249100</v>
@@ -66887,7 +66482,7 @@
         <v>1044175</v>
       </c>
       <c r="AC34" t="n">
-        <v>1044175</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>1044175</v>
@@ -66981,7 +66576,7 @@
         <v>827750</v>
       </c>
       <c r="AC35" t="n">
-        <v>827750</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>827750</v>
@@ -67075,7 +66670,7 @@
         <v>86000</v>
       </c>
       <c r="AC36" t="n">
-        <v>86000</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>86000</v>
@@ -67263,7 +66858,7 @@
         <v>25000</v>
       </c>
       <c r="AC38" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>25000</v>
@@ -67451,7 +67046,7 @@
         <v>5600</v>
       </c>
       <c r="AC40" t="n">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>5600</v>
@@ -67545,7 +67140,7 @@
         <v>2800</v>
       </c>
       <c r="AC41" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>2800</v>
@@ -67733,7 +67328,7 @@
         <v>28950</v>
       </c>
       <c r="AC43" t="n">
-        <v>27450</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>27450</v>
@@ -67827,7 +67422,7 @@
         <v>143532</v>
       </c>
       <c r="AC44" t="n">
-        <v>149892</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>149892</v>
@@ -67921,7 +67516,7 @@
         <v>208835</v>
       </c>
       <c r="AC45" t="n">
-        <v>208835</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>208835</v>
@@ -68015,7 +67610,7 @@
         <v>372488</v>
       </c>
       <c r="AC46" t="n">
-        <v>372488</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>372488</v>
@@ -68109,7 +67704,7 @@
         <v>77400</v>
       </c>
       <c r="AC47" t="n">
-        <v>77400</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>77400</v>
@@ -68297,7 +67892,7 @@
         <v>23750</v>
       </c>
       <c r="AC49" t="n">
-        <v>23750</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>23750</v>
@@ -68651,10 +68246,10 @@
         <v>75182</v>
       </c>
       <c r="AC52" t="n">
-        <v>4860</v>
+        <v>-863355</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>868215</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -68745,7 +68340,7 @@
         <v>1070785</v>
       </c>
       <c r="AC53" t="n">
-        <v>1075645</v>
+        <v>565000</v>
       </c>
       <c r="AD53" t="n">
         <v>1075645</v>
@@ -68839,7 +68434,7 @@
         <v>863355</v>
       </c>
       <c r="AC54" t="n">
-        <v>868215</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>868215</v>
@@ -69880,7 +69475,7 @@
         <v>19200</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>19200</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>19200</v>
@@ -69974,7 +69569,7 @@
         <v>7000</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>7000</v>
@@ -70068,7 +69663,7 @@
         <v>87300</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>87300</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>87300</v>
@@ -70162,7 +69757,7 @@
         <v>61200</v>
       </c>
       <c r="AC13" s="15" t="n">
-        <v>61200</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="15" t="n">
         <v>61200</v>
@@ -70726,7 +70321,7 @@
         <v>212700</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>174700</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>214700</v>
@@ -70820,10 +70415,10 @@
         <v>53450</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-38000</v>
+        <v>-212700</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>40000</v>
+        <v>214700</v>
       </c>
     </row>
     <row r="22">
@@ -70914,7 +70509,7 @@
         <v>219900</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>181900</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>181900</v>
@@ -71008,10 +70603,10 @@
         <v>60650</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>-38000</v>
+        <v>-219900</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>0</v>
+        <v>181900</v>
       </c>
     </row>
     <row r="24">
@@ -71948,7 +71543,7 @@
         <v>220000</v>
       </c>
       <c r="AC33" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>220000</v>
@@ -72042,7 +71637,7 @@
         <v>35000</v>
       </c>
       <c r="AC34" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>35000</v>
@@ -72136,7 +71731,7 @@
         <v>194000</v>
       </c>
       <c r="AC35" t="n">
-        <v>194000</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>194000</v>
@@ -72230,7 +71825,7 @@
         <v>68000</v>
       </c>
       <c r="AC36" t="n">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>68000</v>
@@ -72982,7 +72577,7 @@
         <v>26400</v>
       </c>
       <c r="AC44" t="n">
-        <v>26400</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>26400</v>
@@ -73076,7 +72671,7 @@
         <v>7000</v>
       </c>
       <c r="AC45" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>7000</v>
@@ -73170,7 +72765,7 @@
         <v>87300</v>
       </c>
       <c r="AC46" t="n">
-        <v>87300</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>87300</v>
@@ -73264,7 +72859,7 @@
         <v>61200</v>
       </c>
       <c r="AC47" t="n">
-        <v>61200</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>61200</v>
@@ -73806,10 +73401,10 @@
         <v>60650</v>
       </c>
       <c r="AC52" t="n">
-        <v>-38000</v>
+        <v>-219900</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>181900</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -73900,7 +73495,7 @@
         <v>212700</v>
       </c>
       <c r="AC53" t="n">
-        <v>174700</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>214700</v>
@@ -73994,7 +73589,7 @@
         <v>219900</v>
       </c>
       <c r="AC54" t="n">
-        <v>181900</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>181900</v>
@@ -75035,7 +74630,7 @@
         <v>72000</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>72000</v>
@@ -75129,7 +74724,7 @@
         <v>7600</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>7600</v>
@@ -75223,7 +74818,7 @@
         <v>68850</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>68850</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>68850</v>
@@ -75317,7 +74912,7 @@
         <v>39690</v>
       </c>
       <c r="AC13" s="15" t="n">
-        <v>39690</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="15" t="n">
         <v>39690</v>
@@ -75881,7 +75476,7 @@
         <v>188140</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>188140</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>188140</v>
@@ -75975,10 +75570,10 @@
         <v>0</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>0</v>
+        <v>-188140</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>0</v>
+        <v>188140</v>
       </c>
     </row>
     <row r="22">
@@ -76069,7 +75664,7 @@
         <v>316410</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>316410</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>316410</v>
@@ -76163,10 +75758,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>0</v>
+        <v>-316410</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>0</v>
+        <v>316410</v>
       </c>
     </row>
     <row r="24">
@@ -76727,7 +76322,7 @@
         <v>605000</v>
       </c>
       <c r="AC29" t="n">
-        <v>605000</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>605000</v>
@@ -76821,7 +76416,7 @@
         <v>1632000</v>
       </c>
       <c r="AC30" t="n">
-        <v>1632000</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>1632000</v>
@@ -77009,7 +76604,7 @@
         <v>1090000</v>
       </c>
       <c r="AC32" t="n">
-        <v>1090000</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>1090000</v>
@@ -77103,7 +76698,7 @@
         <v>630000</v>
       </c>
       <c r="AC33" t="n">
-        <v>630001</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>630001</v>
@@ -77197,7 +76792,7 @@
         <v>386000</v>
       </c>
       <c r="AC34" t="n">
-        <v>386000</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>386000</v>
@@ -77291,7 +76886,7 @@
         <v>153000</v>
       </c>
       <c r="AC35" t="n">
-        <v>153000</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>153000</v>
@@ -77385,7 +76980,7 @@
         <v>44100</v>
       </c>
       <c r="AC36" t="n">
-        <v>44100</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>44100</v>
@@ -77761,7 +77356,7 @@
         <v>6050</v>
       </c>
       <c r="AC40" t="n">
-        <v>6050</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>6050</v>
@@ -77855,7 +77450,7 @@
         <v>16320</v>
       </c>
       <c r="AC41" t="n">
-        <v>16320</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>16320</v>
@@ -78043,7 +77638,7 @@
         <v>32700</v>
       </c>
       <c r="AC43" t="n">
-        <v>32700</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>32700</v>
@@ -78137,7 +77732,7 @@
         <v>75600</v>
       </c>
       <c r="AC44" t="n">
-        <v>75600</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>75600</v>
@@ -78231,7 +77826,7 @@
         <v>77200</v>
       </c>
       <c r="AC45" t="n">
-        <v>77200</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>77200</v>
@@ -78325,7 +77920,7 @@
         <v>68850</v>
       </c>
       <c r="AC46" t="n">
-        <v>68850</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>68850</v>
@@ -78419,7 +78014,7 @@
         <v>39690</v>
       </c>
       <c r="AC47" t="n">
-        <v>39690</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>39690</v>
@@ -78961,10 +78556,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>-316410</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>316410</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -79055,7 +78650,7 @@
         <v>188140</v>
       </c>
       <c r="AC53" t="n">
-        <v>188140</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>188140</v>
@@ -79149,7 +78744,7 @@
         <v>316410</v>
       </c>
       <c r="AC54" t="n">
-        <v>316410</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>316410</v>
@@ -79814,7 +79409,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>1500</v>
@@ -79908,7 +79503,7 @@
         <v>7000</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="15" t="n">
         <v>7000</v>
@@ -80096,7 +79691,7 @@
         <v>69000</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>33750</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>33750</v>
@@ -80190,7 +79785,7 @@
         <v>24000</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>85200</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>85200</v>
@@ -80284,7 +79879,7 @@
         <v>60000</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>90000</v>
@@ -80378,7 +79973,7 @@
         <v>0</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>45000</v>
@@ -81036,7 +80631,7 @@
         <v>162000</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>262450</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>262450</v>
@@ -81130,10 +80725,10 @@
         <v>0</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>100450</v>
+        <v>-162000</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>0</v>
+        <v>262450</v>
       </c>
     </row>
     <row r="22">
@@ -81224,7 +80819,7 @@
         <v>162000</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>262450</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>262450</v>
@@ -81318,10 +80913,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>100450</v>
+        <v>-162000</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>0</v>
+        <v>262450</v>
       </c>
     </row>
     <row r="24">
@@ -81882,7 +81477,7 @@
         <v>100000</v>
       </c>
       <c r="AC29" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>150000</v>
@@ -81976,7 +81571,7 @@
         <v>700000</v>
       </c>
       <c r="AC30" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>700000</v>
@@ -82164,7 +81759,7 @@
         <v>2300000</v>
       </c>
       <c r="AC32" t="n">
-        <v>1125000</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>1125000</v>
@@ -82258,7 +81853,7 @@
         <v>200000</v>
       </c>
       <c r="AC33" t="n">
-        <v>710000</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>710000</v>
@@ -82352,7 +81947,7 @@
         <v>300000</v>
       </c>
       <c r="AC34" t="n">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>450000</v>
@@ -82446,7 +82041,7 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>100000</v>
@@ -82916,7 +82511,7 @@
         <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>1500</v>
@@ -83010,7 +82605,7 @@
         <v>7000</v>
       </c>
       <c r="AC41" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>7000</v>
@@ -83198,7 +82793,7 @@
         <v>69000</v>
       </c>
       <c r="AC43" t="n">
-        <v>33750</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>33750</v>
@@ -83292,7 +82887,7 @@
         <v>24000</v>
       </c>
       <c r="AC44" t="n">
-        <v>85200</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>85200</v>
@@ -83386,7 +82981,7 @@
         <v>60000</v>
       </c>
       <c r="AC45" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>90000</v>
@@ -83480,7 +83075,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>45000</v>
@@ -84116,10 +83711,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>100450</v>
+        <v>-162000</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>262450</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -84210,7 +83805,7 @@
         <v>162000</v>
       </c>
       <c r="AC53" t="n">
-        <v>262450</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>262450</v>
@@ -84304,7 +83899,7 @@
         <v>162000</v>
       </c>
       <c r="AC54" t="n">
-        <v>262450</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>262450</v>
@@ -85439,7 +85034,7 @@
         <v>15400</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>15400</v>
@@ -86191,7 +85786,7 @@
         <v>15400</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>15400</v>
@@ -86285,10 +85880,10 @@
         <v>0</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>0</v>
+        <v>-15400</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="22">
@@ -86379,7 +85974,7 @@
         <v>31900</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>32800</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>32800</v>
@@ -86473,10 +86068,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>900</v>
+        <v>-31900</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>0</v>
+        <v>32800</v>
       </c>
     </row>
     <row r="24">
@@ -87225,7 +86820,7 @@
         <v>150000</v>
       </c>
       <c r="AC31" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>180000</v>
@@ -87319,7 +86914,7 @@
         <v>100000</v>
       </c>
       <c r="AC32" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>100000</v>
@@ -87413,7 +87008,7 @@
         <v>77000</v>
       </c>
       <c r="AC33" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>77000</v>
@@ -88259,7 +87854,7 @@
         <v>4500</v>
       </c>
       <c r="AC42" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>5400</v>
@@ -88353,7 +87948,7 @@
         <v>12000</v>
       </c>
       <c r="AC43" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>12000</v>
@@ -88447,7 +88042,7 @@
         <v>15400</v>
       </c>
       <c r="AC44" t="n">
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>15400</v>

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -17366,16 +17366,16 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>402515561715</v>
+        <v>11878287315</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SFF25: Savo digital wallet (Singapore) (Tapix)</t>
+          <t>Erste - George use case (Tapix)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Savo Inc</t>
+          <t>Erste Bank Austria</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -17387,7 +17387,7 @@
         <v>46083</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>40000</v>
+        <v>387000</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>10</v>
@@ -17395,16 +17395,16 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>15855277004</v>
+        <v>402515561715</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>AIB: Paul Dockery - RFx (Tapix)</t>
+          <t>SFF25: Savo digital wallet (Singapore) (Tapix)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>AIB</t>
+          <t>Savo Inc</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -17416,7 +17416,7 @@
         <v>46083</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>370000</v>
+        <v>40000</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>10</v>
@@ -17424,28 +17424,28 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>252845309170</v>
+        <v>15855277004</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>M20-25: Swissborg (Tapix) - deal WON</t>
+          <t>AIB: Paul Dockery - RFx (Tapix)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>swissborg</t>
+          <t>AIB</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
         <v>46083</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>15000</v>
+        <v>370000</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>10</v>
@@ -17453,28 +17453,28 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>11878287315</v>
+        <v>252845309170</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Erste - George use case (Tapix)</t>
+          <t>M20-25: Swissborg (Tapix) - deal WON</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Erste Bank Austria</t>
+          <t>swissborg</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
         <v>46083</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>387000</v>
+        <v>15000</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>10</v>
@@ -22289,7 +22289,7 @@
         <v>22970</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>0</v>
+        <v>23470</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>23470</v>
@@ -22383,10 +22383,10 @@
         <v>11800</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>0</v>
+        <v>11800</v>
       </c>
       <c r="AD7" s="15" t="n">
-        <v>11800</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="8">
@@ -22477,10 +22477,10 @@
         <v>1000</v>
       </c>
       <c r="AC8" s="14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" s="14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -22571,7 +22571,7 @@
         <v>137310</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>0</v>
+        <v>100560</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>100560</v>
@@ -22665,10 +22665,10 @@
         <v>476040</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>0</v>
+        <v>499200</v>
       </c>
       <c r="AD10" s="14" t="n">
-        <v>499200</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="11">
@@ -22759,10 +22759,10 @@
         <v>414435</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>0</v>
+        <v>424435</v>
       </c>
       <c r="AD11" s="15" t="n">
-        <v>424435</v>
+        <v>393435</v>
       </c>
     </row>
     <row r="12">
@@ -22853,10 +22853,10 @@
         <v>1750500</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>225000</v>
+        <v>1669050</v>
       </c>
       <c r="AD12" s="14" t="n">
-        <v>1669050</v>
+        <v>1738800</v>
       </c>
     </row>
     <row r="13">
@@ -22947,7 +22947,7 @@
         <v>509720</v>
       </c>
       <c r="AC13" s="15" t="n">
-        <v>0</v>
+        <v>600890</v>
       </c>
       <c r="AD13" s="15" t="n">
         <v>600890</v>
@@ -23041,7 +23041,7 @@
         <v>38000</v>
       </c>
       <c r="AC14" s="14" t="n">
-        <v>0</v>
+        <v>127015</v>
       </c>
       <c r="AD14" s="14" t="n">
         <v>89015</v>
@@ -23135,7 +23135,7 @@
         <v>118750</v>
       </c>
       <c r="AC15" s="15" t="n">
-        <v>0</v>
+        <v>118750</v>
       </c>
       <c r="AD15" s="15" t="n">
         <v>118750</v>
@@ -23511,10 +23511,10 @@
         <v>4872225</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>1616700</v>
+        <v>4967870</v>
       </c>
       <c r="AD20" s="17" t="n">
-        <v>4968870</v>
+        <v>5015420</v>
       </c>
     </row>
     <row r="21">
@@ -23605,10 +23605,10 @@
         <v>190000</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-3255525</v>
+        <v>95645</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>3352170</v>
+        <v>47550</v>
       </c>
     </row>
     <row r="22">
@@ -23699,10 +23699,10 @@
         <v>4209965</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>495000</v>
+        <v>4368510</v>
       </c>
       <c r="AD22" s="17" t="n">
-        <v>4329510</v>
+        <v>4376060</v>
       </c>
     </row>
     <row r="23">
@@ -23793,10 +23793,10 @@
         <v>276882</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>-3714965</v>
+        <v>158545</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>3834510</v>
+        <v>7550</v>
       </c>
     </row>
     <row r="24">
@@ -24357,7 +24357,7 @@
         <v>3477010</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3527010</v>
       </c>
       <c r="AD29" t="n">
         <v>3527010</v>
@@ -24451,10 +24451,10 @@
         <v>3212009</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3112009</v>
       </c>
       <c r="AD30" t="n">
-        <v>3112009</v>
+        <v>3012009</v>
       </c>
     </row>
     <row r="31" hidden="1">
@@ -24545,10 +24545,10 @@
         <v>100000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AD31" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="32" hidden="1">
@@ -24639,10 +24639,10 @@
         <v>7792010</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>6497011</v>
       </c>
       <c r="AD32" t="n">
-        <v>6497011</v>
+        <v>6497012</v>
       </c>
     </row>
     <row r="33" hidden="1">
@@ -24733,10 +24733,10 @@
         <v>5373100</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>5566101</v>
       </c>
       <c r="AD33" t="n">
-        <v>5566101</v>
+        <v>5631101</v>
       </c>
     </row>
     <row r="34" hidden="1">
@@ -24827,10 +24827,10 @@
         <v>2998175</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3148175</v>
       </c>
       <c r="AD34" t="n">
-        <v>3148175</v>
+        <v>2993175</v>
       </c>
     </row>
     <row r="35" hidden="1">
@@ -24921,10 +24921,10 @@
         <v>4017750</v>
       </c>
       <c r="AC35" t="n">
-        <v>500000</v>
+        <v>3936750</v>
       </c>
       <c r="AD35" t="n">
-        <v>3936750</v>
+        <v>4091750</v>
       </c>
     </row>
     <row r="36" hidden="1">
@@ -25015,7 +25015,7 @@
         <v>776855</v>
       </c>
       <c r="AC36" t="n">
-        <v>300000</v>
+        <v>878155</v>
       </c>
       <c r="AD36" t="n">
         <v>878155</v>
@@ -25109,7 +25109,7 @@
         <v>40000</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>133700</v>
       </c>
       <c r="AD37" t="n">
         <v>93700</v>
@@ -25203,7 +25203,7 @@
         <v>125000</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="AD38" t="n">
         <v>125000</v>
@@ -25391,7 +25391,7 @@
         <v>34770</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>35270</v>
       </c>
       <c r="AD40" t="n">
         <v>35270</v>
@@ -25485,10 +25485,10 @@
         <v>32120</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>31120</v>
       </c>
       <c r="AD41" t="n">
-        <v>31120</v>
+        <v>30120</v>
       </c>
     </row>
     <row r="42" hidden="1">
@@ -25579,10 +25579,10 @@
         <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43" hidden="1">
@@ -25673,7 +25673,7 @@
         <v>233760</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>194910</v>
       </c>
       <c r="AD43" t="n">
         <v>194910</v>
@@ -25767,10 +25767,10 @@
         <v>644772</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>667932</v>
       </c>
       <c r="AD44" t="n">
-        <v>667932</v>
+        <v>675732</v>
       </c>
     </row>
     <row r="45" hidden="1">
@@ -25861,10 +25861,10 @@
         <v>599635</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>629635</v>
       </c>
       <c r="AD45" t="n">
-        <v>629635</v>
+        <v>598635</v>
       </c>
     </row>
     <row r="46" hidden="1">
@@ -25955,10 +25955,10 @@
         <v>1807988</v>
       </c>
       <c r="AC46" t="n">
-        <v>225000</v>
+        <v>1771538</v>
       </c>
       <c r="AD46" t="n">
-        <v>1771538</v>
+        <v>1841288</v>
       </c>
     </row>
     <row r="47" hidden="1">
@@ -26049,7 +26049,7 @@
         <v>699170</v>
       </c>
       <c r="AC47" t="n">
-        <v>270000</v>
+        <v>790340</v>
       </c>
       <c r="AD47" t="n">
         <v>790340</v>
@@ -26143,7 +26143,7 @@
         <v>38000</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>127015</v>
       </c>
       <c r="AD48" t="n">
         <v>89015</v>
@@ -26237,7 +26237,7 @@
         <v>118750</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>118750</v>
       </c>
       <c r="AD49" t="n">
         <v>118750</v>
@@ -26591,10 +26591,10 @@
         <v>276882</v>
       </c>
       <c r="AC52" t="n">
-        <v>-3714965</v>
+        <v>158545</v>
       </c>
       <c r="AD52" t="n">
-        <v>3834510</v>
+        <v>7550</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -26685,10 +26685,10 @@
         <v>4872225</v>
       </c>
       <c r="AC53" t="n">
-        <v>1616700</v>
+        <v>4967870</v>
       </c>
       <c r="AD53" t="n">
-        <v>4968870</v>
+        <v>5015420</v>
       </c>
     </row>
     <row r="54" hidden="1">
@@ -26779,10 +26779,10 @@
         <v>4209965</v>
       </c>
       <c r="AC54" t="n">
-        <v>495000</v>
+        <v>4368510</v>
       </c>
       <c r="AD54" t="n">
-        <v>4329510</v>
+        <v>4376060</v>
       </c>
     </row>
     <row r="55" hidden="1">
@@ -27550,7 +27550,7 @@
         <v>50000</v>
       </c>
       <c r="AC7" s="25" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AD7" s="25" t="n">
         <v>50000</v>
@@ -27738,7 +27738,7 @@
         <v>1860000</v>
       </c>
       <c r="AC9" s="25" t="n">
-        <v>0</v>
+        <v>1860000</v>
       </c>
       <c r="AD9" s="25" t="n">
         <v>1860000</v>
@@ -27832,7 +27832,7 @@
         <v>2902000</v>
       </c>
       <c r="AC10" s="25" t="n">
-        <v>0</v>
+        <v>2532000</v>
       </c>
       <c r="AD10" s="25" t="n">
         <v>2532000</v>
@@ -27926,7 +27926,7 @@
         <v>850000</v>
       </c>
       <c r="AC11" s="25" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="AD11" s="25" t="n">
         <v>750000</v>
@@ -28020,7 +28020,7 @@
         <v>2643000</v>
       </c>
       <c r="AC12" s="25" t="n">
-        <v>500000</v>
+        <v>2362000</v>
       </c>
       <c r="AD12" s="25" t="n">
         <v>2362000</v>
@@ -28114,7 +28114,7 @@
         <v>454255</v>
       </c>
       <c r="AC13" s="25" t="n">
-        <v>0</v>
+        <v>555555</v>
       </c>
       <c r="AD13" s="25" t="n">
         <v>555555</v>
@@ -28208,7 +28208,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="25" t="n">
-        <v>0</v>
+        <v>93700</v>
       </c>
       <c r="AD14" s="25" t="n">
         <v>93700</v>
@@ -28649,7 +28649,7 @@
         <v>2137000</v>
       </c>
       <c r="AC20" s="25" t="n">
-        <v>0</v>
+        <v>2137000</v>
       </c>
       <c r="AD20" s="25" t="n">
         <v>2137000</v>
@@ -28743,7 +28743,7 @@
         <v>350000</v>
       </c>
       <c r="AC21" s="25" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="AD21" s="25" t="n">
         <v>350000</v>
@@ -28931,7 +28931,7 @@
         <v>277002</v>
       </c>
       <c r="AC23" s="25" t="n">
-        <v>0</v>
+        <v>277002</v>
       </c>
       <c r="AD23" s="25" t="n">
         <v>277002</v>
@@ -29119,7 +29119,7 @@
         <v>28000</v>
       </c>
       <c r="AC25" s="25" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="AD25" s="25" t="n">
         <v>28000</v>
@@ -29213,7 +29213,7 @@
         <v>200000</v>
       </c>
       <c r="AC26" s="25" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AD26" s="25" t="n">
         <v>200000</v>
@@ -29495,7 +29495,7 @@
         <v>100000</v>
       </c>
       <c r="AC29" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD29" s="25" t="n">
         <v>100000</v>
@@ -29842,7 +29842,7 @@
         <v>60010</v>
       </c>
       <c r="AC34" s="25" t="n">
-        <v>0</v>
+        <v>60010</v>
       </c>
       <c r="AD34" s="25" t="n">
         <v>60010</v>
@@ -29936,7 +29936,7 @@
         <v>80008</v>
       </c>
       <c r="AC35" s="25" t="n">
-        <v>0</v>
+        <v>80008</v>
       </c>
       <c r="AD35" s="25" t="n">
         <v>80008</v>
@@ -30124,7 +30124,7 @@
         <v>140005</v>
       </c>
       <c r="AC37" s="25" t="n">
-        <v>0</v>
+        <v>90006</v>
       </c>
       <c r="AD37" s="25" t="n">
         <v>90006</v>
@@ -30218,7 +30218,7 @@
         <v>105000</v>
       </c>
       <c r="AC38" s="25" t="n">
-        <v>0</v>
+        <v>158000</v>
       </c>
       <c r="AD38" s="25" t="n">
         <v>158000</v>
@@ -30312,10 +30312,10 @@
         <v>744175</v>
       </c>
       <c r="AC39" s="25" t="n">
-        <v>0</v>
+        <v>744175</v>
       </c>
       <c r="AD39" s="25" t="n">
-        <v>744175</v>
+        <v>589175</v>
       </c>
     </row>
     <row r="40">
@@ -30406,10 +30406,10 @@
         <v>700000</v>
       </c>
       <c r="AC40" s="25" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="AD40" s="25" t="n">
-        <v>700000</v>
+        <v>855000</v>
       </c>
     </row>
     <row r="41">
@@ -30688,7 +30688,7 @@
         <v>25000</v>
       </c>
       <c r="AC43" s="25" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="AD43" s="25" t="n">
         <v>25000</v>
@@ -31411,10 +31411,10 @@
         <v>160000</v>
       </c>
       <c r="AC52" s="25" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="AD52" s="25" t="n">
-        <v>160000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="53">
@@ -31505,7 +31505,7 @@
         <v>35000</v>
       </c>
       <c r="AC53" s="25" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="AD53" s="25" t="n">
         <v>35000</v>
@@ -31599,7 +31599,7 @@
         <v>194000</v>
       </c>
       <c r="AC54" s="25" t="n">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="AD54" s="25" t="n">
         <v>194000</v>
@@ -31693,7 +31693,7 @@
         <v>68000</v>
       </c>
       <c r="AC55" s="25" t="n">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="AD55" s="25" t="n">
         <v>68000</v>
@@ -31787,7 +31787,7 @@
         <v>40000</v>
       </c>
       <c r="AC56" s="25" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AD56" s="25" t="n">
         <v>0</v>
@@ -32604,7 +32604,7 @@
         <v>600000</v>
       </c>
       <c r="AC66" s="25" t="n">
-        <v>0</v>
+        <v>600001</v>
       </c>
       <c r="AD66" s="25" t="n">
         <v>600001</v>
@@ -32698,7 +32698,7 @@
         <v>38000</v>
       </c>
       <c r="AC67" s="25" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="AD67" s="25" t="n">
         <v>38000</v>
@@ -32792,7 +32792,7 @@
         <v>153000</v>
       </c>
       <c r="AC68" s="25" t="n">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="AD68" s="25" t="n">
         <v>153000</v>
@@ -32886,7 +32886,7 @@
         <v>44100</v>
       </c>
       <c r="AC69" s="25" t="n">
-        <v>0</v>
+        <v>44100</v>
       </c>
       <c r="AD69" s="25" t="n">
         <v>44100</v>
@@ -33421,7 +33421,7 @@
         <v>100000</v>
       </c>
       <c r="AC76" s="25" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AD76" s="25" t="n">
         <v>150000</v>
@@ -33515,10 +33515,10 @@
         <v>700000</v>
       </c>
       <c r="AC77" s="25" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="AD77" s="25" t="n">
-        <v>700000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="78">
@@ -33609,10 +33609,10 @@
         <v>100000</v>
       </c>
       <c r="AC78" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD78" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="79">
@@ -33703,7 +33703,7 @@
         <v>2300000</v>
       </c>
       <c r="AC79" s="25" t="n">
-        <v>0</v>
+        <v>1125000</v>
       </c>
       <c r="AD79" s="25" t="n">
         <v>1125000</v>
@@ -33797,7 +33797,7 @@
         <v>200000</v>
       </c>
       <c r="AC80" s="25" t="n">
-        <v>0</v>
+        <v>710000</v>
       </c>
       <c r="AD80" s="25" t="n">
         <v>710000</v>
@@ -33891,7 +33891,7 @@
         <v>300000</v>
       </c>
       <c r="AC81" s="25" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="AD81" s="25" t="n">
         <v>450000</v>
@@ -33985,7 +33985,7 @@
         <v>0</v>
       </c>
       <c r="AC82" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD82" s="25" t="n">
         <v>100000</v>
@@ -35084,7 +35084,7 @@
         <v>77000</v>
       </c>
       <c r="AC95" s="25" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="AD95" s="25" t="n">
         <v>77000</v>
@@ -37064,7 +37064,7 @@
         <v>75000</v>
       </c>
       <c r="AC6" s="25" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AD6" s="25" t="n">
         <v>75000</v>
@@ -37158,7 +37158,7 @@
         <v>250000</v>
       </c>
       <c r="AC7" s="25" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AD7" s="25" t="n">
         <v>150000</v>
@@ -37252,7 +37252,7 @@
         <v>0</v>
       </c>
       <c r="AC8" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD8" s="25" t="n">
         <v>100000</v>
@@ -37346,7 +37346,7 @@
         <v>3010000</v>
       </c>
       <c r="AC9" s="25" t="n">
-        <v>0</v>
+        <v>2910000</v>
       </c>
       <c r="AD9" s="25" t="n">
         <v>2910000</v>
@@ -37440,7 +37440,7 @@
         <v>3027000</v>
       </c>
       <c r="AC10" s="25" t="n">
-        <v>0</v>
+        <v>2657000</v>
       </c>
       <c r="AD10" s="25" t="n">
         <v>2657000</v>
@@ -37534,7 +37534,7 @@
         <v>1078000</v>
       </c>
       <c r="AC11" s="25" t="n">
-        <v>0</v>
+        <v>1078000</v>
       </c>
       <c r="AD11" s="25" t="n">
         <v>1078000</v>
@@ -37628,7 +37628,7 @@
         <v>2643000</v>
       </c>
       <c r="AC12" s="25" t="n">
-        <v>500000</v>
+        <v>2462000</v>
       </c>
       <c r="AD12" s="25" t="n">
         <v>2462000</v>
@@ -37722,7 +37722,7 @@
         <v>578755</v>
       </c>
       <c r="AC13" s="25" t="n">
-        <v>0</v>
+        <v>680055</v>
       </c>
       <c r="AD13" s="25" t="n">
         <v>680055</v>
@@ -37816,7 +37816,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="25" t="n">
-        <v>0</v>
+        <v>93700</v>
       </c>
       <c r="AD14" s="25" t="n">
         <v>93700</v>
@@ -38257,7 +38257,7 @@
         <v>2137000</v>
       </c>
       <c r="AC20" s="25" t="n">
-        <v>0</v>
+        <v>2137000</v>
       </c>
       <c r="AD20" s="25" t="n">
         <v>2137000</v>
@@ -38351,7 +38351,7 @@
         <v>350000</v>
       </c>
       <c r="AC21" s="25" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="AD21" s="25" t="n">
         <v>350000</v>
@@ -38539,7 +38539,7 @@
         <v>277002</v>
       </c>
       <c r="AC23" s="25" t="n">
-        <v>0</v>
+        <v>277002</v>
       </c>
       <c r="AD23" s="25" t="n">
         <v>277002</v>
@@ -38727,7 +38727,7 @@
         <v>78000</v>
       </c>
       <c r="AC25" s="25" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="AD25" s="25" t="n">
         <v>78000</v>
@@ -38821,7 +38821,7 @@
         <v>200000</v>
       </c>
       <c r="AC26" s="25" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AD26" s="25" t="n">
         <v>200000</v>
@@ -38915,7 +38915,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="25" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="25" t="n">
         <v>0</v>
@@ -39103,7 +39103,7 @@
         <v>100000</v>
       </c>
       <c r="AC29" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD29" s="25" t="n">
         <v>100000</v>
@@ -39450,7 +39450,7 @@
         <v>560010</v>
       </c>
       <c r="AC34" s="25" t="n">
-        <v>0</v>
+        <v>560010</v>
       </c>
       <c r="AD34" s="25" t="n">
         <v>560010</v>
@@ -39544,7 +39544,7 @@
         <v>280009</v>
       </c>
       <c r="AC35" s="25" t="n">
-        <v>0</v>
+        <v>280009</v>
       </c>
       <c r="AD35" s="25" t="n">
         <v>280009</v>
@@ -39732,10 +39732,10 @@
         <v>965008</v>
       </c>
       <c r="AC37" s="25" t="n">
-        <v>0</v>
+        <v>915009</v>
       </c>
       <c r="AD37" s="25" t="n">
-        <v>915009</v>
+        <v>915010</v>
       </c>
     </row>
     <row r="38">
@@ -39826,7 +39826,7 @@
         <v>1196100</v>
       </c>
       <c r="AC38" s="25" t="n">
-        <v>0</v>
+        <v>1249100</v>
       </c>
       <c r="AD38" s="25" t="n">
         <v>1249100</v>
@@ -39920,10 +39920,10 @@
         <v>1044175</v>
       </c>
       <c r="AC39" s="25" t="n">
-        <v>0</v>
+        <v>1044175</v>
       </c>
       <c r="AD39" s="25" t="n">
-        <v>1044175</v>
+        <v>889175</v>
       </c>
     </row>
     <row r="40">
@@ -40014,10 +40014,10 @@
         <v>827750</v>
       </c>
       <c r="AC40" s="25" t="n">
-        <v>0</v>
+        <v>827750</v>
       </c>
       <c r="AD40" s="25" t="n">
-        <v>827750</v>
+        <v>982750</v>
       </c>
     </row>
     <row r="41">
@@ -40108,7 +40108,7 @@
         <v>86000</v>
       </c>
       <c r="AC41" s="25" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="AD41" s="25" t="n">
         <v>86000</v>
@@ -40296,7 +40296,7 @@
         <v>25000</v>
       </c>
       <c r="AC43" s="25" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="AD43" s="25" t="n">
         <v>25000</v>
@@ -41019,10 +41019,10 @@
         <v>220000</v>
       </c>
       <c r="AC52" s="25" t="n">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="AD52" s="25" t="n">
-        <v>220000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="53">
@@ -41113,7 +41113,7 @@
         <v>35000</v>
       </c>
       <c r="AC53" s="25" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="AD53" s="25" t="n">
         <v>35000</v>
@@ -41207,7 +41207,7 @@
         <v>194000</v>
       </c>
       <c r="AC54" s="25" t="n">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="AD54" s="25" t="n">
         <v>194000</v>
@@ -41301,7 +41301,7 @@
         <v>68000</v>
       </c>
       <c r="AC55" s="25" t="n">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="AD55" s="25" t="n">
         <v>68000</v>
@@ -41395,7 +41395,7 @@
         <v>40000</v>
       </c>
       <c r="AC56" s="25" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AD56" s="25" t="n">
         <v>0</v>
@@ -41836,7 +41836,7 @@
         <v>605000</v>
       </c>
       <c r="AC62" s="25" t="n">
-        <v>0</v>
+        <v>605000</v>
       </c>
       <c r="AD62" s="25" t="n">
         <v>605000</v>
@@ -41930,7 +41930,7 @@
         <v>1632000</v>
       </c>
       <c r="AC63" s="25" t="n">
-        <v>0</v>
+        <v>1632000</v>
       </c>
       <c r="AD63" s="25" t="n">
         <v>1632000</v>
@@ -42118,7 +42118,7 @@
         <v>1090000</v>
       </c>
       <c r="AC65" s="25" t="n">
-        <v>0</v>
+        <v>1090000</v>
       </c>
       <c r="AD65" s="25" t="n">
         <v>1090000</v>
@@ -42212,7 +42212,7 @@
         <v>630000</v>
       </c>
       <c r="AC66" s="25" t="n">
-        <v>0</v>
+        <v>630001</v>
       </c>
       <c r="AD66" s="25" t="n">
         <v>630001</v>
@@ -42306,7 +42306,7 @@
         <v>386000</v>
       </c>
       <c r="AC67" s="25" t="n">
-        <v>0</v>
+        <v>386000</v>
       </c>
       <c r="AD67" s="25" t="n">
         <v>386000</v>
@@ -42400,7 +42400,7 @@
         <v>153000</v>
       </c>
       <c r="AC68" s="25" t="n">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="AD68" s="25" t="n">
         <v>153000</v>
@@ -42494,7 +42494,7 @@
         <v>44100</v>
       </c>
       <c r="AC69" s="25" t="n">
-        <v>0</v>
+        <v>44100</v>
       </c>
       <c r="AD69" s="25" t="n">
         <v>44100</v>
@@ -43029,7 +43029,7 @@
         <v>100000</v>
       </c>
       <c r="AC76" s="25" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AD76" s="25" t="n">
         <v>150000</v>
@@ -43123,10 +43123,10 @@
         <v>700000</v>
       </c>
       <c r="AC77" s="25" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="AD77" s="25" t="n">
-        <v>700000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="78">
@@ -43217,10 +43217,10 @@
         <v>100000</v>
       </c>
       <c r="AC78" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD78" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="79">
@@ -43311,7 +43311,7 @@
         <v>2300000</v>
       </c>
       <c r="AC79" s="25" t="n">
-        <v>0</v>
+        <v>1125000</v>
       </c>
       <c r="AD79" s="25" t="n">
         <v>1125000</v>
@@ -43405,7 +43405,7 @@
         <v>200000</v>
       </c>
       <c r="AC80" s="25" t="n">
-        <v>0</v>
+        <v>710000</v>
       </c>
       <c r="AD80" s="25" t="n">
         <v>710000</v>
@@ -43499,7 +43499,7 @@
         <v>300000</v>
       </c>
       <c r="AC81" s="25" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="AD81" s="25" t="n">
         <v>450000</v>
@@ -43593,7 +43593,7 @@
         <v>0</v>
       </c>
       <c r="AC82" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD82" s="25" t="n">
         <v>100000</v>
@@ -44504,7 +44504,7 @@
         <v>150000</v>
       </c>
       <c r="AC93" s="25" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="AD93" s="25" t="n">
         <v>180000</v>
@@ -44598,7 +44598,7 @@
         <v>100000</v>
       </c>
       <c r="AC94" s="25" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD94" s="25" t="n">
         <v>100000</v>
@@ -44692,7 +44692,7 @@
         <v>77000</v>
       </c>
       <c r="AC95" s="25" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="AD95" s="25" t="n">
         <v>77000</v>
@@ -46441,16 +46441,16 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>10429685209</v>
+        <v>172443992264</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Trinity Bank</t>
+          <t>Addiko Bank a.d. Beograd - New Deal</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>TRINITY BANK a.s.</t>
+          <t>Addiko Bank a.d. Beograd</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -46462,7 +46462,7 @@
         <v>46027</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28000</v>
+        <v>50000</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>2</v>
@@ -46470,16 +46470,16 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>14758904767</v>
+        <v>172443988194</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>TBI Bank</t>
+          <t>OTP banka Srbija - New Deal</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>TBI Bank</t>
+          <t>OTP Serbia (RS)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -46491,7 +46491,7 @@
         <v>46027</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>2</v>
@@ -46499,16 +46499,16 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>172443988194</v>
+        <v>10429685209</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>OTP banka Srbija - New Deal</t>
+          <t>Trinity Bank</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>OTP Serbia (RS)</t>
+          <t>TRINITY BANK a.s.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -46520,7 +46520,7 @@
         <v>46027</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>100000</v>
+        <v>28000</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>2</v>
@@ -46528,16 +46528,16 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>217669364924</v>
+        <v>14758904767</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Burgan Bank - HPS</t>
+          <t>TBI Bank</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Burgan Bank</t>
+          <t>TBI Bank</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -46557,16 +46557,16 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>245983710407</v>
+        <v>217669364924</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Erste Bank Hungary - RPI</t>
+          <t>Burgan Bank - HPS</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Erste Bank Hungary</t>
+          <t>Burgan Bank</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -46578,7 +46578,7 @@
         <v>46027</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>2</v>
@@ -46586,16 +46586,16 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>246885009623</v>
+        <v>245983710407</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Source: Unchain2025; Company: Payall Payment Systems, Inc.</t>
+          <t>Erste Bank Hungary - RPI</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Payall Payment Systems</t>
+          <t>Erste Bank Hungary</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -46607,7 +46607,7 @@
         <v>46027</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>2</v>
@@ -46615,16 +46615,16 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>167910650045</v>
+        <v>246885009623</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Raiffeisenbank Hrvatska</t>
+          <t>Source: Unchain2025; Company: Payall Payment Systems, Inc.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Raiffeisenbank Hrvatska (HR)</t>
+          <t>Payall Payment Systems</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -46644,15 +46644,17 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>251389531345</v>
+        <v>167910650045</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Ukrgasbank, woodpecker</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v/>
+          <t>Source: Linkedin; Company: Raiffeisenbank Hrvatska</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Raiffeisenbank Hrvatska (HR)</t>
+        </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -46671,17 +46673,15 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>10595004131</v>
+        <v>251389531345</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Contact Form: Arab Bank: Mahmoud Zainab</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Arab Bank </t>
-        </is>
+          <t>Ukrgasbank, woodpecker</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v/>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>46027</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>2</v>
@@ -46700,16 +46700,16 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>172443992264</v>
+        <v>10595004131</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Addiko Bank a.d. Beograd - New Deal</t>
+          <t>Contact Form: Arab Bank: Mahmoud Zainab</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Addiko Bank a.d. Beograd</t>
+          <t xml:space="preserve">Arab Bank </t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -46721,7 +46721,7 @@
         <v>46027</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>50000</v>
+        <v>110000</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>2</v>
@@ -46932,28 +46932,28 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>309212736760</v>
+        <v>420883062971</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ABS: Atom Bank</t>
+          <t>Soulbac - inbound na Support@tapix.io</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Atom bank</t>
+          <t>Soulbac</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
         <v>46030</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>2</v>
@@ -46961,28 +46961,28 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>420883062971</v>
+        <v>309212736760</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Soulbac - inbound na Support@tapix.io</t>
+          <t>ABS: Atom Bank</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Soulbac</t>
+          <t>Atom bank</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
         <v>46030</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>2</v>
@@ -47048,16 +47048,16 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>23044845781</v>
+        <v>359288210631</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Montenegro: CKB bank</t>
+          <t>PKO Bank Polski, woodpecker</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>CKB bank</t>
+          <t>PKO Bank Polski</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -47077,16 +47077,16 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>426352077012</v>
+        <v>145158419661</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>M20-25: PayPo (Tapix)</t>
+          <t>Source: Linkedin; Company: OTP banka, Slovenija</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>PayPo</t>
+          <t>OTP banka, Slovenija (SI)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -47098,7 +47098,7 @@
         <v>46035</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>53000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>3</v>
@@ -47106,16 +47106,16 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>145158419661</v>
+        <v>14723060424</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: OTP banka, Slovenija</t>
+          <t>Source: M24; MAIB</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>OTP banka, Slovenija (SI)</t>
+          <t>maib</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -47127,7 +47127,7 @@
         <v>46035</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>3</v>
@@ -47135,16 +47135,16 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>15154900711</v>
+        <v>23044845781</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Source: Unchain2024; Company: Exim Banca Romaneasca</t>
+          <t>Montenegro: CKB bank</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Exim Banca Romaneasca</t>
+          <t>CKB bank</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -47164,16 +47164,16 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>14723060424</v>
+        <v>426352077012</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Source: M24; MAIB</t>
+          <t>M20-25: PayPo (Tapix)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>maib</t>
+          <t>PayPo</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -47185,7 +47185,7 @@
         <v>46035</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>100000</v>
+        <v>53000</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>3</v>
@@ -47193,16 +47193,16 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>359288210631</v>
+        <v>15154900711</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>PKO Bank Polski, woodpecker</t>
+          <t>Source: Unchain2024; Company: Exim Banca Romaneasca</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>PKO Bank Polski</t>
+          <t>Exim Banca Romaneasca</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -47396,16 +47396,16 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>426073329907</v>
+        <v>431449473269</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>: Szabolcs Herman - contact form</t>
+          <t>infaqy.com: waleed dakheel - contact form</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>stashbeat.com</t>
+          <t>infaqy.com</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -47425,16 +47425,16 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>431449473269</v>
+        <v>426073329907</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>infaqy.com: waleed dakheel - contact form</t>
+          <t>: Szabolcs Herman - contact form</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>infaqy.com</t>
+          <t>stashbeat.com</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -47684,16 +47684,16 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>416185461970</v>
+        <v>377691139292</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CashFish: Tarek Hariss - contact form</t>
+          <t>Euronet Worldwide: Kareem Mohsen - contact form</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>CashFish</t>
+          <t>Euronet Worldwide</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -47713,16 +47713,16 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>377691139292</v>
+        <v>416185461970</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Euronet Worldwide: Kareem Mohsen - contact form</t>
+          <t>CashFish: Tarek Hariss - contact form</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Euronet Worldwide</t>
+          <t>CashFish</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -48235,16 +48235,16 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
-        <v>334129298647</v>
+        <v>379637519563</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Workyard: Parisa Gonzalez - contact form</t>
+          <t>ABS: Instabank ASA</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Workyard</t>
+          <t>Instabank ASA</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -48264,16 +48264,16 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>373912705221</v>
+        <v>334129298647</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ABS: Unioo</t>
+          <t>Workyard: Parisa Gonzalez - contact form</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Unioo</t>
+          <t>Workyard</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -48293,28 +48293,28 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>399499961589</v>
+        <v>373912705221</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Ditta: alessio rede - contact form (Tapix)</t>
+          <t>ABS: Unioo</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Ditta</t>
+          <t>Unioo</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
         <v>46077</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>9</v>
@@ -48322,28 +48322,28 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
-        <v>374662080746</v>
+        <v>399499961589</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive Nordics: CRIF</t>
+          <t>Ditta: alessio rede - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Crif</t>
+          <t>Ditta</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
         <v>46077</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>9</v>
@@ -48351,16 +48351,16 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>379637519563</v>
+        <v>374662080746</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>ABS: Instabank ASA</t>
+          <t>MoneyLive Nordics: CRIF</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Instabank ASA</t>
+          <t>Crif</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -48467,16 +48467,16 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>485336151285</v>
+        <v>307034195141</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Hypnosia: Jaroslav Kelnar - contact form</t>
+          <t>Associated Bank: Ilana Nagib - contact form</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Hypnosia</t>
+          <t>Associated Bank</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -48496,16 +48496,16 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>307034195141</v>
+        <v>485336151285</v>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Associated Bank: Ilana Nagib - contact form</t>
+          <t>Hypnosia: Jaroslav Kelnar - contact form</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Associated Bank</t>
+          <t>Hypnosia</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -48583,16 +48583,16 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>15752294872</v>
+        <v>466117866734</v>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Round Robin: Spendly - Igor Orlov (Tapix)</t>
+          <t>bwino.app: Na'im merchant - contact form</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Spendly</t>
+          <t>Bwino</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -48604,7 +48604,7 @@
         <v>46090</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>11</v>
@@ -48612,16 +48612,16 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>466117866734</v>
+        <v>15752294872</v>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>bwino.app: Na'im merchant - contact form</t>
+          <t>Round Robin: Spendly - Igor Orlov (Tapix)</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Bwino</t>
+          <t>Spendly</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -48633,7 +48633,7 @@
         <v>46090</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>11</v>
@@ -49018,16 +49018,16 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
-        <v>458536692968</v>
+        <v>103440566459</v>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Custodia: Ade Adenuga - contact form (Tapix)</t>
+          <t>Lipefi: Georgy Taranov - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Custodia</t>
+          <t>Lipefi</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -49039,7 +49039,7 @@
         <v>46105</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>13</v>
@@ -49076,16 +49076,16 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
-        <v>103440566459</v>
+        <v>458536692968</v>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Lipefi: Georgy Taranov - contact form (Tapix)</t>
+          <t>Custodia: Ade Adenuga - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Lipefi</t>
+          <t>Custodia</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -49097,7 +49097,7 @@
         <v>46105</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>13</v>
@@ -49163,28 +49163,28 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
-        <v>496480275643</v>
+        <v>378001606869</v>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Gimi (Tapix)</t>
+          <t>MiTrust: Richard Dey - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Gimi – Financial Superskills for Life</t>
+          <t>MiTrust</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
         <v>46119</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>15</v>
@@ -49192,28 +49192,28 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
-        <v>378001606869</v>
+        <v>496480275643</v>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>MiTrust: Richard Dey - contact form (Tapix)</t>
+          <t>Gimi (Tapix)</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>MiTrust</t>
+          <t>Gimi – Financial Superskills for Life</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
         <v>46119</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>22000</v>
+        <v>30000</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>15</v>
@@ -49221,28 +49221,28 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
-        <v>497917440237</v>
+        <v>452087602394</v>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Intellias - New Deal</t>
+          <t>getpocket.uk: Ayden Fennell - contact form</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>getpocket.uk</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
         <v>46120</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>15</v>
@@ -49250,16 +49250,16 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
-        <v>497917441210</v>
+        <v>497917440237</v>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Arbitas - New Deal</t>
+          <t>Intellias - New Deal</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Arbitas</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -49279,28 +49279,28 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
-        <v>226816087270</v>
+        <v>497917441210</v>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>BNP Paribas Fortis BE, woodpecker</t>
+          <t>Arbitas - New Deal</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>BNP Paribas Fortis BE</t>
+          <t>Arbitas</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
         <v>46120</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>15</v>
@@ -49308,21 +49308,21 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
-        <v>452087602394</v>
+        <v>226816087270</v>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>getpocket.uk: Ayden Fennell - contact form</t>
+          <t>BNP Paribas Fortis BE, woodpecker</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>getpocket.uk</t>
+          <t>BNP Paribas Fortis BE</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
@@ -49366,16 +49366,16 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
-        <v>167867497663</v>
+        <v>469739059449</v>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>UniCredit Bank Serbia</t>
+          <t>Zapad banka AD Podgorica, woodpecker</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>UniCredit Bank Serbia</t>
+          <t>Zapad banka AD Podgorica</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -49387,7 +49387,7 @@
         <v>46122</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>15</v>
@@ -49395,21 +49395,21 @@
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
-        <v>276512884926</v>
+        <v>309831687359</v>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB, woodpecker</t>
+          <t xml:space="preserve">ABS: ING Poland </t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB</t>
+          <t>ING Poland</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -49424,16 +49424,16 @@
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
-        <v>131338994917</v>
+        <v>167867497663</v>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>BCR - client labeling</t>
+          <t>UniCredit Bank Serbia</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>BCR</t>
+          <t>UniCredit Bank Serbia</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -49445,7 +49445,7 @@
         <v>46122</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>15</v>
@@ -49453,28 +49453,28 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
-        <v>497781911744</v>
+        <v>276512884926</v>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Logicom Public - New Deal</t>
+          <t>NORD/LB, woodpecker</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Logicom Public</t>
+          <t>NORD/LB</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>15</v>
@@ -49482,21 +49482,21 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
-        <v>400708664525</v>
+        <v>131338994917</v>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>instashopify.com: Imran Khan - contact form</t>
+          <t>BCR - client labeling</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>instashopify</t>
+          <t>BCR</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -49511,28 +49511,28 @@
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
-        <v>286785856703</v>
+        <v>497781911744</v>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB - Norddeutsche Landesbank Girozentrale, woodpecker</t>
+          <t>Logicom Public - New Deal</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>NORD/LB - Norddeutsche Landesbank Girozentrale</t>
+          <t>Logicom Public</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" s="7" t="n">
         <v>15</v>
@@ -49540,28 +49540,28 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
-        <v>141989380324</v>
+        <v>400708664525</v>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Thales - New Deal</t>
+          <t>instashopify.com: Imran Khan - contact form</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>instashopify</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>15</v>
@@ -49569,16 +49569,16 @@
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
-        <v>276545506529</v>
+        <v>286785856703</v>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>ING: Maarten Driessen - contact form</t>
+          <t>NORD/LB - Norddeutsche Landesbank Girozentrale, woodpecker</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>NORD/LB - Norddeutsche Landesbank Girozentrale</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -49598,16 +49598,16 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
-        <v>172850432214</v>
+        <v>141989380324</v>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Garanti BBVA</t>
+          <t>Thales - New Deal</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Garanti BBVA ROMANIA (RBI now)</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -49619,7 +49619,7 @@
         <v>46122</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>15</v>
@@ -49627,19 +49627,21 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
-        <v>467637772510</v>
+        <v>276545506529</v>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>, woodpecker</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v/>
+          <t>ING: Maarten Driessen - contact form</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -49654,28 +49656,28 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
-        <v>498502569192</v>
+        <v>172850432214</v>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Arkam Partnership</t>
+          <t>Source: Linkedin; Company: Garanti BBVA</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Arkamtec</t>
+          <t>Garanti BBVA ROMANIA (RBI now)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Lukáš</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>15</v>
@@ -49683,17 +49685,15 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
-        <v>469739059449</v>
+        <v>467637772510</v>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Zapad banka AD Podgorica, woodpecker</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>Zapad banka AD Podgorica</t>
-        </is>
+          <t>, woodpecker</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v/>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
@@ -49712,28 +49712,28 @@
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
-        <v>311084966087</v>
+        <v>498502569192</v>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Mastercard Slovenia</t>
+          <t>Arkam Partnership</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Mastercard Europe</t>
+          <t>Arkamtec</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Lukáš</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
         <v>46122</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>15</v>
@@ -49741,16 +49741,16 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
-        <v>309831687359</v>
+        <v>311084966087</v>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABS: ING Poland </t>
+          <t>Mastercard Slovenia</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>ING Poland</t>
+          <t>Mastercard Europe</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -49913,16 +49913,16 @@
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
-        <v>498499524811</v>
+        <v>498502332660</v>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Guillermo - Sandbox inbound</t>
+          <t>Micapay - New Deal</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>ThinkUp</t>
+          <t>Micapay</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -49942,16 +49942,16 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
-        <v>498502332660</v>
+        <v>498499524811</v>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Micapay - New Deal</t>
+          <t>Guillermo - Sandbox inbound</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Micapay</t>
+          <t>ThinkUp</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -50000,16 +50000,16 @@
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
-        <v>497918877934</v>
+        <v>270710947026</v>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>easypaisa digital bank - New Deal</t>
+          <t>Source: Linkedin; Company: State Bank of India</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>easypaisa digital bank</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -50029,16 +50029,16 @@
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
-        <v>327598518493</v>
+        <v>275565561070</v>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>SAB - Sibos</t>
+          <t>Source: Linkedin; Company: Al-Mansour Bank For Investment - مصرف المنصور للأستثمار</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>Al-Mansour Bank For Investment - مصرف المنصور للأستثمار</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -50050,7 +50050,7 @@
         <v>46127</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>16</v>
@@ -50058,16 +50058,16 @@
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
-        <v>254411071727</v>
+        <v>497918877934</v>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Standard Chartered Bank</t>
+          <t>easypaisa digital bank - New Deal</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>easypaisa digital bank</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -50087,16 +50087,16 @@
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
-        <v>311146490105</v>
+        <v>327598518493</v>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: STC</t>
+          <t>SAB - Sibos</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>STC Bank</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -50108,7 +50108,7 @@
         <v>46127</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="7" t="n">
         <v>16</v>
@@ -50116,16 +50116,16 @@
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
-        <v>282473940183</v>
+        <v>254411071727</v>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: D360 Bank</t>
+          <t>Source: Linkedin; Company: Standard Chartered Bank</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>D360 Bank</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -50145,16 +50145,16 @@
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
-        <v>15773372113</v>
+        <v>311146490105</v>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>United Arab Bank, woodpecker</t>
+          <t>MoneyKSA: STC</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>United Arab Bank</t>
+          <t>STC Bank</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -50174,16 +50174,16 @@
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
-        <v>275565561070</v>
+        <v>282473940183</v>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Al-Mansour Bank For Investment - مصرف المنصور للأستثمار</t>
+          <t>Source: Linkedin; Company: D360 Bank</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Al-Mansour Bank For Investment - مصرف المنصور للأستثمار</t>
+          <t>D360 Bank</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -50203,16 +50203,16 @@
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
-        <v>282683199716</v>
+        <v>15773372113</v>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: alrajhi bank</t>
+          <t>United Arab Bank, woodpecker</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>alrajhi bank</t>
+          <t>United Arab Bank</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -50232,16 +50232,16 @@
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
-        <v>327954289912</v>
+        <v>282683199716</v>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>BFA - Sibos</t>
+          <t>Source: Linkedin; Company: alrajhi bank</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>alrajhi bank</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -50253,7 +50253,7 @@
         <v>46127</v>
       </c>
       <c r="F136" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>16</v>
@@ -50261,16 +50261,16 @@
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
-        <v>270710947026</v>
+        <v>327954289912</v>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: State Bank of India</t>
+          <t>BFA - Sibos</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -50282,7 +50282,7 @@
         <v>46127</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="7" t="n">
         <v>16</v>
@@ -50406,16 +50406,16 @@
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
-        <v>103713858805</v>
+        <v>103818502365</v>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>ABS: Zurcher Kantonalbank</t>
+          <t>ABS: Bank Cler</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Zurcher Kantonalbank</t>
+          <t>Bank Cler</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -50435,16 +50435,16 @@
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
-        <v>159725408500</v>
+        <v>103713858805</v>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive25: Mutual Trust Bank</t>
+          <t>ABS: Zurcher Kantonalbank</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Mutual Trust Bank</t>
+          <t>Zurcher Kantonalbank</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -50464,16 +50464,16 @@
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
-        <v>102674107641</v>
+        <v>159725408500</v>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>ABS:Migros Bank AG</t>
+          <t>MoneyLive25: Mutual Trust Bank</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Migros Bank AG</t>
+          <t>Mutual Trust Bank</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -50493,16 +50493,16 @@
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
-        <v>156852645094</v>
+        <v>102674107641</v>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive 25: Deutsche Bank</t>
+          <t>ABS:Migros Bank AG</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Migros Bank AG</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -50522,28 +50522,28 @@
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
-        <v>403807522024</v>
+        <v>156852645094</v>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Bank Millennium - PFM/X-selling (Tapix)</t>
+          <t>MoneyLive 25: Deutsche Bank</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Bank Millennium</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
         <v>46129</v>
       </c>
       <c r="F146" s="6" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>16</v>
@@ -50551,28 +50551,28 @@
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
-        <v>103818502365</v>
+        <v>403807522024</v>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>ABS: Bank Cler</t>
+          <t>Bank Millennium - PFM/X-selling (Tapix)</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Bank Cler</t>
+          <t>Bank Millennium</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
         <v>46129</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="G147" s="7" t="n">
         <v>16</v>
@@ -50783,16 +50783,16 @@
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
-        <v>496001965267</v>
+        <v>260160741596</v>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Pay360: iFAST</t>
+          <t>ABS: HSBC Innovation Banking</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>iFAST Global Bank Limited</t>
+          <t>HSBC Innovation Banking</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -50812,21 +50812,21 @@
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
-        <v>475421443291</v>
+        <v>496001965267</v>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>: Szymon Bubak - contact form</t>
+          <t>Pay360: iFAST</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Jiai</t>
+          <t>iFAST Global Bank Limited</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
@@ -50841,21 +50841,21 @@
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
-        <v>260160741596</v>
+        <v>475421443291</v>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>ABS: HSBC Innovation Banking</t>
+          <t>: Szymon Bubak - contact form</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>HSBC Innovation Banking</t>
+          <t>Jiai</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
@@ -50928,28 +50928,28 @@
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
-        <v>494470747350</v>
+        <v>459069370612</v>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>ABS: Moneybox</t>
+          <t>: Mitja Simcic - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Moneybox</t>
+          <t>USBC</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
         <v>46146</v>
       </c>
       <c r="F160" s="6" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>19</v>
@@ -50957,28 +50957,28 @@
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
-        <v>431703028948</v>
+        <v>494470747350</v>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>: Mohamed mezar abdalwahab abdelall - contact form (Tapix)</t>
+          <t>ABS: Moneybox</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Trillioni Pay</t>
+          <t>Moneybox</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
         <v>46146</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G161" s="7" t="n">
         <v>19</v>
@@ -50986,16 +50986,16 @@
     </row>
     <row r="162">
       <c r="A162" s="4" t="n">
-        <v>459069370612</v>
+        <v>431703028948</v>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>: Mitja Simcic - contact form (Tapix)</t>
+          <t>: Mohamed mezar abdalwahab abdelall - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>USBC</t>
+          <t>Trillioni Pay</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -51007,7 +51007,7 @@
         <v>46146</v>
       </c>
       <c r="F162" s="6" t="n">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>19</v>
@@ -51015,16 +51015,16 @@
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
-        <v>500721741008</v>
+        <v>495303654637</v>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>mytally.io: Igor Carreira - contact form (Tapix)</t>
+          <t>THORWallet: Marcel Harmann - contact form</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Tally</t>
+          <t>THORWallet</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -51036,7 +51036,7 @@
         <v>46149</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G163" s="7" t="n">
         <v>19</v>
@@ -51044,16 +51044,16 @@
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
-        <v>495303654637</v>
+        <v>499506157817</v>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>THORWallet: Marcel Harmann - contact form</t>
+          <t>: Magdy Z - contact form</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>THORWallet</t>
+          <t>Magdy Zakey</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -51073,16 +51073,16 @@
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
-        <v>499506157817</v>
+        <v>500721741008</v>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>: Magdy Z - contact form</t>
+          <t>mytally.io: Igor Carreira - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Magdy Zakey</t>
+          <t>Tally</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -51094,7 +51094,7 @@
         <v>46149</v>
       </c>
       <c r="F165" s="6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G165" s="7" t="n">
         <v>19</v>
@@ -51189,16 +51189,16 @@
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
-        <v>317181618398</v>
+        <v>291359215826</v>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Emirates NBD</t>
+          <t>BRI - Digital banking</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>PT Bank Rakyat Indonesia (Persero) Tbk</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -51210,7 +51210,7 @@
         <v>46155</v>
       </c>
       <c r="F169" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G169" s="7" t="n">
         <v>20</v>
@@ -51218,16 +51218,16 @@
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
-        <v>496216189115</v>
+        <v>285672625370</v>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Inbound - Manager.one - New Deal (Tapix)</t>
+          <t>Source: Linkedin; Company: The BENEFIT Company</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Manager.one</t>
+          <t>Benefit</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -51239,7 +51239,7 @@
         <v>46155</v>
       </c>
       <c r="F170" s="6" t="n">
-        <v>34175</v>
+        <v>0</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>20</v>
@@ -51247,16 +51247,16 @@
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
-        <v>285715773629</v>
+        <v>247761688768</v>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>SADA PAY</t>
+          <t>Fintech Dubai - Mashreq</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>SadaPay</t>
+          <t>Mashreq Bank</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -51268,7 +51268,7 @@
         <v>46155</v>
       </c>
       <c r="F171" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G171" s="7" t="n">
         <v>20</v>
@@ -51276,16 +51276,16 @@
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
-        <v>328780895427</v>
+        <v>317181618398</v>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>FintechDubai - ADIB (Tapix)</t>
+          <t>Source: Linkedin; Company: Emirates NBD</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>ADIB</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -51297,7 +51297,7 @@
         <v>46155</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>20</v>
@@ -51305,16 +51305,16 @@
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
-        <v>284788523206</v>
+        <v>496216189115</v>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>ABS: Emirates NBD - TBD</t>
+          <t>Inbound - Manager.one - New Deal (Tapix)</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Manager.one</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -51326,7 +51326,7 @@
         <v>46155</v>
       </c>
       <c r="F173" s="6" t="n">
-        <v>0</v>
+        <v>34175</v>
       </c>
       <c r="G173" s="7" t="n">
         <v>20</v>
@@ -51334,16 +51334,16 @@
     </row>
     <row r="174">
       <c r="A174" s="4" t="n">
-        <v>31881524471</v>
+        <v>285715773629</v>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>National Bank of Kuwait - Sami (Tapix)</t>
+          <t>SADA PAY</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>National Bank of Kuwait</t>
+          <t>SadaPay</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -51355,7 +51355,7 @@
         <v>46155</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>20</v>
@@ -51363,16 +51363,16 @@
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
-        <v>453943420130</v>
+        <v>328780895427</v>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finnovex25 - Emirates NBD </t>
+          <t>FintechDubai - ADIB (Tapix)</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>ADIB</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -51384,7 +51384,7 @@
         <v>46155</v>
       </c>
       <c r="F175" s="6" t="n">
-        <v>200000</v>
+        <v>270000</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>20</v>
@@ -51392,21 +51392,21 @@
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
-        <v>496650984634</v>
+        <v>284788523206</v>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Pay360: Banco do Brasil</t>
+          <t>ABS: Emirates NBD - TBD</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Banco do Brasil</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
@@ -51421,16 +51421,16 @@
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
-        <v>285672625370</v>
+        <v>31881524471</v>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: The BENEFIT Company</t>
+          <t>National Bank of Kuwait - Sami (Tapix)</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Benefit</t>
+          <t>National Bank of Kuwait</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -51442,7 +51442,7 @@
         <v>46155</v>
       </c>
       <c r="F177" s="6" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>20</v>
@@ -51450,16 +51450,16 @@
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
-        <v>311443594430</v>
+        <v>453943420130</v>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>LiP2025: CitiBank</t>
+          <t xml:space="preserve">Finnovex25 - Emirates NBD </t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -51471,7 +51471,7 @@
         <v>46155</v>
       </c>
       <c r="F178" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>20</v>
@@ -51479,28 +51479,28 @@
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
-        <v>291359215826</v>
+        <v>496650984634</v>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>BRI - Digital banking</t>
+          <t>Pay360: Banco do Brasil</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>PT Bank Rakyat Indonesia (Persero) Tbk</t>
+          <t>Banco do Brasil</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
         <v>46155</v>
       </c>
       <c r="F179" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G179" s="7" t="n">
         <v>20</v>
@@ -51508,16 +51508,16 @@
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
-        <v>247761688768</v>
+        <v>311443594430</v>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Fintech Dubai - Mashreq</t>
+          <t>LiP2025: CitiBank</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Mashreq Bank</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -51711,16 +51711,16 @@
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
-        <v>467775515879</v>
+        <v>390652136650</v>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Arion Bank, woodpecker</t>
+          <t>MoneyLive Nordics - Holm Bank</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Arion Bank</t>
+          <t>Holm Bank</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -51740,16 +51740,16 @@
     </row>
     <row r="188">
       <c r="A188" s="4" t="n">
-        <v>390652136650</v>
+        <v>467775515879</v>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive Nordics - Holm Bank</t>
+          <t>Arion Bank, woodpecker</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Holm Bank</t>
+          <t>Arion Bank</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -51914,16 +51914,16 @@
     </row>
     <row r="194">
       <c r="A194" s="4" t="n">
-        <v>361599102167</v>
+        <v>480078702810</v>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Plebicom: Benjamin STUTZ - contact form (Tapix)</t>
+          <t>Boshhh Group: lewis camilleri - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Plebicom</t>
+          <t>Boshhh Group</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -51935,7 +51935,7 @@
         <v>46167</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>22</v>
@@ -51943,28 +51943,28 @@
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
-        <v>493860038900</v>
+        <v>361599102167</v>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Raiffeisenbank HR (Tapix)</t>
+          <t>Plebicom: Benjamin STUTZ - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Raiffeisenbank Hrvatska (HR)</t>
+          <t>Plebicom</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
         <v>46167</v>
       </c>
       <c r="F195" s="6" t="n">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="G195" s="7" t="n">
         <v>22</v>
@@ -51972,28 +51972,28 @@
     </row>
     <row r="196">
       <c r="A196" s="4" t="n">
-        <v>480078702810</v>
+        <v>493860038900</v>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Boshhh Group: lewis camilleri - contact form (Tapix)</t>
+          <t>Raiffeisenbank HR (Tapix)</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Boshhh Group</t>
+          <t>Raiffeisenbank Hrvatska (HR)</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
         <v>46167</v>
       </c>
       <c r="F196" s="6" t="n">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>22</v>
@@ -52059,16 +52059,16 @@
     </row>
     <row r="199">
       <c r="A199" s="4" t="n">
-        <v>504371551475</v>
+        <v>495879879885</v>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>fixv: Ramin Rastegar - contact form</t>
+          <t>es.ey.com: Carlota Navarrete - contact form</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>fixv</t>
+          <t>EY Spain</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -52088,16 +52088,16 @@
     </row>
     <row r="200">
       <c r="A200" s="4" t="n">
-        <v>474457421016</v>
+        <v>504371551475</v>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Paylot / Linkedin</t>
+          <t>fixv: Ramin Rastegar - contact form</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Paylot</t>
+          <t>fixv</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -52117,16 +52117,16 @@
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
-        <v>499027245254</v>
+        <v>474457421016</v>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>BRED Banque Populaire: christelle guibout - contact form</t>
+          <t>Paylot / Linkedin</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>BRED Banque Populaire</t>
+          <t>Paylot</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -52146,16 +52146,16 @@
     </row>
     <row r="202">
       <c r="A202" s="4" t="n">
-        <v>495879879885</v>
+        <v>499027245254</v>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>es.ey.com: Carlota Navarrete - contact form</t>
+          <t>BRED Banque Populaire: christelle guibout - contact form</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>EY Spain</t>
+          <t>BRED Banque Populaire</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -52407,16 +52407,16 @@
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
-        <v>90309296366</v>
+        <v>285394684142</v>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>FintechConnect24: Mano.bank</t>
+          <t>N26 - RPI (Tapix)</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Mano.bank</t>
+          <t>N26</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -52428,7 +52428,7 @@
         <v>46184</v>
       </c>
       <c r="F211" s="6" t="n">
-        <v>20000</v>
+        <v>81000</v>
       </c>
       <c r="G211" s="7" t="n">
         <v>24</v>
@@ -52436,16 +52436,16 @@
     </row>
     <row r="212">
       <c r="A212" s="4" t="n">
-        <v>200712206579</v>
+        <v>202506743999</v>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>INTELICA CONSULTING: Meiker Lazo - contact form</t>
+          <t>Belfius</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>INTELICA CONSULTING</t>
+          <t>Belfius</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -52457,7 +52457,7 @@
         <v>46184</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>24</v>
@@ -52465,16 +52465,16 @@
     </row>
     <row r="213">
       <c r="A213" s="4" t="n">
-        <v>273762210003</v>
+        <v>90309296366</v>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>N26, woodpecker</t>
+          <t>FintechConnect24: Mano.bank</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>N26</t>
+          <t>Mano.bank</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -52486,7 +52486,7 @@
         <v>46184</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G213" s="7" t="n">
         <v>24</v>
@@ -52494,19 +52494,21 @@
     </row>
     <row r="214">
       <c r="A214" s="4" t="n">
-        <v>505781803242</v>
+        <v>200712206579</v>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Kuwait Finance House: Abdulrahman M Alsaqran - contact form</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="n">
-        <v/>
+          <t>INTELICA CONSULTING: Meiker Lazo - contact form</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>INTELICA CONSULTING</t>
+        </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Veronika</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
@@ -52521,16 +52523,16 @@
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
-        <v>43653769413</v>
+        <v>273762210003</v>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Uniglobal 24: Volksbank Wien</t>
+          <t>N26, woodpecker</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Volksbank Wien</t>
+          <t>N26</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -52542,7 +52544,7 @@
         <v>46184</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215" s="7" t="n">
         <v>24</v>
@@ -52550,28 +52552,26 @@
     </row>
     <row r="216">
       <c r="A216" s="4" t="n">
-        <v>78258022608</v>
+        <v>505781803242</v>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>FintechConnect24: Luzerner Kantonalbank</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
-          <t>Luzerner Kantonalbank</t>
-        </is>
+          <t>Kuwait Finance House: Abdulrahman M Alsaqran - contact form</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="n">
+        <v/>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Veronika</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" s="7" t="n">
         <v>24</v>
@@ -52579,16 +52579,16 @@
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
-        <v>285394684142</v>
+        <v>43653769413</v>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>N26 - RPI (Tapix)</t>
+          <t>Uniglobal 24: Volksbank Wien</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>N26</t>
+          <t>Volksbank Wien</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -52600,7 +52600,7 @@
         <v>46184</v>
       </c>
       <c r="F217" s="6" t="n">
-        <v>81000</v>
+        <v>1</v>
       </c>
       <c r="G217" s="7" t="n">
         <v>24</v>
@@ -52608,16 +52608,16 @@
     </row>
     <row r="218">
       <c r="A218" s="4" t="n">
-        <v>14786803914</v>
+        <v>78258022608</v>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>M24:Rabobank - New Deal</t>
+          <t>FintechConnect24: Luzerner Kantonalbank</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Rabobank</t>
+          <t>Luzerner Kantonalbank</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -52629,7 +52629,7 @@
         <v>46184</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>24</v>
@@ -52637,16 +52637,16 @@
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
-        <v>202506743999</v>
+        <v>14786803914</v>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Belfius</t>
+          <t>M24:Rabobank - New Deal</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Belfius</t>
+          <t>Rabobank</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -52658,7 +52658,7 @@
         <v>46184</v>
       </c>
       <c r="F219" s="6" t="n">
-        <v>1</v>
+        <v>20000</v>
       </c>
       <c r="G219" s="7" t="n">
         <v>24</v>
@@ -52981,15 +52981,17 @@
     </row>
     <row r="231">
       <c r="A231" s="4" t="n">
-        <v>499951318240</v>
+        <v>500849831140</v>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>: Antoine Lefebvre - contact form</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="n">
-        <v/>
+          <t>Calcul.IA: Camille Bernard - contact form</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>Calcul.IA</t>
+        </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
@@ -53008,17 +53010,15 @@
     </row>
     <row r="232">
       <c r="A232" s="4" t="n">
-        <v>504456380660</v>
+        <v>500697270483</v>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Cornerstone Asset Managers: Mukisa Moses - contact form</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>Cornerstone Asset Managers</t>
-        </is>
+          <t>: Marie Rousseau - contact form</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="n">
+        <v/>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
@@ -53037,11 +53037,11 @@
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
-        <v>499908905161</v>
+        <v>499903363308</v>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>: Léa Morel - contact form</t>
+          <t>: Camille Bernard - contact form</t>
         </is>
       </c>
       <c r="C233" s="4" t="n">
@@ -53064,17 +53064,15 @@
     </row>
     <row r="234">
       <c r="A234" s="4" t="n">
-        <v>314791510235</v>
+        <v>499899778280</v>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>FIZ - New Deal Alex Kosovskiy</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr">
-        <is>
-          <t>FIZ</t>
-        </is>
+          <t>: Chloé Lambert - contact form</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="n">
+        <v/>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
@@ -53085,7 +53083,7 @@
         <v>46202</v>
       </c>
       <c r="F234" s="6" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>27</v>
@@ -53093,15 +53091,17 @@
     </row>
     <row r="235">
       <c r="A235" s="4" t="n">
-        <v>499903363308</v>
+        <v>504698194164</v>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>: Camille Bernard - contact form</t>
-        </is>
-      </c>
-      <c r="C235" s="4" t="n">
-        <v/>
+          <t>Toptal: Stefan Pajkovic - contact form</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>Toptal</t>
+        </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
@@ -53147,11 +53147,11 @@
     </row>
     <row r="237">
       <c r="A237" s="4" t="n">
-        <v>500570087661</v>
+        <v>499951318240</v>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>: Pierre Moreau - contact form</t>
+          <t>: Antoine Lefebvre - contact form</t>
         </is>
       </c>
       <c r="C237" s="4" t="n">
@@ -53174,15 +53174,17 @@
     </row>
     <row r="238">
       <c r="A238" s="4" t="n">
-        <v>500697270483</v>
+        <v>504456380660</v>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>: Marie Rousseau - contact form</t>
-        </is>
-      </c>
-      <c r="C238" s="4" t="n">
-        <v/>
+          <t>Cornerstone Asset Managers: Mukisa Moses - contact form</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Cornerstone Asset Managers</t>
+        </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
@@ -53201,17 +53203,15 @@
     </row>
     <row r="239">
       <c r="A239" s="4" t="n">
-        <v>500700135636</v>
+        <v>499908905161</v>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Calcul.IA: Marie Rousseau - contact form</t>
-        </is>
-      </c>
-      <c r="C239" s="4" t="inlineStr">
-        <is>
-          <t>Calcul.IA</t>
-        </is>
+          <t>: Léa Morel - contact form</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="n">
+        <v/>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
@@ -53230,16 +53230,16 @@
     </row>
     <row r="240">
       <c r="A240" s="4" t="n">
-        <v>500849831140</v>
+        <v>314791510235</v>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Calcul.IA: Camille Bernard - contact form</t>
+          <t>FIZ - New Deal Alex Kosovskiy</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Calcul.IA</t>
+          <t>FIZ</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -53251,7 +53251,7 @@
         <v>46202</v>
       </c>
       <c r="F240" s="6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>27</v>
@@ -53259,11 +53259,11 @@
     </row>
     <row r="241">
       <c r="A241" s="4" t="n">
-        <v>499899778280</v>
+        <v>500570087661</v>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>: Chloé Lambert - contact form</t>
+          <t>: Pierre Moreau - contact form</t>
         </is>
       </c>
       <c r="C241" s="4" t="n">
@@ -53286,16 +53286,16 @@
     </row>
     <row r="242">
       <c r="A242" s="4" t="n">
-        <v>504698194164</v>
+        <v>500700135636</v>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Toptal: Stefan Pajkovic - contact form</t>
+          <t>Calcul.IA: Marie Rousseau - contact form</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Toptal</t>
+          <t>Calcul.IA</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -53518,16 +53518,16 @@
     </row>
     <row r="250">
       <c r="A250" s="4" t="n">
-        <v>311526355159</v>
+        <v>285342572762</v>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: BSF</t>
+          <t>Source: Linkedin; Company: Banque Patronus</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Banque Saudi Fransi</t>
+          <t>Banque Patronus</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -53547,16 +53547,16 @@
     </row>
     <row r="251">
       <c r="A251" s="4" t="n">
-        <v>16200551119</v>
+        <v>245212643546</v>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Jordan Ahli Bank, woodpecker</t>
+          <t>Fintech Dubai:Wio UAE</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Jordan Ahli Bank</t>
+          <t>Wio UAE</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -53568,7 +53568,7 @@
         <v>46219</v>
       </c>
       <c r="F251" s="6" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G251" s="7" t="n">
         <v>29</v>
@@ -53576,16 +53576,16 @@
     </row>
     <row r="252">
       <c r="A252" s="4" t="n">
-        <v>285715078373</v>
+        <v>311526355159</v>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>AXIS India</t>
+          <t>MoneyKSA: BSF</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Axis Bank</t>
+          <t>Banque Saudi Fransi</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -53597,7 +53597,7 @@
         <v>46219</v>
       </c>
       <c r="F252" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>29</v>
@@ -53605,16 +53605,16 @@
     </row>
     <row r="253">
       <c r="A253" s="4" t="n">
-        <v>495269111005</v>
+        <v>16200551119</v>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Manager.one: Melanie FAUCHON - contact form</t>
+          <t>Jordan Ahli Bank, woodpecker</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Manager.one</t>
+          <t>Jordan Ahli Bank</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -53626,7 +53626,7 @@
         <v>46219</v>
       </c>
       <c r="F253" s="6" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G253" s="7" t="n">
         <v>29</v>
@@ -53634,16 +53634,16 @@
     </row>
     <row r="254">
       <c r="A254" s="4" t="n">
-        <v>311549636806</v>
+        <v>285715078373</v>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>MoneyKSA: Drahim</t>
+          <t>AXIS India</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Drahim</t>
+          <t>Axis Bank</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -53655,7 +53655,7 @@
         <v>46219</v>
       </c>
       <c r="F254" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G254" s="7" t="n">
         <v>29</v>
@@ -53663,16 +53663,16 @@
     </row>
     <row r="255">
       <c r="A255" s="4" t="n">
-        <v>501313743042</v>
+        <v>495269111005</v>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank DXB - discovery</t>
+          <t>Manager.one: Melanie FAUCHON - contact form</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>Manager.one</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -53684,7 +53684,7 @@
         <v>46219</v>
       </c>
       <c r="F255" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G255" s="7" t="n">
         <v>29</v>
@@ -53692,16 +53692,16 @@
     </row>
     <row r="256">
       <c r="A256" s="4" t="n">
-        <v>460476222664</v>
+        <v>311549636806</v>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Al Barid Bank - from HPS</t>
+          <t>MoneyKSA: Drahim</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Al Barid Bank</t>
+          <t>Drahim</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -53713,7 +53713,7 @@
         <v>46219</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>29</v>
@@ -53721,16 +53721,16 @@
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
-        <v>285342572762</v>
+        <v>501313743042</v>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: Banque Patronus</t>
+          <t>Standard Chartered Bank DXB - discovery</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Banque Patronus</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -53742,7 +53742,7 @@
         <v>46219</v>
       </c>
       <c r="F257" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G257" s="7" t="n">
         <v>29</v>
@@ -53750,16 +53750,16 @@
     </row>
     <row r="258">
       <c r="A258" s="4" t="n">
-        <v>245212643546</v>
+        <v>460476222664</v>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Fintech Dubai:Wio UAE</t>
+          <t>Al Barid Bank - from HPS</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Wio UAE</t>
+          <t>Al Barid Bank</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -53771,7 +53771,7 @@
         <v>46219</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G258" s="7" t="n">
         <v>29</v>
@@ -54530,7 +54530,7 @@
         <v>500</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD7" s="15" t="n">
         <v>500</v>
@@ -54718,7 +54718,7 @@
         <v>55800</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>0</v>
+        <v>55800</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>55800</v>
@@ -54812,7 +54812,7 @@
         <v>348240</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>0</v>
+        <v>303840</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>303840</v>
@@ -54906,7 +54906,7 @@
         <v>170000</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>150000</v>
@@ -55000,7 +55000,7 @@
         <v>1189350</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>225000</v>
+        <v>1062900</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>1062900</v>
@@ -55094,7 +55094,7 @@
         <v>408830</v>
       </c>
       <c r="AC13" s="15" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="AD13" s="15" t="n">
         <v>500000</v>
@@ -55188,7 +55188,7 @@
         <v>0</v>
       </c>
       <c r="AC14" s="14" t="n">
-        <v>0</v>
+        <v>89015</v>
       </c>
       <c r="AD14" s="14" t="n">
         <v>89015</v>
@@ -55658,7 +55658,7 @@
         <v>2202420</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>254700</v>
+        <v>2191755</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>2191755</v>
@@ -55752,10 +55752,10 @@
         <v>135050</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-1947720</v>
+        <v>-10665</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>1937055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -55846,7 +55846,7 @@
         <v>2382620</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>225000</v>
+        <v>2433955</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>2433955</v>
@@ -55940,10 +55940,10 @@
         <v>141050</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>-2157620</v>
+        <v>51335</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>2208955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -56504,7 +56504,7 @@
         <v>75000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AD29" t="n">
         <v>75000</v>
@@ -56598,7 +56598,7 @@
         <v>250000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AD30" t="n">
         <v>150000</v>
@@ -56692,7 +56692,7 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD31" t="n">
         <v>100000</v>
@@ -56786,7 +56786,7 @@
         <v>3010000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2910000</v>
       </c>
       <c r="AD32" t="n">
         <v>2910000</v>
@@ -56880,7 +56880,7 @@
         <v>3027000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2657000</v>
       </c>
       <c r="AD33" t="n">
         <v>2657000</v>
@@ -56974,7 +56974,7 @@
         <v>1078000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1078000</v>
       </c>
       <c r="AD34" t="n">
         <v>1078000</v>
@@ -57068,7 +57068,7 @@
         <v>2643000</v>
       </c>
       <c r="AC35" t="n">
-        <v>500000</v>
+        <v>2462000</v>
       </c>
       <c r="AD35" t="n">
         <v>2462000</v>
@@ -57162,7 +57162,7 @@
         <v>578755</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>680055</v>
       </c>
       <c r="AD36" t="n">
         <v>680055</v>
@@ -57256,7 +57256,7 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>93700</v>
       </c>
       <c r="AD37" t="n">
         <v>93700</v>
@@ -57538,7 +57538,7 @@
         <v>750</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="AD40" t="n">
         <v>750</v>
@@ -57632,7 +57632,7 @@
         <v>2500</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AD41" t="n">
         <v>1500</v>
@@ -57726,7 +57726,7 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
         <v>1000</v>
@@ -57820,7 +57820,7 @@
         <v>90300</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>87300</v>
       </c>
       <c r="AD43" t="n">
         <v>87300</v>
@@ -57914,7 +57914,7 @@
         <v>363240</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>318840</v>
       </c>
       <c r="AD44" t="n">
         <v>318840</v>
@@ -58008,7 +58008,7 @@
         <v>215600</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>215600</v>
       </c>
       <c r="AD45" t="n">
         <v>215600</v>
@@ -58102,7 +58102,7 @@
         <v>1189350</v>
       </c>
       <c r="AC46" t="n">
-        <v>225000</v>
+        <v>1107900</v>
       </c>
       <c r="AD46" t="n">
         <v>1107900</v>
@@ -58196,7 +58196,7 @@
         <v>520880</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>612050</v>
       </c>
       <c r="AD47" t="n">
         <v>612050</v>
@@ -58290,7 +58290,7 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>89015</v>
       </c>
       <c r="AD48" t="n">
         <v>89015</v>
@@ -58738,10 +58738,10 @@
         <v>141050</v>
       </c>
       <c r="AC52" t="n">
-        <v>-2157620</v>
+        <v>51335</v>
       </c>
       <c r="AD52" t="n">
-        <v>2208955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -58832,7 +58832,7 @@
         <v>2202420</v>
       </c>
       <c r="AC53" t="n">
-        <v>254700</v>
+        <v>2191755</v>
       </c>
       <c r="AD53" t="n">
         <v>2191755</v>
@@ -58926,7 +58926,7 @@
         <v>2382620</v>
       </c>
       <c r="AC54" t="n">
-        <v>225000</v>
+        <v>2433955</v>
       </c>
       <c r="AD54" t="n">
         <v>2433955</v>
@@ -59591,7 +59591,7 @@
         <v>21370</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>0</v>
+        <v>21370</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>21370</v>
@@ -59685,7 +59685,7 @@
         <v>3500</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="AD7" s="15" t="n">
         <v>3500</v>
@@ -59873,7 +59873,7 @@
         <v>8310</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>0</v>
+        <v>8310</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>8310</v>
@@ -60061,7 +60061,7 @@
         <v>5600</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>5600</v>
@@ -60155,7 +60155,7 @@
         <v>90000</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>90000</v>
@@ -60437,7 +60437,7 @@
         <v>95000</v>
       </c>
       <c r="AC15" s="15" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="AD15" s="15" t="n">
         <v>95000</v>
@@ -60813,7 +60813,7 @@
         <v>1020780</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>797000</v>
+        <v>1020780</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>1020780</v>
@@ -60907,10 +60907,10 @@
         <v>0</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-223780</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>223780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -61001,7 +61001,7 @@
         <v>233780</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>270000</v>
+        <v>233780</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>233780</v>
@@ -61095,10 +61095,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>36220</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>-36220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -61565,7 +61565,7 @@
         <v>2137000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2137000</v>
       </c>
       <c r="AD28" t="n">
         <v>2137000</v>
@@ -61659,7 +61659,7 @@
         <v>350000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="AD29" t="n">
         <v>350000</v>
@@ -61847,7 +61847,7 @@
         <v>277002</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>277002</v>
       </c>
       <c r="AD31" t="n">
         <v>277002</v>
@@ -62035,7 +62035,7 @@
         <v>78000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="AD33" t="n">
         <v>78000</v>
@@ -62129,7 +62129,7 @@
         <v>200000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AD34" t="n">
         <v>200000</v>
@@ -62223,7 +62223,7 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -62411,7 +62411,7 @@
         <v>100000</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD37" t="n">
         <v>100000</v>
@@ -62599,7 +62599,7 @@
         <v>21370</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>21370</v>
       </c>
       <c r="AD39" t="n">
         <v>21370</v>
@@ -62693,7 +62693,7 @@
         <v>3500</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="AD40" t="n">
         <v>3500</v>
@@ -62881,7 +62881,7 @@
         <v>8310</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>8310</v>
       </c>
       <c r="AD42" t="n">
         <v>8310</v>
@@ -63069,7 +63069,7 @@
         <v>15600</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="AD44" t="n">
         <v>15600</v>
@@ -63163,7 +63163,7 @@
         <v>90000</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="AD45" t="n">
         <v>90000</v>
@@ -63257,7 +63257,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -63445,7 +63445,7 @@
         <v>95000</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="AD48" t="n">
         <v>95000</v>
@@ -63944,7 +63944,7 @@
         <v>600</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>600</v>
@@ -64038,7 +64038,7 @@
         <v>800</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="AD7" s="15" t="n">
         <v>800</v>
@@ -64226,7 +64226,7 @@
         <v>4200</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>2700</v>
@@ -64320,7 +64320,7 @@
         <v>12600</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>0</v>
+        <v>18960</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>18960</v>
@@ -64414,10 +64414,10 @@
         <v>148835</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>0</v>
+        <v>148835</v>
       </c>
       <c r="AD11" s="15" t="n">
-        <v>148835</v>
+        <v>117835</v>
       </c>
     </row>
     <row r="12">
@@ -64508,10 +64508,10 @@
         <v>315000</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>0</v>
+        <v>315000</v>
       </c>
       <c r="AD12" s="14" t="n">
-        <v>315000</v>
+        <v>384750</v>
       </c>
     </row>
     <row r="13">
@@ -64790,7 +64790,7 @@
         <v>23750</v>
       </c>
       <c r="AC15" s="15" t="n">
-        <v>0</v>
+        <v>23750</v>
       </c>
       <c r="AD15" s="15" t="n">
         <v>23750</v>
@@ -65166,10 +65166,10 @@
         <v>1070785</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>565000</v>
+        <v>1075645</v>
       </c>
       <c r="AD20" s="17" t="n">
-        <v>1075645</v>
+        <v>1114395</v>
       </c>
     </row>
     <row r="21">
@@ -65260,10 +65260,10 @@
         <v>1500</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-505785</v>
+        <v>4860</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>510645</v>
+        <v>38750</v>
       </c>
     </row>
     <row r="22">
@@ -65354,10 +65354,10 @@
         <v>863355</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>0</v>
+        <v>868215</v>
       </c>
       <c r="AD22" s="17" t="n">
-        <v>868215</v>
+        <v>906965</v>
       </c>
     </row>
     <row r="23">
@@ -65448,10 +65448,10 @@
         <v>75182</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>-863355</v>
+        <v>4860</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>868215</v>
+        <v>38750</v>
       </c>
     </row>
     <row r="24">
@@ -66012,7 +66012,7 @@
         <v>560010</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>560010</v>
       </c>
       <c r="AD29" t="n">
         <v>560010</v>
@@ -66106,7 +66106,7 @@
         <v>280009</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>280009</v>
       </c>
       <c r="AD30" t="n">
         <v>280009</v>
@@ -66294,10 +66294,10 @@
         <v>965008</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>915009</v>
       </c>
       <c r="AD32" t="n">
-        <v>915009</v>
+        <v>915010</v>
       </c>
     </row>
     <row r="33" hidden="1">
@@ -66388,7 +66388,7 @@
         <v>1196100</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1249100</v>
       </c>
       <c r="AD33" t="n">
         <v>1249100</v>
@@ -66482,10 +66482,10 @@
         <v>1044175</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1044175</v>
       </c>
       <c r="AD34" t="n">
-        <v>1044175</v>
+        <v>889175</v>
       </c>
     </row>
     <row r="35" hidden="1">
@@ -66576,10 +66576,10 @@
         <v>827750</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>827750</v>
       </c>
       <c r="AD35" t="n">
-        <v>827750</v>
+        <v>982750</v>
       </c>
     </row>
     <row r="36" hidden="1">
@@ -66670,7 +66670,7 @@
         <v>86000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="AD36" t="n">
         <v>86000</v>
@@ -66858,7 +66858,7 @@
         <v>25000</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="AD38" t="n">
         <v>25000</v>
@@ -67046,7 +67046,7 @@
         <v>5600</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="AD40" t="n">
         <v>5600</v>
@@ -67140,7 +67140,7 @@
         <v>2800</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="AD41" t="n">
         <v>2800</v>
@@ -67328,7 +67328,7 @@
         <v>28950</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>27450</v>
       </c>
       <c r="AD43" t="n">
         <v>27450</v>
@@ -67422,7 +67422,7 @@
         <v>143532</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>149892</v>
       </c>
       <c r="AD44" t="n">
         <v>149892</v>
@@ -67516,10 +67516,10 @@
         <v>208835</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>208835</v>
       </c>
       <c r="AD45" t="n">
-        <v>208835</v>
+        <v>177835</v>
       </c>
     </row>
     <row r="46" hidden="1">
@@ -67610,10 +67610,10 @@
         <v>372488</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>372488</v>
       </c>
       <c r="AD46" t="n">
-        <v>372488</v>
+        <v>442238</v>
       </c>
     </row>
     <row r="47" hidden="1">
@@ -67704,7 +67704,7 @@
         <v>77400</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>77400</v>
       </c>
       <c r="AD47" t="n">
         <v>77400</v>
@@ -67892,7 +67892,7 @@
         <v>23750</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>23750</v>
       </c>
       <c r="AD49" t="n">
         <v>23750</v>
@@ -68246,10 +68246,10 @@
         <v>75182</v>
       </c>
       <c r="AC52" t="n">
-        <v>-863355</v>
+        <v>4860</v>
       </c>
       <c r="AD52" t="n">
-        <v>868215</v>
+        <v>38750</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -68340,10 +68340,10 @@
         <v>1070785</v>
       </c>
       <c r="AC53" t="n">
-        <v>565000</v>
+        <v>1075645</v>
       </c>
       <c r="AD53" t="n">
-        <v>1075645</v>
+        <v>1114395</v>
       </c>
     </row>
     <row r="54" hidden="1">
@@ -68434,10 +68434,10 @@
         <v>863355</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>868215</v>
       </c>
       <c r="AD54" t="n">
-        <v>868215</v>
+        <v>906965</v>
       </c>
     </row>
     <row r="55" hidden="1">
@@ -69475,10 +69475,10 @@
         <v>19200</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="AD10" s="14" t="n">
-        <v>19200</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="11">
@@ -69569,7 +69569,7 @@
         <v>7000</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>7000</v>
@@ -69663,7 +69663,7 @@
         <v>87300</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>0</v>
+        <v>87300</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>87300</v>
@@ -69757,7 +69757,7 @@
         <v>61200</v>
       </c>
       <c r="AC13" s="15" t="n">
-        <v>0</v>
+        <v>61200</v>
       </c>
       <c r="AD13" s="15" t="n">
         <v>61200</v>
@@ -69851,7 +69851,7 @@
         <v>38000</v>
       </c>
       <c r="AC14" s="14" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="AD14" s="14" t="n">
         <v>0</v>
@@ -70321,10 +70321,10 @@
         <v>212700</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>0</v>
+        <v>212700</v>
       </c>
       <c r="AD20" s="17" t="n">
-        <v>214700</v>
+        <v>222500</v>
       </c>
     </row>
     <row r="21">
@@ -70415,10 +70415,10 @@
         <v>53450</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-212700</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>214700</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="22">
@@ -70509,10 +70509,10 @@
         <v>219900</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>0</v>
+        <v>219900</v>
       </c>
       <c r="AD22" s="17" t="n">
-        <v>181900</v>
+        <v>189700</v>
       </c>
     </row>
     <row r="23">
@@ -70603,10 +70603,10 @@
         <v>60650</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>-219900</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>181900</v>
+        <v>-30200</v>
       </c>
     </row>
     <row r="24">
@@ -71543,10 +71543,10 @@
         <v>220000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="AD33" t="n">
-        <v>220000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="34" hidden="1">
@@ -71637,7 +71637,7 @@
         <v>35000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="AD34" t="n">
         <v>35000</v>
@@ -71731,7 +71731,7 @@
         <v>194000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="AD35" t="n">
         <v>194000</v>
@@ -71825,7 +71825,7 @@
         <v>68000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="AD36" t="n">
         <v>68000</v>
@@ -71919,7 +71919,7 @@
         <v>40000</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -72577,10 +72577,10 @@
         <v>26400</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="AD44" t="n">
-        <v>26400</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="45" hidden="1">
@@ -72671,7 +72671,7 @@
         <v>7000</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="AD45" t="n">
         <v>7000</v>
@@ -72765,7 +72765,7 @@
         <v>87300</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>87300</v>
       </c>
       <c r="AD46" t="n">
         <v>87300</v>
@@ -72859,7 +72859,7 @@
         <v>61200</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>61200</v>
       </c>
       <c r="AD47" t="n">
         <v>61200</v>
@@ -72953,7 +72953,7 @@
         <v>38000</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -73401,10 +73401,10 @@
         <v>60650</v>
       </c>
       <c r="AC52" t="n">
-        <v>-219900</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>181900</v>
+        <v>-30200</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -73495,10 +73495,10 @@
         <v>212700</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>212700</v>
       </c>
       <c r="AD53" t="n">
-        <v>214700</v>
+        <v>222500</v>
       </c>
     </row>
     <row r="54" hidden="1">
@@ -73589,10 +73589,10 @@
         <v>219900</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>219900</v>
       </c>
       <c r="AD54" t="n">
-        <v>181900</v>
+        <v>189700</v>
       </c>
     </row>
     <row r="55" hidden="1">
@@ -74630,7 +74630,7 @@
         <v>72000</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>72000</v>
@@ -74724,7 +74724,7 @@
         <v>7600</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>7600</v>
@@ -74818,7 +74818,7 @@
         <v>68850</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>0</v>
+        <v>68850</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>68850</v>
@@ -74912,7 +74912,7 @@
         <v>39690</v>
       </c>
       <c r="AC13" s="15" t="n">
-        <v>0</v>
+        <v>39690</v>
       </c>
       <c r="AD13" s="15" t="n">
         <v>39690</v>
@@ -75476,7 +75476,7 @@
         <v>188140</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>0</v>
+        <v>188140</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>188140</v>
@@ -75570,10 +75570,10 @@
         <v>0</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-188140</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>188140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -75664,7 +75664,7 @@
         <v>316410</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>0</v>
+        <v>316410</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>316410</v>
@@ -75758,10 +75758,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>-316410</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>316410</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -76322,7 +76322,7 @@
         <v>605000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>605000</v>
       </c>
       <c r="AD29" t="n">
         <v>605000</v>
@@ -76416,7 +76416,7 @@
         <v>1632000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1632000</v>
       </c>
       <c r="AD30" t="n">
         <v>1632000</v>
@@ -76604,7 +76604,7 @@
         <v>1090000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1090000</v>
       </c>
       <c r="AD32" t="n">
         <v>1090000</v>
@@ -76698,7 +76698,7 @@
         <v>630000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>630001</v>
       </c>
       <c r="AD33" t="n">
         <v>630001</v>
@@ -76792,7 +76792,7 @@
         <v>386000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>386000</v>
       </c>
       <c r="AD34" t="n">
         <v>386000</v>
@@ -76886,7 +76886,7 @@
         <v>153000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="AD35" t="n">
         <v>153000</v>
@@ -76980,7 +76980,7 @@
         <v>44100</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>44100</v>
       </c>
       <c r="AD36" t="n">
         <v>44100</v>
@@ -77356,7 +77356,7 @@
         <v>6050</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>6050</v>
       </c>
       <c r="AD40" t="n">
         <v>6050</v>
@@ -77450,7 +77450,7 @@
         <v>16320</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>16320</v>
       </c>
       <c r="AD41" t="n">
         <v>16320</v>
@@ -77638,7 +77638,7 @@
         <v>32700</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="AD43" t="n">
         <v>32700</v>
@@ -77732,7 +77732,7 @@
         <v>75600</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>75600</v>
       </c>
       <c r="AD44" t="n">
         <v>75600</v>
@@ -77826,7 +77826,7 @@
         <v>77200</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>77200</v>
       </c>
       <c r="AD45" t="n">
         <v>77200</v>
@@ -77920,7 +77920,7 @@
         <v>68850</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>68850</v>
       </c>
       <c r="AD46" t="n">
         <v>68850</v>
@@ -78014,7 +78014,7 @@
         <v>39690</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>39690</v>
       </c>
       <c r="AD47" t="n">
         <v>39690</v>
@@ -78556,10 +78556,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>-316410</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>316410</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -78650,7 +78650,7 @@
         <v>188140</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>188140</v>
       </c>
       <c r="AD53" t="n">
         <v>188140</v>
@@ -78744,7 +78744,7 @@
         <v>316410</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>316410</v>
       </c>
       <c r="AD54" t="n">
         <v>316410</v>
@@ -79409,7 +79409,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>1500</v>
@@ -79503,10 +79503,10 @@
         <v>7000</v>
       </c>
       <c r="AC7" s="15" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="AD7" s="15" t="n">
-        <v>7000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="8">
@@ -79597,10 +79597,10 @@
         <v>1000</v>
       </c>
       <c r="AC8" s="14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" s="14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -79691,7 +79691,7 @@
         <v>69000</v>
       </c>
       <c r="AC9" s="15" t="n">
-        <v>0</v>
+        <v>33750</v>
       </c>
       <c r="AD9" s="15" t="n">
         <v>33750</v>
@@ -79785,7 +79785,7 @@
         <v>24000</v>
       </c>
       <c r="AC10" s="14" t="n">
-        <v>0</v>
+        <v>85200</v>
       </c>
       <c r="AD10" s="14" t="n">
         <v>85200</v>
@@ -79879,7 +79879,7 @@
         <v>60000</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>90000</v>
@@ -79973,7 +79973,7 @@
         <v>0</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AD12" s="14" t="n">
         <v>45000</v>
@@ -80631,7 +80631,7 @@
         <v>162000</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>0</v>
+        <v>263450</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>262450</v>
@@ -80725,10 +80725,10 @@
         <v>0</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-162000</v>
+        <v>101450</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>262450</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="22">
@@ -80819,7 +80819,7 @@
         <v>162000</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>0</v>
+        <v>263450</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>262450</v>
@@ -80913,10 +80913,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>-162000</v>
+        <v>101450</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>262450</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="24">
@@ -81477,7 +81477,7 @@
         <v>100000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AD29" t="n">
         <v>150000</v>
@@ -81571,10 +81571,10 @@
         <v>700000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="AD30" t="n">
-        <v>700000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="31" hidden="1">
@@ -81665,10 +81665,10 @@
         <v>100000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="32" hidden="1">
@@ -81759,7 +81759,7 @@
         <v>2300000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1125000</v>
       </c>
       <c r="AD32" t="n">
         <v>1125000</v>
@@ -81853,7 +81853,7 @@
         <v>200000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>710000</v>
       </c>
       <c r="AD33" t="n">
         <v>710000</v>
@@ -81947,7 +81947,7 @@
         <v>300000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="AD34" t="n">
         <v>450000</v>
@@ -82041,7 +82041,7 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD35" t="n">
         <v>100000</v>
@@ -82511,7 +82511,7 @@
         <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AD40" t="n">
         <v>1500</v>
@@ -82605,10 +82605,10 @@
         <v>7000</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="AD41" t="n">
-        <v>7000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="42" hidden="1">
@@ -82699,10 +82699,10 @@
         <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="43" hidden="1">
@@ -82793,7 +82793,7 @@
         <v>69000</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>33750</v>
       </c>
       <c r="AD43" t="n">
         <v>33750</v>
@@ -82887,7 +82887,7 @@
         <v>24000</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>85200</v>
       </c>
       <c r="AD44" t="n">
         <v>85200</v>
@@ -82981,7 +82981,7 @@
         <v>60000</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="AD45" t="n">
         <v>90000</v>
@@ -83075,7 +83075,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AD46" t="n">
         <v>45000</v>
@@ -83711,10 +83711,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>-162000</v>
+        <v>101450</v>
       </c>
       <c r="AD52" t="n">
-        <v>262450</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -83805,7 +83805,7 @@
         <v>162000</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>263450</v>
       </c>
       <c r="AD53" t="n">
         <v>262450</v>
@@ -83899,7 +83899,7 @@
         <v>162000</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>263450</v>
       </c>
       <c r="AD54" t="n">
         <v>262450</v>
@@ -85034,7 +85034,7 @@
         <v>15400</v>
       </c>
       <c r="AC11" s="15" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AD11" s="15" t="n">
         <v>15400</v>
@@ -85786,7 +85786,7 @@
         <v>15400</v>
       </c>
       <c r="AC20" s="17" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AD20" s="17" t="n">
         <v>15400</v>
@@ -85880,10 +85880,10 @@
         <v>0</v>
       </c>
       <c r="AC21" s="17" t="n">
-        <v>-15400</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="17" t="n">
-        <v>15400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -85974,7 +85974,7 @@
         <v>31900</v>
       </c>
       <c r="AC22" s="17" t="n">
-        <v>0</v>
+        <v>32800</v>
       </c>
       <c r="AD22" s="17" t="n">
         <v>32800</v>
@@ -86068,10 +86068,10 @@
         <v>0</v>
       </c>
       <c r="AC23" s="17" t="n">
-        <v>-31900</v>
+        <v>900</v>
       </c>
       <c r="AD23" s="17" t="n">
-        <v>32800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -86820,7 +86820,7 @@
         <v>150000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="AD31" t="n">
         <v>180000</v>
@@ -86914,7 +86914,7 @@
         <v>100000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD32" t="n">
         <v>100000</v>
@@ -87008,7 +87008,7 @@
         <v>77000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="AD33" t="n">
         <v>77000</v>
@@ -87854,7 +87854,7 @@
         <v>4500</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="AD42" t="n">
         <v>5400</v>
@@ -87948,7 +87948,7 @@
         <v>12000</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="AD43" t="n">
         <v>12000</v>
@@ -88042,7 +88042,7 @@
         <v>15400</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="AD44" t="n">
         <v>15400</v>

--- a/outputs/Sales_Reporting_2026.xlsx
+++ b/outputs/Sales_Reporting_2026.xlsx
@@ -49163,28 +49163,28 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
-        <v>378001606869</v>
+        <v>496480275643</v>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>MiTrust: Richard Dey - contact form (Tapix)</t>
+          <t>Gimi (Tapix)</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>MiTrust</t>
+          <t>Gimi – Financial Superskills for Life</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
         <v>46119</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>22000</v>
+        <v>30000</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>15</v>
@@ -49192,28 +49192,28 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
-        <v>496480275643</v>
+        <v>378001606869</v>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Gimi (Tapix)</t>
+          <t>MiTrust: Richard Dey - contact form (Tapix)</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Gimi – Financial Superskills for Life</t>
+          <t>MiTrust</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
         <v>46119</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>15</v>
@@ -50638,21 +50638,21 @@
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
-        <v>278819580147</v>
+        <v>442319480017</v>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Source: Linkedin; Company: DIB</t>
+          <t>MoneyLive25:Nordea Finland</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>DIB</t>
+          <t>Nordea</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Olda</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
@@ -50667,21 +50667,21 @@
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
-        <v>442319480017</v>
+        <v>278819580147</v>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>MoneyLive25:Nordea Finland</t>
+          <t>Source: Linkedin; Company: DIB</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Nordea</t>
+          <t>DIB</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Olda</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
